--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R114"/>
+  <dimension ref="A1:R117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5155,22 +5155,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quito 3832</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810404273</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5212,14 +5212,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.420412</v>
+        <v>-58.416237</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.616726</v>
+        <v>-34.65477</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,22 +5241,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5298,10 +5298,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.416237</v>
+        <v>-58.411426</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.65477</v>
+        <v>-34.633266</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,22 +5327,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5377,21 +5377,21 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.411426</v>
+        <v>-58.435731</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.633266</v>
+        <v>-34.597659</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,22 +5413,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/24/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>Munich 1715</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810447258</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5463,31 +5463,31 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.435731</v>
+        <v>-58.453119</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.597659</v>
+        <v>-34.55489</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>BLO-C</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,27 +5499,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10/24/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>QUITO 3954</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810447247</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5553,17 +5553,17 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.422216</v>
+        <v>-58.4018</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.616828</v>
+        <v>-34.590471</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/24/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Munich 1715</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810447258</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5642,24 +5642,24 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.453119</v>
+        <v>-58.418542</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.55489</v>
+        <v>-34.624609</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>BLO-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>INDEPENDENCIA AV. 3690</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810451588</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5725,17 +5725,17 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.4018</v>
+        <v>-58.417821</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.590471</v>
+        <v>-34.621158</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5814,14 +5814,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.418542</v>
+        <v>-58.430613</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.624609</v>
+        <v>-34.608805</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 3690</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810451588</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5900,24 +5900,24 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.417821</v>
+        <v>-58.50161</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.621158</v>
+        <v>-34.647648</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5929,22 +5929,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5986,14 +5986,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.430613</v>
+        <v>-58.439164</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.608805</v>
+        <v>-34.597069</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6015,22 +6015,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6072,24 +6072,24 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.50161</v>
+        <v>-58.417634</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.647648</v>
+        <v>-34.587439</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6101,7 +6101,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1684</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01230516</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>colocar columna para pedir traspaso de nodo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6158,14 +6158,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.439164</v>
+        <v>-58.402647</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.597069</v>
+        <v>-34.591114</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6187,27 +6187,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>S01150217</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>Vera 311</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>01230602</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Traspasar Fuente</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6232,22 +6232,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.417634</v>
+        <v>-58.436262</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.587439</v>
+        <v>-34.600478</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6273,22 +6273,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1684</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01230516</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>colocar columna para pedir traspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6330,24 +6330,24 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.402647</v>
+        <v>-58.48121</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.591114</v>
+        <v>-34.61126</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6359,22 +6359,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>QUITO 4180</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>810471618</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6416,14 +6416,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.425596</v>
+        <v>-58.440031</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.617038</v>
+        <v>-34.575409</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6445,27 +6445,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S01150217</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vera 311</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01230602</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Traspasar Fuente</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6490,26 +6490,26 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.436262</v>
+        <v>-58.413563</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.600478</v>
+        <v>-34.624645</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6531,22 +6531,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6588,24 +6588,24 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.48121</v>
+        <v>-58.364132</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.61126</v>
+        <v>-34.628423</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6617,22 +6617,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t xml:space="preserve">7829 </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6674,14 +6674,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.440031</v>
+        <v>-58.460356</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.575409</v>
+        <v>-34.630793</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6703,22 +6703,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6760,14 +6760,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.413563</v>
+        <v>-58.389676</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.624645</v>
+        <v>-34.618127</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6789,22 +6789,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>GUTENBERG 3212</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810651343</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Cambiar columna y ver que el vano quede separado del balcon esta inclinada hacia la casa</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6846,56 +6846,56 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.364132</v>
+        <v>-58.501325</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.628423</v>
+        <v>-34.594325</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>PUE-Q</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PUE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7829 </t>
+          <t>-670</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>Timoteo Gordillo 1666</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810651269</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6932,24 +6932,24 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.460356</v>
+        <v>-58.510994</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.630793</v>
+        <v>-34.655027</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6961,22 +6961,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7018,14 +7018,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.389676</v>
+        <v>-58.418108</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.618127</v>
+        <v>-34.62564</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7047,22 +7047,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GUTENBERG 3212</t>
+          <t>2 DE ABRIL DE 1982 6510</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>810651343</t>
+          <t>01411184</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cambiar columna y ver que el vano quede separado del balcon esta inclinada hacia la casa</t>
+          <t>Desmontar poste en desuso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7097,63 +7097,63 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.501325</v>
+        <v>-58.490261</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.594325</v>
+        <v>-34.677337</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PUE-Q</t>
+          <t>PAV-M</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-670</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Timoteo Gordillo 1666</t>
+          <t>CAMPICHUELO 215</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>810651269</t>
+          <t>810712875</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7190,24 +7190,24 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.510994</v>
+        <v>-58.433771</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.655027</v>
+        <v>-34.614668</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7219,7 +7219,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7276,14 +7276,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.418108</v>
+        <v>-58.433855</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.62564</v>
+        <v>-34.614487</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7305,22 +7305,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2 DE ABRIL DE 1982 6510</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7335,17 +7335,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01411184</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Desmontar poste en desuso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7355,31 +7355,31 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.490261</v>
+        <v>-58.441198</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.677337</v>
+        <v>-34.605341</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PAV-M</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7391,22 +7391,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 215</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>810712875</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7448,14 +7448,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.433771</v>
+        <v>-58.439239</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.614668</v>
+        <v>-34.6604</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7477,22 +7477,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7534,14 +7534,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.433855</v>
+        <v>-58.388529</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.614487</v>
+        <v>-34.655949</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7563,22 +7563,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7620,14 +7620,14 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.441198</v>
+        <v>-58.491325</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.605341</v>
+        <v>-34.647761</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7649,22 +7649,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t xml:space="preserve">7869 </t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7706,14 +7706,14 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.439239</v>
+        <v>-58.469394</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.6604</v>
+        <v>-34.626925</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7735,22 +7735,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7792,14 +7792,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.388529</v>
+        <v>-58.390974</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.655949</v>
+        <v>-34.594177</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7821,22 +7821,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t xml:space="preserve">7898 </t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7878,24 +7878,24 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.491325</v>
+        <v>-58.459955</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.647761</v>
+        <v>-34.631973</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7907,22 +7907,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869 </t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7964,51 +7964,51 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.469394</v>
+        <v>-58.48802</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.626925</v>
+        <v>-34.641075</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>Cafayate 5230</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811198624</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8050,14 +8050,14 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.390974</v>
+        <v>-58.465491</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.594177</v>
+        <v>-34.687203</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>PAV-T</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8079,22 +8079,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898 </t>
+          <t>7927</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>Pico 3481</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811198751</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8129,31 +8129,31 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.459955</v>
+        <v>-58.484883</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.631973</v>
+        <v>-34.54464</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8165,22 +8165,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8222,51 +8222,51 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.48802</v>
+        <v>-58.463198</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.641075</v>
+        <v>-34.62624</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cafayate 5230</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811198624</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8308,51 +8308,51 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.465491</v>
+        <v>-58.471183</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.687203</v>
+        <v>-34.638988</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PAV-T</t>
+          <t>PCH-O</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t xml:space="preserve">7997 </t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pico 3481</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811198751</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8387,31 +8387,31 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.484883</v>
+        <v>-58.46357</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.54464</v>
+        <v>-34.623187</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8423,22 +8423,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t xml:space="preserve">8001 </t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>CASTRO, EMILIO AV. 7650</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811299445</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8473,31 +8473,31 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.463198</v>
+        <v>-58.524273</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.62624</v>
+        <v>-34.65615</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PAV-I</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8509,22 +8509,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t xml:space="preserve">8061 </t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t xml:space="preserve">FOREST AV. 957 </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8559,21 +8559,21 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.471183</v>
+        <v>-58.45732</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.638988</v>
+        <v>-34.581366</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8583,29 +8583,29 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>PCH-O</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7997 </t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8652,10 +8652,10 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.46357</v>
+        <v>-58.459547</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.623187</v>
+        <v>-34.626309</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8681,22 +8681,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8001 </t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CASTRO, EMILIO AV. 7650</t>
+          <t>USPALLATA 3625</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811299445</t>
+          <t>811454350</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8731,31 +8731,31 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.524273</v>
+        <v>-58.414313</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.65615</v>
+        <v>-34.641194</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>PAV-I</t>
+          <t>PPT-G</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8767,22 +8767,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8061 </t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOREST AV. 957 </t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8817,31 +8817,31 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.45732</v>
+        <v>-58.465166</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.581366</v>
+        <v>-34.670435</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8853,22 +8853,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t xml:space="preserve">8145 </t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>GUAMINI 5049</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811498019</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t xml:space="preserve">corroida </t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8910,10 +8910,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.459547</v>
+        <v>-58.475365</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.626309</v>
+        <v>-34.688865</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PAV-S</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8939,17 +8939,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USPALLATA 3625</t>
+          <t xml:space="preserve">TRAFUL 3812 </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811454350</t>
+          <t>811498075</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8996,14 +8996,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.414313</v>
+        <v>-58.414437</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.641194</v>
+        <v>-34.651882</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>PPT-G</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9025,17 +9025,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9055,12 +9055,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9082,14 +9082,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.465166</v>
+        <v>-58.438399</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.670435</v>
+        <v>-34.663958</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9111,17 +9111,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8145 </t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GUAMINI 5049</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811498019</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida </t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9168,10 +9168,10 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.475365</v>
+        <v>-58.475565</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.688865</v>
+        <v>-34.660488</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>PAV-S</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9197,22 +9197,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1/23/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRAFUL 3812 </t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811498075</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9254,14 +9254,14 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.414437</v>
+        <v>-58.460855</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.651882</v>
+        <v>-34.631046</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9283,17 +9283,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9340,14 +9340,14 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>-58.438399</v>
+        <v>-58.479751</v>
       </c>
       <c r="N104" t="n">
-        <v>-34.663958</v>
+        <v>-34.677211</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9369,22 +9369,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -9426,51 +9426,51 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>-58.475565</v>
+        <v>-58.491573</v>
       </c>
       <c r="N105" t="n">
-        <v>-34.660488</v>
+        <v>-34.639215</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -9512,36 +9512,36 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>-58.460855</v>
+        <v>-58.487715</v>
       </c>
       <c r="N106" t="n">
-        <v>-34.631046</v>
+        <v>-34.636671</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t xml:space="preserve">8245 </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -9598,51 +9598,51 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>-58.479751</v>
+        <v>-58.488539</v>
       </c>
       <c r="N107" t="n">
-        <v>-34.677211</v>
+        <v>-34.640962</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -9684,51 +9684,51 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>-58.491573</v>
+        <v>-58.481162</v>
       </c>
       <c r="N108" t="n">
-        <v>-34.639215</v>
+        <v>-34.665875</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>-747</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9770,51 +9770,47 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>-58.487715</v>
+        <v>-58.413945</v>
       </c>
       <c r="N109" t="n">
-        <v>-34.636671</v>
+        <v>-34.582774</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245 </t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
+          <t>S01421388</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9829,12 +9825,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9853,49 +9849,49 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-58.488539</v>
+        <v>-58.437739</v>
       </c>
       <c r="N110" t="n">
-        <v>-34.640962</v>
+        <v>-34.638224</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>LEGUIZAMON, MARTINIANO 3983</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9915,12 +9911,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9935,17 +9931,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>-58.481162</v>
+        <v>-58.479051</v>
       </c>
       <c r="N111" t="n">
-        <v>-34.665875</v>
+        <v>-34.675657</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9971,18 +9967,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S01421388</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2/10/2026</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>LEGUIZAMON, MARTINIANO 3951</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10021,13 +10021,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>-58.437739</v>
+        <v>-58.479542</v>
       </c>
       <c r="N112" t="n">
-        <v>-34.638224</v>
+        <v>-34.675295</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10053,22 +10053,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>-759</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LEGUIZAMON, MARTINIANO 3983</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10103,17 +10103,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>-58.479051</v>
+        <v>-58.469878</v>
       </c>
       <c r="N113" t="n">
-        <v>-34.675657</v>
+        <v>-34.626919</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10139,86 +10139,344 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LEGUIZAMON, MARTINIANO 3951</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>inclinada corroida</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-58.46026</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-34.640706</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>PPT-N</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>8268</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MONTREAL 5391</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>inclinada</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L114" t="n">
-        <v>1</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-58.479542</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-34.675295</v>
-      </c>
-      <c r="O114" t="inlineStr">
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>-58.480708</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-34.667639</v>
+      </c>
+      <c r="O115" t="inlineStr">
         <is>
           <t>Boedo</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="P115" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>PAV-Q</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="R115" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>8244</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZELADA 4401 </t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-58.488539</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-34.640962</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>PCH-S</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2PCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>S00936659</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>inclinada</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>-58.474151</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-34.630046</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>NRA-R</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R117"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,22 +1895,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2/17/2025</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN PEDRITO AV. 96</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>803607768</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.468938</v>
+        <v>-58.423042</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.632015</v>
+        <v>-34.625868</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1981,27 +1981,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>3/27/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>THAMES 649</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>804309655</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2038,14 +2038,14 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.423042</v>
+        <v>-58.441405</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.625868</v>
+        <v>-34.594348</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>THAMES 649</t>
+          <t>ZELARRAYAN 6147</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2097,14 +2097,10 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>804309655</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
-        </is>
-      </c>
+          <t>804309801</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2124,14 +2120,14 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.441405</v>
+        <v>-58.483821</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.594348</v>
+        <v>-34.677698</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2141,7 +2137,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2153,27 +2149,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ZELARRAYAN 6147</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2183,10 +2179,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>804309801</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>804569065</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2206,14 +2206,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.483821</v>
+        <v>-58.425764</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.677698</v>
+        <v>-34.604359</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2235,22 +2235,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/22/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MONTES DE OCA, MANUEL AV. 511</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804876051</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>Pegar los ductos al prfv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2292,14 +2292,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.425764</v>
+        <v>-58.375515</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.604359</v>
+        <v>-34.634393</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2321,17 +2321,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4/22/2025</t>
+          <t>5/4/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 511</t>
+          <t>AZARA 15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>804876051</t>
+          <t>805655333</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pegar los ductos al prfv</t>
+          <t>Picada entro tambien como reclamo 7611</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2378,10 +2378,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.375515</v>
+        <v>-58.372751</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.634393</v>
+        <v>-34.631917</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2407,22 +2407,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2464,14 +2464,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.372751</v>
+        <v>-58.395063</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.631917</v>
+        <v>-34.606257</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2493,22 +2493,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2523,51 +2523,51 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.395063</v>
+        <v>-58.483927</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.606257</v>
+        <v>-34.570689</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2579,22 +2579,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2636,24 +2636,24 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.483927</v>
+        <v>-58.477944</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.570689</v>
+        <v>-34.675149</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2665,27 +2665,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5/29/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GARCIA, PEDRO A.,CNEL. 5887</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>807044186</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Columna con base corroída</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2722,14 +2722,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.467789</v>
+        <v>-58.416477</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.68463</v>
+        <v>-34.61303</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2751,22 +2751,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2801,21 +2801,21 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.477944</v>
+        <v>-58.425478</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.675149</v>
+        <v>-34.601865</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2837,22 +2837,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6/4/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EL SERENO 358</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2867,78 +2867,78 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>807168098</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Poste inclinado</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.487371</v>
+        <v>-58.401624</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.640099</v>
+        <v>-34.612001</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2953,14 +2953,10 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>807215439</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Picada</t>
-        </is>
-      </c>
+          <t>807851584</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2980,10 +2976,10 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.416477</v>
+        <v>-58.401827</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.61303</v>
+        <v>-34.617667</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3009,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>8/6/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>SAN ANTONIO 1221</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3039,17 +3035,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>808733914</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Aplomar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3066,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.425478</v>
+        <v>-58.375684</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.601865</v>
+        <v>-34.656092</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3083,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3095,22 +3091,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>8/7/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>RIVADAVIA MARTIN, COMODORO 1350</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3125,51 +3121,51 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>808749184</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Desmontar PRFV 400</t>
+          <t>Poste inclinado ingreso tambien como 7201</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.401624</v>
+        <v>-58.461024</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.612001</v>
+        <v>-34.539409</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>BLO-F</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3181,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3211,10 +3207,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>807851584</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>808918687</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3231,13 +3231,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.401827</v>
+        <v>-58.425858</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.617667</v>
+        <v>-34.61629</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>9/2/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2 DE ABRIL DE 1982 6982</t>
+          <t>Pedro Rivera 2546</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,51 +3293,51 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ICD30334420</t>
+          <t>ICD30612785</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Traspasar a columna o cortar redes en punta y desmontar poste</t>
+          <t>Colocar R200 para pedir traspaso de equipos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.494864</v>
+        <v>-58.462479</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.678826</v>
+        <v>-34.55765</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>PAV-M</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAN ANTONIO 1221</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>808733914</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3406,24 +3406,24 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.375684</v>
+        <v>-58.458298</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.656092</v>
+        <v>-34.566511</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8/7/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RIVADAVIA MARTIN, COMODORO 1350</t>
+          <t>LARRALDE, CRISOLOGO AV. 3875</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>808749184</t>
+          <t>809784524</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Poste inclinado ingreso tambien como 7201</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.461024</v>
+        <v>-58.481316</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.539409</v>
+        <v>-34.556157</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>BLO-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,27 +3521,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3551,41 +3551,41 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.425858</v>
+        <v>-58.409278</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.61629</v>
+        <v>-34.653566</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9/2/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pedro Rivera 2546</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ICD30612785</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipos</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,24 +3664,24 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.462479</v>
+        <v>-58.399262</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.55765</v>
+        <v>-34.639685</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,17 +3693,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/23/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>CIUDAD DE LA PAZ 911</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>ICD30958043</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Desmonte de columna ya traspasaron un nodo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3750,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.458298</v>
+        <v>-58.447743</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.566511</v>
+        <v>-34.570457</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>COG-C</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9/15/2025</t>
+          <t>9/25/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAN NICOLAS 5123</t>
+          <t>MANZANARES 4186</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>809758863</t>
+          <t>809979726</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3829,21 +3829,21 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.516218</v>
+        <v>-58.485454</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.589343</v>
+        <v>-34.555745</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LARRALDE, CRISOLOGO AV. 3875</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>809784524</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3915,31 +3915,31 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.481316</v>
+        <v>-58.384406</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.556157</v>
+        <v>-34.622932</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>BONIFACIO, JOSE 2409</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,17 +3981,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>810132768</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada volvio a ingresar mail con caso 7597</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4001,21 +4001,21 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.409278</v>
+        <v>-58.461482</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.653566</v>
+        <v>-34.632432</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,27 +4037,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4094,14 +4094,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.399262</v>
+        <v>-58.465176</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.639685</v>
+        <v>-34.680979</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9/23/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 911</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ICD30958043</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Desmonte de columna ya traspasaron un nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4180,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.447743</v>
+        <v>-58.46138</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.570457</v>
+        <v>-34.629774</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MANZANARES 4186</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>809979726</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4266,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.485454</v>
+        <v>-58.458516</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.555745</v>
+        <v>-34.646422</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BACACAY AV. 5805</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>809979728</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cambiar y reparar rienda</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4345,58 +4345,58 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.509324</v>
+        <v>-58.374086</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.635335</v>
+        <v>-34.633168</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>DEV-M</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MIRALLA 954</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>809979735</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4438,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.501431</v>
+        <v>-58.416237</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.647791</v>
+        <v>-34.65477</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4524,10 +4524,10 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.384406</v>
+        <v>-58.411426</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.622932</v>
+        <v>-34.633266</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PERIBEBUY 6814</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810132728</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4603,31 +4603,31 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.521719</v>
+        <v>-58.435731</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.647467</v>
+        <v>-34.597659</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PAV-C</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/24/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2409</t>
+          <t>Munich 1715</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810132768</t>
+          <t>810447258</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada volvio a ingresar mail con caso 7597</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4696,24 +4696,24 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.461482</v>
+        <v>-58.453119</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.632432</v>
+        <v>-34.55489</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>BLO-C</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,22 +4725,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4779,17 +4779,17 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.465176</v>
+        <v>-58.4018</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.680979</v>
+        <v>-34.590471</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,22 +4811,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4868,10 +4868,10 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.46138</v>
+        <v>-58.418542</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.629774</v>
+        <v>-34.624609</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,22 +4897,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4954,14 +4954,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.458516</v>
+        <v>-58.430613</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.646422</v>
+        <v>-34.608805</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,24 +5040,24 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.374086</v>
+        <v>-58.50161</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.633168</v>
+        <v>-34.647648</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,22 +5069,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10/17/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ALCARAZ 5168</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810378783</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5126,24 +5126,24 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.50875</v>
+        <v>-58.439164</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.623434</v>
+        <v>-34.597069</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>DEV-H</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,22 +5155,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5212,14 +5212,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.416237</v>
+        <v>-58.417634</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.65477</v>
+        <v>-34.587439</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,27 +5241,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>S01150217</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>Vera 311</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>01230602</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Traspasar Fuente</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5286,26 +5286,26 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.411426</v>
+        <v>-58.436262</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.633266</v>
+        <v>-34.600478</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,22 +5327,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5377,31 +5377,31 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.435731</v>
+        <v>-58.48121</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.597659</v>
+        <v>-34.61126</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,22 +5413,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/24/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Munich 1715</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810447258</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5470,24 +5470,24 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.453119</v>
+        <v>-58.440031</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.55489</v>
+        <v>-34.575409</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>BLO-C</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,27 +5499,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5553,17 +5553,17 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.4018</v>
+        <v>-58.413563</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.590471</v>
+        <v>-34.624645</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5642,14 +5642,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.418542</v>
+        <v>-58.364132</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.624609</v>
+        <v>-34.628423</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,22 +5671,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t xml:space="preserve">7829 </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 3690</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810451588</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5728,10 +5728,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.417821</v>
+        <v>-58.460356</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.621158</v>
+        <v>-34.630793</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,22 +5757,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5814,14 +5814,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.430613</v>
+        <v>-58.389676</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.608805</v>
+        <v>-34.618127</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,17 +5843,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>-670</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>Timoteo Gordillo 1666</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810651269</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5900,10 +5900,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.50161</v>
+        <v>-58.510994</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.647648</v>
+        <v>-34.655027</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5929,22 +5929,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5986,14 +5986,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.439164</v>
+        <v>-58.418108</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.597069</v>
+        <v>-34.62564</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6015,22 +6015,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>CAMPICHUELO 215</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810712875</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6072,14 +6072,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.417634</v>
+        <v>-58.433771</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.587439</v>
+        <v>-34.614668</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1684</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01230516</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>colocar columna para pedir traspaso de nodo</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6158,14 +6158,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.402647</v>
+        <v>-58.433855</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.591114</v>
+        <v>-34.614487</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6187,17 +6187,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01150217</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vera 311</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01230602</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Traspasar Fuente</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6232,36 +6232,36 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.436262</v>
+        <v>-58.441198</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.600478</v>
+        <v>-34.605341</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6273,22 +6273,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6330,24 +6330,24 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.48121</v>
+        <v>-58.439239</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.61126</v>
+        <v>-34.6604</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6359,22 +6359,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6416,14 +6416,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.440031</v>
+        <v>-58.388529</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.575409</v>
+        <v>-34.655949</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6445,22 +6445,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6502,24 +6502,24 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.413563</v>
+        <v>-58.491325</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.624645</v>
+        <v>-34.647761</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6531,22 +6531,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t xml:space="preserve">7869 </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6588,14 +6588,14 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.364132</v>
+        <v>-58.469394</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.628423</v>
+        <v>-34.626925</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6617,22 +6617,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7829 </t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6674,14 +6674,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.460356</v>
+        <v>-58.390974</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.630793</v>
+        <v>-34.594177</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6703,22 +6703,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t xml:space="preserve">7898 </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6760,14 +6760,14 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.389676</v>
+        <v>-58.459955</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.618127</v>
+        <v>-34.631973</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6789,22 +6789,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GUTENBERG 3212</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>810651343</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Cambiar columna y ver que el vano quede separado del balcon esta inclinada hacia la casa</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6846,14 +6846,14 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.501325</v>
+        <v>-58.48802</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.594325</v>
+        <v>-34.641075</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6863,39 +6863,39 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PUE-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PUE</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-670</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Timoteo Gordillo 1666</t>
+          <t>Pico 3481</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>810651269</t>
+          <t>811198751</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6925,21 +6925,21 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.510994</v>
+        <v>-58.484883</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.655027</v>
+        <v>-34.54464</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6961,22 +6961,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7018,10 +7018,10 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.418108</v>
+        <v>-58.463198</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.62564</v>
+        <v>-34.62624</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7047,22 +7047,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2 DE ABRIL DE 1982 6510</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>01411184</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Desmontar poste en desuso</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Desmonte</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7097,58 +7097,58 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.490261</v>
+        <v>-58.471183</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.677337</v>
+        <v>-34.638988</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PAV-M</t>
+          <t>PCH-O</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t xml:space="preserve">7997 </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 215</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>810712875</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7190,14 +7190,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.433771</v>
+        <v>-58.46357</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.614668</v>
+        <v>-34.623187</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7219,22 +7219,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>CASTRO, EMILIO AV. 7650</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>811299445</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7269,31 +7269,31 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.433855</v>
+        <v>-58.524273</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.614487</v>
+        <v>-34.65615</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PAV-I</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7305,17 +7305,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t xml:space="preserve">8061 </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t xml:space="preserve">FOREST AV. 957 </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7355,21 +7355,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.441198</v>
+        <v>-58.45732</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.605341</v>
+        <v>-34.581366</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7391,22 +7391,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7448,14 +7448,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.439239</v>
+        <v>-58.459547</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.6604</v>
+        <v>-34.626309</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7477,17 +7477,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>USPALLATA 3625</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>811454350</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7534,14 +7534,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.388529</v>
+        <v>-58.414313</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.655949</v>
+        <v>-34.641194</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PPT-G</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7563,22 +7563,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7620,24 +7620,24 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.491325</v>
+        <v>-58.465166</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.647761</v>
+        <v>-34.670435</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7649,22 +7649,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869 </t>
+          <t xml:space="preserve">8145 </t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>GUAMINI 5049</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>811498019</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t xml:space="preserve">corroida </t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7706,10 +7706,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.469394</v>
+        <v>-58.475365</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.626925</v>
+        <v>-34.688865</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PAV-S</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7735,22 +7735,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t xml:space="preserve">TRAFUL 3812 </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811498075</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7792,14 +7792,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.390974</v>
+        <v>-58.414437</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.594177</v>
+        <v>-34.651882</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7821,22 +7821,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898 </t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7878,14 +7878,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.459955</v>
+        <v>-58.438399</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.631973</v>
+        <v>-34.663958</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7907,22 +7907,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7964,51 +7964,51 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.48802</v>
+        <v>-58.475565</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.641075</v>
+        <v>-34.660488</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cafayate 5230</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8023,12 +8023,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811198624</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8050,10 +8050,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.465491</v>
+        <v>-58.460855</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.687203</v>
+        <v>-34.631046</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PAV-T</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8079,22 +8079,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pico 3481</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811198751</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8129,31 +8129,31 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L90" t="n">
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.484883</v>
+        <v>-58.479751</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.54464</v>
+        <v>-34.677211</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8165,22 +8165,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8222,51 +8222,51 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.463198</v>
+        <v>-58.491573</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.62624</v>
+        <v>-34.639215</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8308,10 +8308,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.471183</v>
+        <v>-58.487715</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.638988</v>
+        <v>-34.636671</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PCH-O</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8337,22 +8337,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7997 </t>
+          <t xml:space="preserve">8245 </t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8394,51 +8394,51 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.46357</v>
+        <v>-58.488539</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.623187</v>
+        <v>-34.640962</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8001 </t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CASTRO, EMILIO AV. 7650</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811299445</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8473,31 +8473,31 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.524273</v>
+        <v>-58.481162</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.65615</v>
+        <v>-34.665875</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>PAV-I</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8509,22 +8509,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8061 </t>
+          <t>-747</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOREST AV. 957 </t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8559,31 +8559,31 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.45732</v>
+        <v>-58.413945</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.581366</v>
+        <v>-34.582774</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8595,17 +8595,13 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S00982176</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1/9/2026</t>
-        </is>
-      </c>
+          <t>S01421388</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8625,7 +8621,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8649,13 +8645,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.459547</v>
+        <v>-58.437739</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.626309</v>
+        <v>-34.638224</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8669,7 +8665,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8681,22 +8677,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USPALLATA 3625</t>
+          <t>LEGUIZAMON, MARTINIANO 3983</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8711,7 +8707,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>811454350</t>
+          <t>812440040</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8731,17 +8727,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.414313</v>
+        <v>-58.479051</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.641194</v>
+        <v>-34.675657</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8755,7 +8751,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>PPT-G</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8767,17 +8763,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>LEGUIZAMON, MARTINIANO 3951</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8797,7 +8793,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>812440035</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8824,10 +8820,10 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>-58.465166</v>
+        <v>-58.479542</v>
       </c>
       <c r="N98" t="n">
-        <v>-34.670435</v>
+        <v>-34.675295</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8841,7 +8837,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -8853,22 +8849,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8145 </t>
+          <t>-759</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GUAMINI 5049</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8883,12 +8879,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>811498019</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8910,10 +8906,10 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>-58.475365</v>
+        <v>-58.469878</v>
       </c>
       <c r="N99" t="n">
-        <v>-34.688865</v>
+        <v>-34.626919</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8927,7 +8923,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>PAV-S</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -8939,22 +8935,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRAFUL 3812 </t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8969,12 +8965,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>811498075</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8996,14 +8992,14 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>-58.414437</v>
+        <v>-58.46026</v>
       </c>
       <c r="N100" t="n">
-        <v>-34.651882</v>
+        <v>-34.640706</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9013,7 +9009,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9025,17 +9021,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9055,12 +9051,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9082,14 +9078,14 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>-58.438399</v>
+        <v>-58.480708</v>
       </c>
       <c r="N101" t="n">
-        <v>-34.663958</v>
+        <v>-34.667639</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9099,7 +9095,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9111,22 +9107,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9141,12 +9137,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9168,46 +9164,46 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>-58.475565</v>
+        <v>-58.488539</v>
       </c>
       <c r="N102" t="n">
-        <v>-34.660488</v>
+        <v>-34.640962</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9227,12 +9223,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9254,1227 +9250,27 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>-58.460855</v>
+        <v>-58.474151</v>
       </c>
       <c r="N103" t="n">
-        <v>-34.631046</v>
+        <v>-34.630046</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>S01281615</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>811626968</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>1</v>
-      </c>
-      <c r="M104" t="n">
-        <v>-58.479751</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-34.677211</v>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>S01447367</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>MOZART 216</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>811626897</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L105" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" t="n">
-        <v>-58.491573</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-34.639215</v>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>S01447520</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>811626894</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>1</v>
-      </c>
-      <c r="M106" t="n">
-        <v>-58.487715</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-34.636671</v>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8245 </t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>811626837</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" t="n">
-        <v>-58.488539</v>
-      </c>
-      <c r="N107" t="n">
-        <v>-34.640962</v>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>8270</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2/3/2026</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>811627028</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
-        <v>1</v>
-      </c>
-      <c r="M108" t="n">
-        <v>-58.481162</v>
-      </c>
-      <c r="N108" t="n">
-        <v>-34.665875</v>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>-747</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2/4/2026</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ugarteche 2816</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>811627090</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>corroida inclinada</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L109" t="n">
-        <v>1</v>
-      </c>
-      <c r="M109" t="n">
-        <v>-58.413945</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-34.582774</v>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>AGU-M</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>S01421388</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>MITRE, EMILIO 1602</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="n">
-        <v>-58.437739</v>
-      </c>
-      <c r="N110" t="n">
-        <v>-34.638224</v>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>PPT-S</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>8302</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2/10/2026</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>LEGUIZAMON, MARTINIANO 3983</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
-        <v>1</v>
-      </c>
-      <c r="M111" t="n">
-        <v>-58.479051</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-34.675657</v>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>8303</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2/10/2026</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>LEGUIZAMON, MARTINIANO 3951</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L112" t="n">
-        <v>1</v>
-      </c>
-      <c r="M112" t="n">
-        <v>-58.479542</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-34.675295</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>-759</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>TERRADA 402</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
-        <v>1</v>
-      </c>
-      <c r="M113" t="n">
-        <v>-58.469878</v>
-      </c>
-      <c r="N113" t="n">
-        <v>-34.626919</v>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>NRA-L</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>S00086082</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2/5/2026</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>inclinada corroida</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L114" t="n">
-        <v>1</v>
-      </c>
-      <c r="M114" t="n">
-        <v>-58.46026</v>
-      </c>
-      <c r="N114" t="n">
-        <v>-34.640706</v>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>PPT-N</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>8268</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>MONTREAL 5391</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L115" t="n">
-        <v>1</v>
-      </c>
-      <c r="M115" t="n">
-        <v>-58.480708</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-34.667639</v>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>8244</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>1</v>
-      </c>
-      <c r="M116" t="n">
-        <v>-58.488539</v>
-      </c>
-      <c r="N116" t="n">
-        <v>-34.640962</v>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>S00936659</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>-58.474151</v>
-      </c>
-      <c r="N117" t="n">
-        <v>-34.630046</v>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>NRA-R</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.2NRA</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1PPT</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
@@ -3005,27 +3005,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8/6/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAN ANTONIO 1221</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3035,22 +3035,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>808733914</t>
+          <t>808918687</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Aplomar</t>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3059,17 +3059,17 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.375684</v>
+        <v>-58.425858</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.656092</v>
+        <v>-34.61629</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,17 +3091,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8/7/2025</t>
+          <t>9/2/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RIVADAVIA MARTIN, COMODORO 1350</t>
+          <t>Pedro Rivera 2546</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3121,37 +3121,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>808749184</t>
+          <t>ICD30612785</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Poste inclinado ingreso tambien como 7201</t>
+          <t>Colocar R200 para pedir traspaso de equipos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.461024</v>
+        <v>-58.462479</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.539409</v>
+        <v>-34.55765</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>BLO-F</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,27 +3177,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3231,27 +3231,27 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.425858</v>
+        <v>-58.458298</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.61629</v>
+        <v>-34.566511</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9/2/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pedro Rivera 2546</t>
+          <t>LARRALDE, CRISOLOGO AV. 3875</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ICD30612785</t>
+          <t>809784524</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipos</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3308,22 +3308,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.462479</v>
+        <v>-58.481316</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.55765</v>
+        <v>-34.556157</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3399,31 +3399,31 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.458298</v>
+        <v>-58.409278</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.566511</v>
+        <v>-34.653566</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LARRALDE, CRISOLOGO AV. 3875</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>809784524</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3485,31 +3485,31 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.481316</v>
+        <v>-58.399262</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.556157</v>
+        <v>-34.639685</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,22 +3521,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.409278</v>
+        <v>-58.384406</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.653566</v>
+        <v>-34.622932</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>BONIFACIO, JOSE 2409</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>810132768</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Picada volvio a ingresar mail con caso 7597</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.399262</v>
+        <v>-58.461482</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.639685</v>
+        <v>-34.632432</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,27 +3693,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9/23/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 911</t>
+          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ICD30958043</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Desmonte de columna ya traspasaron un nodo</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3750,24 +3750,24 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.447743</v>
+        <v>-58.465176</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.570457</v>
+        <v>-34.680979</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>COG-C</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9/25/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MANZANARES 4186</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>809979726</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3836,24 +3836,24 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.485454</v>
+        <v>-58.46138</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.555745</v>
+        <v>-34.629774</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.384406</v>
+        <v>-58.458516</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.622932</v>
+        <v>-34.646422</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2409</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810132768</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada volvio a ingresar mail con caso 7597</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.461482</v>
+        <v>-58.374086</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.632432</v>
+        <v>-34.633168</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,39 +4025,39 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4094,14 +4094,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.465176</v>
+        <v>-58.416237</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.680979</v>
+        <v>-34.65477</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,14 +4180,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.46138</v>
+        <v>-58.411426</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.629774</v>
+        <v>-34.633266</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4259,21 +4259,21 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.458516</v>
+        <v>-58.435731</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.646422</v>
+        <v>-34.597659</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/24/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>Munich 1715</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810447258</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4352,24 +4352,24 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.374086</v>
+        <v>-58.453119</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.633168</v>
+        <v>-34.55489</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>BLO-C</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,27 +4381,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4435,17 +4435,17 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.416237</v>
+        <v>-58.4018</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.65477</v>
+        <v>-34.590471</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,17 +4467,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4524,14 +4524,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.411426</v>
+        <v>-58.418542</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.633266</v>
+        <v>-34.624609</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4603,21 +4603,21 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.435731</v>
+        <v>-58.430613</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.597659</v>
+        <v>-34.608805</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/24/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Munich 1715</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810447258</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.453119</v>
+        <v>-58.50161</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.55489</v>
+        <v>-34.647648</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>BLO-C</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,27 +4725,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4779,17 +4779,17 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.4018</v>
+        <v>-58.439164</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.590471</v>
+        <v>-34.597069</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,22 +4811,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,14 +4868,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.418542</v>
+        <v>-58.417634</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.624609</v>
+        <v>-34.587439</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,27 +4897,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>S01150217</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>Vera 311</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>01230602</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Traspasar Fuente</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,26 +4942,26 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.430613</v>
+        <v>-58.436262</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.608805</v>
+        <v>-34.600478</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,14 +5040,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.50161</v>
+        <v>-58.48121</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.647648</v>
+        <v>-34.61126</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,22 +5069,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5126,10 +5126,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.439164</v>
+        <v>-58.440031</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.597069</v>
+        <v>-34.575409</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,22 +5155,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5212,14 +5212,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.417634</v>
+        <v>-58.413563</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.587439</v>
+        <v>-34.624645</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,27 +5241,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S01150217</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vera 311</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01230602</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Traspasar Fuente</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5286,26 +5286,26 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.436262</v>
+        <v>-58.364132</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.600478</v>
+        <v>-34.628423</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,22 +5327,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t xml:space="preserve">7829 </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5384,24 +5384,24 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.48121</v>
+        <v>-58.460356</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.61126</v>
+        <v>-34.630793</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,22 +5413,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5470,14 +5470,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.440031</v>
+        <v>-58.389676</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.575409</v>
+        <v>-34.618127</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,27 +5499,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>-670</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>Timoteo Gordillo 1666</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810651269</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5556,24 +5556,24 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.413563</v>
+        <v>-58.510994</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.624645</v>
+        <v>-34.655027</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5642,14 +5642,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.364132</v>
+        <v>-58.418108</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.628423</v>
+        <v>-34.62564</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,22 +5671,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7829 </t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>CAMPICHUELO 215</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810712875</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5728,14 +5728,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.460356</v>
+        <v>-58.433771</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.630793</v>
+        <v>-34.614668</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,22 +5757,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5814,14 +5814,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.389676</v>
+        <v>-58.433855</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.618127</v>
+        <v>-34.614487</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,27 +5843,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>-670</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Timoteo Gordillo 1666</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810651269</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5900,14 +5900,14 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.510994</v>
+        <v>-58.441198</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.655027</v>
+        <v>-34.605341</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5929,22 +5929,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5986,14 +5986,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.418108</v>
+        <v>-58.439239</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.62564</v>
+        <v>-34.6604</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6015,22 +6015,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 215</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810712875</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6072,14 +6072,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.433771</v>
+        <v>-58.388529</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.614668</v>
+        <v>-34.655949</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6158,24 +6158,24 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.433855</v>
+        <v>-58.491325</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.614487</v>
+        <v>-34.647761</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6187,22 +6187,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t xml:space="preserve">7869 </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6244,24 +6244,24 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.441198</v>
+        <v>-58.469394</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.605341</v>
+        <v>-34.626925</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6273,22 +6273,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6330,14 +6330,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.439239</v>
+        <v>-58.390974</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.6604</v>
+        <v>-34.594177</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6359,22 +6359,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t xml:space="preserve">7898 </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6416,14 +6416,14 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.388529</v>
+        <v>-58.459955</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.655949</v>
+        <v>-34.631973</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6445,22 +6445,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6502,10 +6502,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.491325</v>
+        <v>-58.48802</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.647761</v>
+        <v>-34.641075</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6519,34 +6519,34 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869 </t>
+          <t>7927</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>Pico 3481</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>811198751</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6581,31 +6581,31 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.469394</v>
+        <v>-58.484883</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.626925</v>
+        <v>-34.54464</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6617,22 +6617,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6674,14 +6674,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.390974</v>
+        <v>-58.463198</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.594177</v>
+        <v>-34.62624</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6703,22 +6703,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898 </t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6760,51 +6760,47 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.459955</v>
+        <v>-58.471183</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.631973</v>
+        <v>-34.638988</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PCH-F</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t xml:space="preserve">7997 </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6819,12 +6815,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6846,51 +6842,51 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.48802</v>
+        <v>-58.46357</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.641075</v>
+        <v>-34.623187</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pico 3481</t>
+          <t>CASTRO, EMILIO AV. 7650</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6905,12 +6901,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811198751</t>
+          <t>811299445</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6925,21 +6921,21 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.484883</v>
+        <v>-58.524273</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.54464</v>
+        <v>-34.65615</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6949,7 +6945,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>PAV-I</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6961,22 +6957,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t xml:space="preserve">8061 </t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t xml:space="preserve">FOREST AV. 957 </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6991,12 +6987,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7011,31 +7007,31 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.463198</v>
+        <v>-58.45732</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.62624</v>
+        <v>-34.581366</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7047,22 +7043,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7077,7 +7073,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7104,51 +7100,51 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.471183</v>
+        <v>-58.459547</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.638988</v>
+        <v>-34.626309</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PCH-O</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7997 </t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>USPALLATA 3625</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7163,12 +7159,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811454350</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7190,10 +7186,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.46357</v>
+        <v>-58.414313</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.623187</v>
+        <v>-34.641194</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7207,7 +7203,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PPT-G</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7219,22 +7215,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CASTRO, EMILIO AV. 7650</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7249,7 +7245,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811299445</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7269,31 +7265,31 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.524273</v>
+        <v>-58.465166</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.65615</v>
+        <v>-34.670435</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PAV-I</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7305,22 +7301,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8061 </t>
+          <t>8145</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOREST AV. 957 </t>
+          <t>GUAMINI 5049</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7335,12 +7331,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811498019</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7355,31 +7351,31 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.45732</v>
+        <v>-58.475365</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.581366</v>
+        <v>-34.688865</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PAV-S</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7391,22 +7387,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t xml:space="preserve">TRAFUL 3812 </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7421,7 +7417,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811498075</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7448,14 +7444,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.459547</v>
+        <v>-58.414437</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.626309</v>
+        <v>-34.651882</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7465,7 +7461,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7477,22 +7473,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USPALLATA 3625</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7507,12 +7503,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811454350</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7534,14 +7530,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.414313</v>
+        <v>-58.438399</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.641194</v>
+        <v>-34.663958</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7551,7 +7547,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PPT-G</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7563,17 +7559,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7593,12 +7589,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7620,10 +7616,10 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.465166</v>
+        <v>-58.475565</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.670435</v>
+        <v>-34.660488</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7637,7 +7633,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7649,22 +7645,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8145 </t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GUAMINI 5049</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7679,12 +7675,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811498019</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">corroida </t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7706,10 +7702,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.475365</v>
+        <v>-58.460855</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.688865</v>
+        <v>-34.631046</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7723,7 +7719,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PAV-S</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7735,22 +7731,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1/23/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRAFUL 3812 </t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7765,12 +7761,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811498075</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7792,14 +7788,14 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.414437</v>
+        <v>-58.479751</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.651882</v>
+        <v>-34.677211</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7809,7 +7805,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7821,22 +7817,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7851,12 +7847,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7878,51 +7874,51 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.438399</v>
+        <v>-58.491573</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.663958</v>
+        <v>-34.639215</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7937,7 +7933,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7964,51 +7960,51 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.475565</v>
+        <v>-58.487715</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.660488</v>
+        <v>-34.636671</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t xml:space="preserve">8245 </t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8023,12 +8019,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8050,46 +8046,46 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.460855</v>
+        <v>-58.488539</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.631046</v>
+        <v>-34.640962</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8109,12 +8105,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8136,10 +8132,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.479751</v>
+        <v>-58.481162</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.677211</v>
+        <v>-34.665875</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8165,22 +8161,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>-747</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8195,12 +8191,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8222,51 +8218,47 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.491573</v>
+        <v>-58.413945</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.639215</v>
+        <v>-34.582774</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S01447520</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
+          <t>S01421388</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8281,7 +8273,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8308,51 +8300,51 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.487715</v>
+        <v>-58.437739</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.636671</v>
+        <v>-34.638224</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245 </t>
+          <t>-759</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8367,12 +8359,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8394,51 +8386,51 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.488539</v>
+        <v>-58.469878</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.640962</v>
+        <v>-34.626919</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8453,12 +8445,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8480,10 +8472,10 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.481162</v>
+        <v>-58.46026</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.665875</v>
+        <v>-34.640706</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8497,7 +8489,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8509,22 +8501,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>-747</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8539,12 +8531,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8566,14 +8558,14 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.413945</v>
+        <v>-58.480708</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.582774</v>
+        <v>-34.667639</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -8583,7 +8575,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -8595,18 +8587,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S01421388</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>8244</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8621,12 +8617,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8645,54 +8641,54 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>-58.437739</v>
+        <v>-58.488539</v>
       </c>
       <c r="N96" t="n">
-        <v>-34.638224</v>
+        <v>-34.640962</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LEGUIZAMON, MARTINIANO 3983</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8707,7 +8703,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>812440040</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8727,550 +8723,34 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>-58.479051</v>
+        <v>-58.474151</v>
       </c>
       <c r="N97" t="n">
-        <v>-34.675657</v>
+        <v>-34.630046</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>8303</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2/10/2026</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>LEGUIZAMON, MARTINIANO 3951</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>812440035</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L98" t="n">
-        <v>1</v>
-      </c>
-      <c r="M98" t="n">
-        <v>-58.479542</v>
-      </c>
-      <c r="N98" t="n">
-        <v>-34.675295</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>-759</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>TERRADA 402</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>812440368</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L99" t="n">
-        <v>1</v>
-      </c>
-      <c r="M99" t="n">
-        <v>-58.469878</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-34.626919</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>NRA-L</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>S00086082</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2/5/2026</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>812439923</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>inclinada corroida</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
-        <v>1</v>
-      </c>
-      <c r="M100" t="n">
-        <v>-58.46026</v>
-      </c>
-      <c r="N100" t="n">
-        <v>-34.640706</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>PPT-N</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>8268</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>MONTREAL 5391</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>812440314</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L101" t="n">
-        <v>1</v>
-      </c>
-      <c r="M101" t="n">
-        <v>-58.480708</v>
-      </c>
-      <c r="N101" t="n">
-        <v>-34.667639</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>8244</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>812440296</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L102" t="n">
-        <v>1</v>
-      </c>
-      <c r="M102" t="n">
-        <v>-58.488539</v>
-      </c>
-      <c r="N102" t="n">
-        <v>-34.640962</v>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>S00936659</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>812440276</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L103" t="n">
-        <v>1</v>
-      </c>
-      <c r="M103" t="n">
-        <v>-58.474151</v>
-      </c>
-      <c r="N103" t="n">
-        <v>-34.630046</v>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>NRA-R</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.2NRA</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,22 +863,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>12/19/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MEXICO 4249</t>
+          <t>LORA, FELIX 27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>799981143</t>
+          <t>801768138</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ver foto, colocar columna para traspasar</t>
+          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -920,14 +920,14 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-58.425997</v>
+        <v>-58.443626</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.620454</v>
+        <v>-34.621032</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -949,27 +949,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12/19/2024</t>
+          <t>2/20/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LORA, FELIX 27</t>
+          <t>ZABALA 2844</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>801768138</t>
+          <t>780340125</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
+          <t>cambiar columna y emprolijar cables y cajas de empalme que se ven en las fotos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1006,24 +1006,24 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.443626</v>
+        <v>-58.452328</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.621032</v>
+        <v>-34.572196</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>ATH-Q</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1035,22 +1035,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>-111</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2/20/2024</t>
+          <t>7/12/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZABALA 2844</t>
+          <t>CATAMARCA /ALT/ 1127</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>780340125</t>
+          <t>790298182</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>cambiar columna y emprolijar cables y cajas de empalme que se ven en las fotos</t>
+          <t>Cambio de columna.-</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1089,27 +1089,27 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.452328</v>
+        <v>-58.404265</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.572196</v>
+        <v>-34.623154</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ATH-Q</t>
+          <t>CEN-K</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1121,27 +1121,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-111</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7/12/2024</t>
+          <t>11/7/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CATAMARCA /ALT/ 1127</t>
+          <t>OLLEROS 2952</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>790298182</t>
+          <t>799450967</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cambio de columna.-</t>
+          <t>Terminar transferencia, retirar columna vieja</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1178,14 +1178,14 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.404265</v>
+        <v>-58.447022</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.623154</v>
+        <v>-34.575873</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1207,22 +1207,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11/7/2024</t>
+          <t>12/21/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OLLEROS 2952</t>
+          <t>MERCEDES 254</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>799450967</t>
+          <t>801901755</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Solo retirar columna ya se realizo traspaso</t>
+          <t>Colocar R200 para pedir traspaso de equipo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1261,49 +1261,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.447022</v>
+        <v>-58.484232</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.575873</v>
+        <v>-34.631431</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>DEV-L</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2DEV</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12/21/2024</t>
+          <t>1/14/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MERCEDES 254</t>
+          <t>Campana	534</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>801901755</t>
+          <t>802657454</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1350,10 +1350,10 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.484232</v>
+        <v>-58.477376</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.631431</v>
+        <v>-34.626126</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1367,39 +1367,39 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>DEV-L</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2DEV</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1/14/2025</t>
+          <t>1/22/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Campana	534</t>
+          <t>CUENCA 3345</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>802657454</t>
+          <t>802843289</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1436,14 +1436,14 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.477376</v>
+        <v>-58.496935</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.626126</v>
+        <v>-34.599084</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1453,39 +1453,39 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1/22/2025</t>
+          <t>1/24/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CUENCA 3345</t>
+          <t>BRASIL 2561</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>802843289</t>
+          <t>802871857</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna R400 - Fuente Teco</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1522,24 +1522,24 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.496935</v>
+        <v>-58.400156</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.599084</v>
+        <v>-34.631369</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1551,17 +1551,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1/24/2025</t>
+          <t>1/30/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BRASIL 2561</t>
+          <t>RONDEAU 2775</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>802871857</t>
+          <t>802988219</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Colocar columna R400 - Fuente Teco</t>
+          <t>Relevar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1608,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.400156</v>
+        <v>-58.402062</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.631369</v>
+        <v>-34.635143</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1637,27 +1637,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1/30/2025</t>
+          <t>2/10/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RONDEAU 2775</t>
+          <t>YERBAL 489</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>802988219</t>
+          <t>803607520</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Relevar</t>
+          <t>Desmonte de columna ya traspasaron nodo</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1694,14 +1694,14 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.402062</v>
+        <v>-58.438053</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.635143</v>
+        <v>-34.617481</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>ALM-G</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2/10/2025</t>
+          <t>2/14/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>YERBAL 489</t>
+          <t>CHACO 195</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>803607520</t>
+          <t>803607699</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Desmonte de columna ya traspasaron nodo</t>
+          <t>Desmontar columna personal propio traspaso nodo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1780,10 +1780,10 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.438053</v>
+        <v>-58.431522</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.617481</v>
+        <v>-34.617523</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ALM-G</t>
+          <t>ALM-F</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1809,22 +1809,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2/14/2025</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHACO 195</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>803607699</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Desmontar columna personal propio traspaso nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1866,10 +1866,10 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.431522</v>
+        <v>-58.423042</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.617523</v>
+        <v>-34.625868</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ALM-F</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1895,27 +1895,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>3/27/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>THAMES 649</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>804309655</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1952,14 +1952,14 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.423042</v>
+        <v>-58.441405</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.625868</v>
+        <v>-34.594348</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>THAMES 649</t>
+          <t>ZELARRAYAN 6147</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2011,14 +2011,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>804309655</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
-        </is>
-      </c>
+          <t>804309801</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2038,14 +2034,14 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.441405</v>
+        <v>-58.483821</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.594348</v>
+        <v>-34.677698</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2055,7 +2051,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2067,27 +2063,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ZELARRAYAN 6147</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2097,10 +2093,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>804309801</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>804569065</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2120,14 +2120,14 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.483821</v>
+        <v>-58.425764</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.677698</v>
+        <v>-34.604359</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2149,22 +2149,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/22/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MONTES DE OCA, MANUEL AV. 511</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804876051</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>Pegar los ductos al prfv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2206,14 +2206,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.425764</v>
+        <v>-58.375515</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.604359</v>
+        <v>-34.634393</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2223,29 +2223,29 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4/22/2025</t>
+          <t>5/4/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 511</t>
+          <t>AZARA 15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>804876051</t>
+          <t>805655333</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pegar los ductos al prfv</t>
+          <t>Picada entro tambien como reclamo 7611</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2292,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.375515</v>
+        <v>-58.372751</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.634393</v>
+        <v>-34.631917</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2321,22 +2321,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2378,14 +2378,14 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.372751</v>
+        <v>-58.395063</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.631917</v>
+        <v>-34.606257</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.395063</v>
+        <v>-58.483927</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.606257</v>
+        <v>-34.570689</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2493,22 +2493,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2523,17 +2523,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2550,24 +2550,24 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.483927</v>
+        <v>-58.477944</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.570689</v>
+        <v>-34.675149</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2579,27 +2579,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2624,26 +2624,26 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.477944</v>
+        <v>-58.416477</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.675149</v>
+        <v>-34.61303</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2665,7 +2665,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2722,10 +2722,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.416477</v>
+        <v>-58.425478</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.61303</v>
+        <v>-34.601865</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2751,22 +2751,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2808,10 +2808,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.425478</v>
+        <v>-58.401624</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.601865</v>
+        <v>-34.612001</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2837,17 +2837,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2867,14 +2867,10 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810533286</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Desmontar PRFV 400</t>
-        </is>
-      </c>
+          <t>807851584</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2882,7 +2878,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2894,10 +2890,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.401624</v>
+        <v>-58.401827</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.612001</v>
+        <v>-34.617667</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2911,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2923,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2953,10 +2949,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>807851584</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>808918687</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.401827</v>
+        <v>-58.425858</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.617667</v>
+        <v>-34.61629</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,27 +3005,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>9/2/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>Pedro Rivera 2546</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>ICD30612785</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Colocar R200 para pedir traspaso de equipos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3059,27 +3059,27 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.425858</v>
+        <v>-58.462479</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.61629</v>
+        <v>-34.55765</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,17 +3091,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9/2/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pedro Rivera 2546</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ICD30612785</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipos</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3148,14 +3148,14 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.462479</v>
+        <v>-58.458298</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.55765</v>
+        <v>-34.566511</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>LARRALDE, CRISOLOGO AV. 3875</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809784524</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3227,21 +3227,21 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.458298</v>
+        <v>-58.481316</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.566511</v>
+        <v>-34.556157</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LARRALDE, CRISOLOGO AV. 3875</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,17 +3293,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>809784524</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3320,24 +3320,24 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.481316</v>
+        <v>-58.409278</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.556157</v>
+        <v>-34.653566</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3399,17 +3399,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.409278</v>
+        <v>-58.399262</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.653566</v>
+        <v>-34.639685</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3492,10 +3492,10 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.399262</v>
+        <v>-58.384406</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.639685</v>
+        <v>-34.622932</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>BONIFACIO, JOSE 2409</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810132768</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada volvio a ingresar mail con caso 7597</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3578,14 +3578,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.384406</v>
+        <v>-58.461482</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.622932</v>
+        <v>-34.632432</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,27 +3607,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2409</t>
+          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810132768</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada volvio a ingresar mail con caso 7597</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,10 +3664,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.461482</v>
+        <v>-58.465176</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.632432</v>
+        <v>-34.680979</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,27 +3693,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3750,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.465176</v>
+        <v>-58.46138</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.680979</v>
+        <v>-34.629774</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,17 +3779,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.46138</v>
+        <v>-58.458516</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.629774</v>
+        <v>-34.646422</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,7 +3865,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.458516</v>
+        <v>-58.374086</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.646422</v>
+        <v>-34.633168</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,29 +3939,29 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4008,10 +4008,10 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.374086</v>
+        <v>-58.416237</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.633168</v>
+        <v>-34.65477</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4025,34 +4025,34 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,10 +4094,10 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.416237</v>
+        <v>-58.411426</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.65477</v>
+        <v>-34.633266</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4173,21 +4173,21 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.411426</v>
+        <v>-58.435731</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.633266</v>
+        <v>-34.597659</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,27 +4209,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,26 +4254,26 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.435731</v>
+        <v>-58.4018</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.597659</v>
+        <v>-34.590471</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/24/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Munich 1715</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810447258</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4352,24 +4352,24 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.453119</v>
+        <v>-58.418542</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.55489</v>
+        <v>-34.624609</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>BLO-C</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4435,17 +4435,17 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.4018</v>
+        <v>-58.430613</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.590471</v>
+        <v>-34.608805</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,7 +4467,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4524,24 +4524,24 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.418542</v>
+        <v>-58.50161</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.624609</v>
+        <v>-34.647648</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4610,14 +4610,14 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.430613</v>
+        <v>-58.439164</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.608805</v>
+        <v>-34.597069</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4696,24 +4696,24 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.50161</v>
+        <v>-58.417634</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.647648</v>
+        <v>-34.587439</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,17 +4725,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>S01150217</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>Vera 311</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01230602</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspasar Fuente</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,22 +4770,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.439164</v>
+        <v>-58.436262</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.597069</v>
+        <v>-34.600478</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,22 +4811,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,24 +4868,24 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.417634</v>
+        <v>-58.48121</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.587439</v>
+        <v>-34.61126</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,27 +4897,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S01150217</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vera 311</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01230602</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Traspasar Fuente</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,22 +4942,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.436262</v>
+        <v>-58.440031</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.600478</v>
+        <v>-34.575409</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,7 +4983,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5040,24 +5040,24 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.48121</v>
+        <v>-58.413563</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.61126</v>
+        <v>-34.624645</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,22 +5069,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5126,14 +5126,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.440031</v>
+        <v>-58.364132</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.575409</v>
+        <v>-34.628423</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,22 +5155,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t xml:space="preserve">7829 </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5212,10 +5212,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.413563</v>
+        <v>-58.460356</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.624645</v>
+        <v>-34.630793</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,22 +5241,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5298,10 +5298,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.364132</v>
+        <v>-58.389676</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.628423</v>
+        <v>-34.618127</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,27 +5327,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7829 </t>
+          <t>-670</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>Timoteo Gordillo 1666</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810651269</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5384,24 +5384,24 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.460356</v>
+        <v>-58.510994</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.630793</v>
+        <v>-34.655027</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,22 +5413,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5470,14 +5470,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.389676</v>
+        <v>-58.418108</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.618127</v>
+        <v>-34.62564</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,27 +5499,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-670</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Timoteo Gordillo 1666</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810651269</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5556,24 +5556,24 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.510994</v>
+        <v>-58.433855</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.655027</v>
+        <v>-34.614487</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5642,24 +5642,24 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.418108</v>
+        <v>-58.441198</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.62564</v>
+        <v>-34.605341</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,22 +5671,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 215</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810712875</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5728,14 +5728,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.433771</v>
+        <v>-58.439239</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.614668</v>
+        <v>-34.6604</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,22 +5757,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5814,14 +5814,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.433855</v>
+        <v>-58.388529</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.614487</v>
+        <v>-34.655949</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,22 +5843,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5900,14 +5900,14 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.441198</v>
+        <v>-58.491325</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.605341</v>
+        <v>-34.647761</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5929,22 +5929,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t xml:space="preserve">7869 </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5986,14 +5986,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.439239</v>
+        <v>-58.469394</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.6604</v>
+        <v>-34.626925</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6015,22 +6015,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6072,14 +6072,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.388529</v>
+        <v>-58.390974</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.655949</v>
+        <v>-34.594177</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t xml:space="preserve">7898 </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6158,24 +6158,24 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.491325</v>
+        <v>-58.459955</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.647761</v>
+        <v>-34.631973</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6187,22 +6187,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869 </t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6244,51 +6244,51 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.469394</v>
+        <v>-58.48802</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.626925</v>
+        <v>-34.641075</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>Pico 3481</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>811198751</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,36 +6318,36 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.390974</v>
+        <v>-58.484883</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.594177</v>
+        <v>-34.54464</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6359,17 +6359,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898 </t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6416,10 +6416,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.459955</v>
+        <v>-58.463198</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.631973</v>
+        <v>-34.62624</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6445,22 +6445,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6502,10 +6502,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.48802</v>
+        <v>-58.471183</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.641075</v>
+        <v>-34.638988</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6519,34 +6519,30 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t xml:space="preserve">7997 </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pico 3481</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6561,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811198751</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6581,31 +6577,31 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.484883</v>
+        <v>-58.46357</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.54464</v>
+        <v>-34.623187</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6617,22 +6613,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>CASTRO, EMILIO AV. 7650</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6647,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811299445</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6667,31 +6663,31 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.463198</v>
+        <v>-58.524273</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.62624</v>
+        <v>-34.65615</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PAV-I</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6703,22 +6699,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6733,12 +6729,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6753,21 +6749,21 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.471183</v>
+        <v>-58.45732</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.638988</v>
+        <v>-34.581366</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6777,25 +6773,29 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+          <t>ATH-N</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7997 </t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6842,10 +6842,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.46357</v>
+        <v>-58.459547</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.623187</v>
+        <v>-34.626309</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6871,22 +6871,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CASTRO, EMILIO AV. 7650</t>
+          <t>USPALLATA 3625</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811299445</t>
+          <t>811454350</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6921,31 +6921,31 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.524273</v>
+        <v>-58.414313</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.65615</v>
+        <v>-34.641194</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PAV-I</t>
+          <t>PPT-G</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6957,22 +6957,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8061 </t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOREST AV. 957 </t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7007,31 +7007,31 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.45732</v>
+        <v>-58.465166</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.581366</v>
+        <v>-34.670435</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7043,22 +7043,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>GUAMINI 5049</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811498019</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7100,10 +7100,10 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.459547</v>
+        <v>-58.475365</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.626309</v>
+        <v>-34.688865</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PAV-S</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7129,17 +7129,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USPALLATA 3625</t>
+          <t xml:space="preserve">TRAFUL 3812 </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811454350</t>
+          <t>811498075</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7186,14 +7186,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.414313</v>
+        <v>-58.414437</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.641194</v>
+        <v>-34.651882</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PPT-G</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7215,17 +7215,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7272,14 +7272,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.465166</v>
+        <v>-58.438399</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.670435</v>
+        <v>-34.663958</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7301,17 +7301,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GUAMINI 5049</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811498019</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7358,10 +7358,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.475365</v>
+        <v>-58.475565</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.688865</v>
+        <v>-34.660488</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PAV-S</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7387,22 +7387,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/23/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRAFUL 3812 </t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811498075</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7444,14 +7444,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.414437</v>
+        <v>-58.460855</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.651882</v>
+        <v>-34.631046</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7530,14 +7530,14 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.438399</v>
+        <v>-58.479751</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.663958</v>
+        <v>-34.677211</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7559,22 +7559,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7616,51 +7616,51 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.475565</v>
+        <v>-58.491573</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.660488</v>
+        <v>-34.639215</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7702,36 +7702,36 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.460855</v>
+        <v>-58.487715</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.631046</v>
+        <v>-34.636671</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t xml:space="preserve">8245 </t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7788,51 +7788,51 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.479751</v>
+        <v>-58.488539</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.677211</v>
+        <v>-34.640962</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7874,51 +7874,51 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.491573</v>
+        <v>-58.481162</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.639215</v>
+        <v>-34.665875</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>-747</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7960,51 +7960,47 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.487715</v>
+        <v>-58.413945</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.636671</v>
+        <v>-34.582774</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245 </t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
+          <t>S01421388</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8019,12 +8015,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8046,51 +8042,51 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.488539</v>
+        <v>-58.437739</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.640962</v>
+        <v>-34.638224</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>-759</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8105,12 +8101,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8132,10 +8128,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.481162</v>
+        <v>-58.469878</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.665875</v>
+        <v>-34.626919</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8149,7 +8145,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8161,22 +8157,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>-747</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8191,12 +8187,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8218,14 +8214,14 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.413945</v>
+        <v>-58.46026</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.582774</v>
+        <v>-34.640706</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8235,7 +8231,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8247,18 +8243,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S01421388</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>8268</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8300,10 +8300,10 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.437739</v>
+        <v>-58.480708</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.638224</v>
+        <v>-34.667639</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8329,7 +8329,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>-759</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8359,12 +8359,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8386,46 +8386,46 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.469878</v>
+        <v>-58.488539</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.626919</v>
+        <v>-34.640962</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8472,36 +8472,36 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.46026</v>
+        <v>-58.474151</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.640706</v>
+        <v>-34.630046</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -8546,22 +8546,22 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>-58.480708</v>
+        <v>-58.464382</v>
       </c>
       <c r="N95" t="n">
-        <v>-34.667639</v>
+        <v>-34.683083</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8575,184 +8575,12 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>8244</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>812440296</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" t="n">
-        <v>-58.488539</v>
-      </c>
-      <c r="N96" t="n">
-        <v>-34.640962</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>S00936659</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>812440276</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
-        <v>1</v>
-      </c>
-      <c r="M97" t="n">
-        <v>-58.474151</v>
-      </c>
-      <c r="N97" t="n">
-        <v>-34.630046</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>NRA-R</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,27 +1035,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-111</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7/12/2024</t>
+          <t>11/7/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CATAMARCA /ALT/ 1127</t>
+          <t>OLLEROS 2952</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>790298182</t>
+          <t>799450967</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cambio de columna.-</t>
+          <t>Terminar transferencia, retirar columna vieja</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1092,14 +1092,14 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.404265</v>
+        <v>-58.447022</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.623154</v>
+        <v>-34.575873</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CEN-K</t>
+          <t>ATH-P</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1121,22 +1121,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11/7/2024</t>
+          <t>12/21/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OLLEROS 2952</t>
+          <t>MERCEDES 254</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>799450967</t>
+          <t>801901755</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Terminar transferencia, retirar columna vieja</t>
+          <t>Colocar R200 para pedir traspaso de equipo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1175,49 +1175,49 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.447022</v>
+        <v>-58.484232</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.575873</v>
+        <v>-34.631431</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>DEV-L</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2DEV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12/21/2024</t>
+          <t>1/14/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MERCEDES 254</t>
+          <t>Campana	534</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>801901755</t>
+          <t>802657454</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.484232</v>
+        <v>-58.477376</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.631431</v>
+        <v>-34.626126</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1281,39 +1281,39 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>DEV-L</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2DEV</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1/14/2025</t>
+          <t>1/22/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Campana	534</t>
+          <t>CUENCA 3345</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>802657454</t>
+          <t>802843289</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1350,14 +1350,14 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.477376</v>
+        <v>-58.496935</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.626126</v>
+        <v>-34.599084</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1367,39 +1367,39 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1/22/2025</t>
+          <t>1/24/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CUENCA 3345</t>
+          <t>BRASIL 2561</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>802843289</t>
+          <t>802871857</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar columna R400 - Fuente Teco</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1436,24 +1436,24 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.496935</v>
+        <v>-58.400156</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.599084</v>
+        <v>-34.631369</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1465,17 +1465,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1/24/2025</t>
+          <t>1/30/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BRASIL 2561</t>
+          <t>RONDEAU 2775</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>802871857</t>
+          <t>802988219</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Colocar columna R400 - Fuente Teco</t>
+          <t>Relevar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1522,10 +1522,10 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.400156</v>
+        <v>-58.402062</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.631369</v>
+        <v>-34.635143</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1551,27 +1551,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1/30/2025</t>
+          <t>2/10/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RONDEAU 2775</t>
+          <t>YERBAL 489</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>802988219</t>
+          <t>803607520</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Relevar</t>
+          <t>Desmonte de columna ya traspasaron nodo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1608,14 +1608,14 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.402062</v>
+        <v>-58.438053</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.635143</v>
+        <v>-34.617481</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>ALM-G</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1637,17 +1637,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2/10/2025</t>
+          <t>2/14/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>YERBAL 489</t>
+          <t>CHACO 195</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>803607520</t>
+          <t>803607699</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Desmonte de columna ya traspasaron nodo</t>
+          <t>Desmontar columna personal propio traspaso nodo</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1694,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.438053</v>
+        <v>-58.431522</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.617481</v>
+        <v>-34.617523</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ALM-G</t>
+          <t>ALM-F</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1723,27 +1723,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2/14/2025</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHACO 195</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>803607699</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Desmontar columna personal propio traspaso nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1780,10 +1780,10 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.431522</v>
+        <v>-58.423042</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.617523</v>
+        <v>-34.625868</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ALM-F</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1809,27 +1809,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>3/27/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>THAMES 649</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>804309655</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1866,14 +1866,14 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.423042</v>
+        <v>-58.441405</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.625868</v>
+        <v>-34.594348</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>THAMES 649</t>
+          <t>ZELARRAYAN 6147</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1925,14 +1925,10 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>804309655</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
-        </is>
-      </c>
+          <t>804309801</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -1952,14 +1948,14 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.441405</v>
+        <v>-58.483821</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.594348</v>
+        <v>-34.677698</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1969,7 +1965,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1981,27 +1977,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ZELARRAYAN 6147</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2011,10 +2007,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>804309801</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>804569065</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2034,14 +2034,14 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.483821</v>
+        <v>-58.425764</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.677698</v>
+        <v>-34.604359</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2063,22 +2063,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>4/22/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>MONTES DE OCA, MANUEL AV. 511</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>804876051</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>Pegar los ductos al prfv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2120,14 +2120,14 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.425764</v>
+        <v>-58.375515</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.604359</v>
+        <v>-34.634393</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2137,29 +2137,29 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4/22/2025</t>
+          <t>5/4/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 511</t>
+          <t>AZARA 15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>804876051</t>
+          <t>805655333</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pegar los ductos al prfv</t>
+          <t>Picada entro tambien como reclamo 7611</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2206,10 +2206,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.375515</v>
+        <v>-58.372751</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.634393</v>
+        <v>-34.631917</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2235,22 +2235,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2292,14 +2292,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.372751</v>
+        <v>-58.395063</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.631917</v>
+        <v>-34.606257</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2309,34 +2309,34 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2351,51 +2351,51 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.395063</v>
+        <v>-58.483927</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.606257</v>
+        <v>-34.570689</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2407,22 +2407,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2464,24 +2464,24 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.483927</v>
+        <v>-58.477944</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.570689</v>
+        <v>-34.675149</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2493,27 +2493,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>MAZA 181</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>807215439</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2538,26 +2538,26 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.477944</v>
+        <v>-58.416477</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.675149</v>
+        <v>-34.61303</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>CLI-I</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2636,10 +2636,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.416477</v>
+        <v>-58.425478</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.61303</v>
+        <v>-34.601865</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2665,22 +2665,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2722,10 +2722,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.425478</v>
+        <v>-58.401624</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.601865</v>
+        <v>-34.612001</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2751,17 +2751,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>6/30/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>CHILE 2561</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2781,14 +2781,10 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810533286</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Desmontar PRFV 400</t>
-        </is>
-      </c>
+          <t>807851584</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2796,7 +2792,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2808,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.401624</v>
+        <v>-58.401827</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.612001</v>
+        <v>-34.617667</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2825,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>CEN-M</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2837,22 +2833,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>8/12/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>MARMOL, JOSE 228</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2867,10 +2863,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>807851584</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>808918687</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.401827</v>
+        <v>-58.425858</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.617667</v>
+        <v>-34.61629</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-D</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,27 +2919,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>-579</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>9/2/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>Pedro Rivera 2546</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>ICD30612785</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Colocar R200 para pedir traspaso de equipos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2973,27 +2973,27 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.425858</v>
+        <v>-58.462479</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.61629</v>
+        <v>-34.55765</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>COG-K</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,17 +3005,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9/2/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pedro Rivera 2546</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ICD30612785</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipos</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3062,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.462479</v>
+        <v>-58.458298</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.55765</v>
+        <v>-34.566511</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,22 +3091,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/16/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>LARRALDE, CRISOLOGO AV. 3875</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809784524</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3141,21 +3141,21 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.458298</v>
+        <v>-58.481316</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.566511</v>
+        <v>-34.556157</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>COG-O</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LARRALDE, CRISOLOGO AV. 3875</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>809784524</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3234,24 +3234,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.481316</v>
+        <v>-58.409278</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.556157</v>
+        <v>-34.653566</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3293,17 +3293,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.409278</v>
+        <v>-58.399262</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.653566</v>
+        <v>-34.639685</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3406,10 +3406,10 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.399262</v>
+        <v>-58.384406</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.639685</v>
+        <v>-34.622932</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>BONIFACIO, JOSE 2409</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810132768</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada volvio a ingresar mail con caso 7597</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3492,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.384406</v>
+        <v>-58.461482</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.622932</v>
+        <v>-34.632432</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,27 +3521,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2409</t>
+          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810132768</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada volvio a ingresar mail con caso 7597</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.461482</v>
+        <v>-58.465176</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.632432</v>
+        <v>-34.680979</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,27 +3607,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,10 +3664,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.465176</v>
+        <v>-58.46138</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.680979</v>
+        <v>-34.629774</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,17 +3693,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3750,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.46138</v>
+        <v>-58.458516</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.629774</v>
+        <v>-34.646422</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3836,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.458516</v>
+        <v>-58.374086</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.646422</v>
+        <v>-34.633168</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,29 +3853,29 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3922,10 +3922,10 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.374086</v>
+        <v>-58.416237</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.633168</v>
+        <v>-34.65477</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3939,34 +3939,34 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,10 +4008,10 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.416237</v>
+        <v>-58.411426</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.65477</v>
+        <v>-34.633266</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4087,21 +4087,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.411426</v>
+        <v>-58.435731</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.633266</v>
+        <v>-34.597659</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,27 +4123,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>01230434</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4168,26 +4168,26 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.435731</v>
+        <v>-58.4018</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.597659</v>
+        <v>-34.590471</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>AGU-F</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4263,17 +4263,17 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.4018</v>
+        <v>-58.418542</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.590471</v>
+        <v>-34.624609</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,7 +4295,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,14 +4352,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.418542</v>
+        <v>-58.430613</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.624609</v>
+        <v>-34.608805</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4438,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.430613</v>
+        <v>-58.50161</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.608805</v>
+        <v>-34.647648</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4524,24 +4524,24 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.50161</v>
+        <v>-58.439164</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.647648</v>
+        <v>-34.597069</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,7 +4553,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4610,10 +4610,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.439164</v>
+        <v>-58.417634</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.597069</v>
+        <v>-34.587439</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,27 +4639,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>S01150217</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>Vera 311</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>01230602</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Traspasar Fuente</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4684,22 +4684,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.417634</v>
+        <v>-58.436262</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.587439</v>
+        <v>-34.600478</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,27 +4725,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S01150217</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vera 311</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01230602</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Traspasar Fuente</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,36 +4770,36 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.436262</v>
+        <v>-58.48121</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.600478</v>
+        <v>-34.61126</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4868,24 +4868,24 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.48121</v>
+        <v>-58.440031</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.61126</v>
+        <v>-34.575409</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4897,7 +4897,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4954,14 +4954,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.440031</v>
+        <v>-58.413563</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.575409</v>
+        <v>-34.624645</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,14 +5040,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.413563</v>
+        <v>-58.364132</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.624645</v>
+        <v>-34.628423</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,22 +5069,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t xml:space="preserve">7829 </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5126,14 +5126,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.364132</v>
+        <v>-58.460356</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.628423</v>
+        <v>-34.630793</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5155,22 +5155,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7829 </t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5212,14 +5212,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.460356</v>
+        <v>-58.389676</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.630793</v>
+        <v>-34.618127</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5241,27 +5241,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>-670</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>Timoteo Gordillo 1666</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810651269</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5298,24 +5298,24 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.389676</v>
+        <v>-58.510994</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.618127</v>
+        <v>-34.655027</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PAV-J</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5327,27 +5327,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-670</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Timoteo Gordillo 1666</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810651269</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5384,24 +5384,24 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.510994</v>
+        <v>-58.418108</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.655027</v>
+        <v>-34.62564</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5413,7 +5413,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5470,14 +5470,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.418108</v>
+        <v>-58.433855</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.62564</v>
+        <v>-34.614487</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5499,22 +5499,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5556,24 +5556,24 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.433855</v>
+        <v>-58.441198</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.614487</v>
+        <v>-34.605341</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5585,22 +5585,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5642,24 +5642,24 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.441198</v>
+        <v>-58.439239</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.605341</v>
+        <v>-34.6604</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5728,10 +5728,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.439239</v>
+        <v>-58.388529</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.6604</v>
+        <v>-34.655949</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5757,22 +5757,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5814,24 +5814,24 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.388529</v>
+        <v>-58.491325</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.655949</v>
+        <v>-34.647761</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t xml:space="preserve">7869 </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5900,24 +5900,24 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.491325</v>
+        <v>-58.469394</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.647761</v>
+        <v>-34.626925</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5929,22 +5929,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869 </t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5986,14 +5986,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.469394</v>
+        <v>-58.390974</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.626925</v>
+        <v>-34.594177</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6015,22 +6015,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t xml:space="preserve">7898 </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6072,14 +6072,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.390974</v>
+        <v>-58.459955</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.594177</v>
+        <v>-34.631973</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6101,22 +6101,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898 </t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6158,51 +6158,51 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.459955</v>
+        <v>-58.48802</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.631973</v>
+        <v>-34.641075</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>Pico 3481</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811198751</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6237,21 +6237,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.48802</v>
+        <v>-58.484883</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.641075</v>
+        <v>-34.54464</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6261,19 +6261,19 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pico 3481</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811198751</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6323,31 +6323,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.484883</v>
+        <v>-58.463198</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.54464</v>
+        <v>-34.62624</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6359,22 +6359,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6416,51 +6416,47 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.463198</v>
+        <v>-58.471183</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.62624</v>
+        <v>-34.638988</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>NRA-E</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t xml:space="preserve">7997 </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6475,7 +6471,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6502,32 +6498,36 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.471183</v>
+        <v>-58.46357</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.638988</v>
+        <v>-34.623187</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
+          <t>NRA-E</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7997 </t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>CASTRO, EMILIO AV. 7650</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811299445</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6577,31 +6577,31 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.46357</v>
+        <v>-58.524273</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.623187</v>
+        <v>-34.65615</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PAV-I</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6613,22 +6613,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CASTRO, EMILIO AV. 7650</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>811299445</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6670,14 +6670,14 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.524273</v>
+        <v>-58.45732</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.65615</v>
+        <v>-34.581366</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PAV-I</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6699,22 +6699,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6749,31 +6749,31 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.45732</v>
+        <v>-58.459547</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.581366</v>
+        <v>-34.626309</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6785,22 +6785,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/13/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>USPALLATA 3625</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811454350</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6842,10 +6842,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.459547</v>
+        <v>-58.414313</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.626309</v>
+        <v>-34.641194</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PPT-G</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6871,22 +6871,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1/13/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USPALLATA 3625</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>811454350</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6928,10 +6928,10 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.414313</v>
+        <v>-58.465166</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.641194</v>
+        <v>-34.670435</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PPT-G</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6957,17 +6957,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/16/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>GUAMINI 5049</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811498019</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7014,10 +7014,10 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.465166</v>
+        <v>-58.475365</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.670435</v>
+        <v>-34.688865</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PAV-S</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7043,22 +7043,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1/16/2026</t>
+          <t>1/23/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GUAMINI 5049</t>
+          <t xml:space="preserve">TRAFUL 3812 </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>811498019</t>
+          <t>811498075</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7100,14 +7100,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.475365</v>
+        <v>-58.414437</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.688865</v>
+        <v>-34.651882</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PAV-S</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7129,22 +7129,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1/23/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRAFUL 3812 </t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>811498075</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7186,10 +7186,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.414437</v>
+        <v>-58.438399</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.651882</v>
+        <v>-34.663958</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7272,14 +7272,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.438399</v>
+        <v>-58.475565</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.663958</v>
+        <v>-34.660488</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7301,22 +7301,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7358,10 +7358,10 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.475565</v>
+        <v>-58.460855</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.660488</v>
+        <v>-34.631046</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7387,22 +7387,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7444,10 +7444,10 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.460855</v>
+        <v>-58.479751</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.631046</v>
+        <v>-34.677211</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7530,36 +7530,36 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>-58.479751</v>
+        <v>-58.491573</v>
       </c>
       <c r="N83" t="n">
-        <v>-34.677211</v>
+        <v>-34.639215</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7616,10 +7616,10 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>-58.491573</v>
+        <v>-58.487715</v>
       </c>
       <c r="N84" t="n">
-        <v>-34.639215</v>
+        <v>-34.636671</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t xml:space="preserve">8245 </t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7702,10 +7702,10 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>-58.487715</v>
+        <v>-58.488539</v>
       </c>
       <c r="N85" t="n">
-        <v>-34.636671</v>
+        <v>-34.640962</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7731,22 +7731,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245 </t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7788,51 +7788,51 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-58.488539</v>
+        <v>-58.481162</v>
       </c>
       <c r="N86" t="n">
-        <v>-34.640962</v>
+        <v>-34.665875</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>-747</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7874,14 +7874,14 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-58.481162</v>
+        <v>-58.413945</v>
       </c>
       <c r="N87" t="n">
-        <v>-34.665875</v>
+        <v>-34.582774</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7903,22 +7903,18 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>-747</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2/4/2026</t>
-        </is>
-      </c>
+          <t>S01421388</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7933,12 +7929,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7960,14 +7956,14 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-58.413945</v>
+        <v>-58.437739</v>
       </c>
       <c r="N88" t="n">
-        <v>-34.582774</v>
+        <v>-34.638224</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -7977,7 +7973,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7989,13 +7985,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S01421388</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>-759</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8042,10 +8042,10 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-58.437739</v>
+        <v>-58.469878</v>
       </c>
       <c r="N89" t="n">
-        <v>-34.638224</v>
+        <v>-34.626919</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8071,17 +8071,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>-759</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8128,10 +8128,10 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-58.469878</v>
+        <v>-58.46026</v>
       </c>
       <c r="N90" t="n">
-        <v>-34.626919</v>
+        <v>-34.640706</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8157,22 +8157,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8214,10 +8214,10 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-58.46026</v>
+        <v>-58.480708</v>
       </c>
       <c r="N91" t="n">
-        <v>-34.640706</v>
+        <v>-34.667639</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8300,36 +8300,36 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>-58.480708</v>
+        <v>-58.488539</v>
       </c>
       <c r="N92" t="n">
-        <v>-34.667639</v>
+        <v>-34.640962</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>812440296</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8386,10 +8386,10 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>-58.488539</v>
+        <v>-58.474151</v>
       </c>
       <c r="N93" t="n">
-        <v>-34.640962</v>
+        <v>-34.630046</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8403,19 +8403,19 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8460,125 +8460,39 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>-58.474151</v>
+        <v>-58.464382</v>
       </c>
       <c r="N94" t="n">
-        <v>-34.630046</v>
+        <v>-34.683083</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2NRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>S00552343</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>inclinada base corroida</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>-58.464382</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-34.683083</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>PAV-U</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,96 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tipo de tarea</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tipo de Elemento</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
@@ -5069,7 +5057,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7829 </t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5843,7 +5831,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869 </t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6015,7 +6003,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7898 </t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6441,7 +6429,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7997 </t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7645,7 +7633,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245 </t>
+          <t>8245</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7817,7 +7805,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>-747</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7985,7 +7973,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>-759</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8493,6 +8481,432 @@
         </is>
       </c>
       <c r="R94" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>S00176142</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CULPINA 533</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>-58.464205</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-34.636221</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8554</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OLIDEN 55</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>columna inclinada</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-58.517269</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-34.639879</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>PAV-B</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>-772</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LA PLATA AV. 2304</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Desplazar Columna</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-58.423086</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-34.641356</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>-773</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LA PLATA AV. 2244</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>desmonte</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Desmonte</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>-58.423288</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-34.640581</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>-774</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CASEROS AV. 4131</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>mover a 4111</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>-58.422741</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-34.639999</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,27 +683,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>798897149</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10/16/2024</t>
+          <t>11/5/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>José Andrés Pacheco de Melo 2084</t>
+          <t>GODOY CRUZ 2604</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -713,37 +713,41 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>798897149</t>
+          <t>799246642</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pendiente de traspaso Fuente TECO y retiro de columna</t>
+          <t>Realizar traspasos y retiro de columna vieja</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-58.395656</v>
+        <v>-58.426169</v>
       </c>
       <c r="N4" t="n">
-        <v>-34.590364</v>
+        <v>-34.579697</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -753,7 +757,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>RET-C</t>
+          <t>VCR-N</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -765,22 +769,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11/5/2024</t>
+          <t>12/19/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GODOY CRUZ 2604</t>
+          <t>LORA, FELIX 27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -795,41 +799,41 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>799246642</t>
+          <t>801768138</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Realizar traspasos y retiro de columna vieja</t>
+          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-58.426169</v>
+        <v>-58.443626</v>
       </c>
       <c r="N5" t="n">
-        <v>-34.579697</v>
+        <v>-34.621032</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -839,7 +843,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>VCR-N</t>
+          <t>PCH-G</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -851,22 +855,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12/19/2024</t>
+          <t>1/14/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LORA, FELIX 27</t>
+          <t>Campana	534</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,12 +885,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>801768138</t>
+          <t>802657454</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -896,7 +900,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -908,56 +912,56 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-58.443626</v>
+        <v>-58.477376</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.621032</v>
+        <v>-34.626126</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2/20/2024</t>
+          <t>1/24/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ZABALA 2844</t>
+          <t>BRASIL 2561</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -967,12 +971,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>780340125</t>
+          <t>802871857</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>cambiar columna y emprolijar cables y cajas de empalme que se ven en las fotos</t>
+          <t>Colocar columna R400 - Fuente Teco</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -982,7 +986,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -994,24 +998,24 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.452328</v>
+        <v>-58.400156</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.572196</v>
+        <v>-34.631369</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ATH-Q</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1023,27 +1027,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11/7/2024</t>
+          <t>1/30/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OLLEROS 2952</t>
+          <t>RONDEAU 2775</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1053,12 +1057,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>799450967</t>
+          <t>802988219</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Terminar transferencia, retirar columna vieja</t>
+          <t>Relevar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1077,17 +1081,17 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.447022</v>
+        <v>-58.402062</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.575873</v>
+        <v>-34.635143</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ATH-P</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1109,27 +1113,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12/21/2024</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MERCEDES 254</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1139,12 +1143,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>801901755</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1154,7 +1158,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1166,51 +1170,51 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.484232</v>
+        <v>-58.423042</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.631431</v>
+        <v>-34.625868</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>DEV-L</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2DEV</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1/14/2025</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Campana	534</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1225,12 +1229,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>802657454</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1252,56 +1256,56 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.477376</v>
+        <v>-58.425764</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.626126</v>
+        <v>-34.604359</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1/22/2025</t>
+          <t>4/22/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CUENCA 3345</t>
+          <t>MONTES DE OCA, MANUEL AV. 511</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1311,12 +1315,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>802843289</t>
+          <t>804876051</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Pegar los ductos al prfv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1326,7 +1330,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1338,46 +1342,46 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.496935</v>
+        <v>-58.375515</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.599084</v>
+        <v>-34.634393</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>PUE-B</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1/24/2025</t>
+          <t>5/4/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BRASIL 2561</t>
+          <t>AZARA 15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1397,12 +1401,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>802871857</t>
+          <t>805655333</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Colocar columna R400 - Fuente Teco</t>
+          <t>Picada entro tambien como reclamo 7611</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1412,7 +1416,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1424,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.400156</v>
+        <v>-58.372751</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.631369</v>
+        <v>-34.631917</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1441,34 +1445,34 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1/30/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RONDEAU 2775</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1483,12 +1487,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>802988219</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Relevar</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1510,14 +1514,14 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.402062</v>
+        <v>-58.395063</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.635143</v>
+        <v>-34.606257</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1527,7 +1531,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1539,27 +1543,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2/10/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>YERBAL 489</t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1569,51 +1573,51 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>803607520</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Desmonte de columna ya traspasaron nodo</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.438053</v>
+        <v>-58.483927</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.617481</v>
+        <v>-34.570689</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ALM-G</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1625,27 +1629,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2/14/2025</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHACO 195</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1655,12 +1659,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>803607699</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Desmontar columna personal propio traspaso nodo</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1670,22 +1674,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.431522</v>
+        <v>-58.477944</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.617523</v>
+        <v>-34.675149</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1699,7 +1703,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ALM-F</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1711,17 +1715,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1741,12 +1745,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1768,14 +1772,14 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.423042</v>
+        <v>-58.425478</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.625868</v>
+        <v>-34.601865</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1797,27 +1801,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>THAMES 649</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1827,12 +1831,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>804309655</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>QAP traspaso fuente propia para posterior pasar a TLC</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1842,7 +1846,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1854,14 +1858,14 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.441405</v>
+        <v>-58.401624</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.594348</v>
+        <v>-34.612001</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1871,7 +1875,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1883,27 +1887,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3/27/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZELARRAYAN 6147</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1913,10 +1917,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>804309801</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>809642175</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -1924,7 +1932,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1936,24 +1944,24 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.483821</v>
+        <v>-58.458298</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.677698</v>
+        <v>-34.566511</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1965,22 +1973,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,17 +2003,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2015,21 +2023,21 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.425764</v>
+        <v>-58.409278</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.604359</v>
+        <v>-34.653566</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2051,17 +2059,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4/22/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 511</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2081,12 +2089,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>804876051</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pegar los ductos al prfv</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2108,10 +2116,10 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.375515</v>
+        <v>-58.399262</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.634393</v>
+        <v>-34.639685</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2125,34 +2133,34 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2167,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2194,10 +2202,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.372751</v>
+        <v>-58.384406</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.631917</v>
+        <v>-34.622932</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2211,34 +2219,34 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2253,12 +2261,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2268,7 +2276,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2280,14 +2288,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.395063</v>
+        <v>-58.46138</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.606257</v>
+        <v>-34.629774</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2297,7 +2305,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2309,22 +2317,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2339,17 +2347,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2359,31 +2367,31 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.483927</v>
+        <v>-58.458516</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.570689</v>
+        <v>-34.646422</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2395,22 +2403,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2425,12 +2433,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2445,21 +2453,21 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.477944</v>
+        <v>-58.374086</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.675149</v>
+        <v>-34.633168</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2469,39 +2477,39 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MAZA 181</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2511,7 +2519,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>807215439</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2526,7 +2534,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2538,14 +2546,14 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.416477</v>
+        <v>-58.416237</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.61303</v>
+        <v>-34.65477</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2555,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CLI-I</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2567,17 +2575,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2597,12 +2605,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2624,14 +2632,14 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.425478</v>
+        <v>-58.411426</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.601865</v>
+        <v>-34.633266</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2641,7 +2649,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2653,22 +2661,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2683,12 +2691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Desmontar PRFV 400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2698,26 +2706,26 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.401624</v>
+        <v>-58.435731</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.612001</v>
+        <v>-34.597659</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2727,7 +2735,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2739,27 +2747,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6/30/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHILE 2561</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2769,10 +2777,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>807851584</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>810451584</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Picada</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Cambio</t>
@@ -2780,7 +2792,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2792,14 +2804,14 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.401827</v>
+        <v>-58.418542</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.617667</v>
+        <v>-34.624609</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2809,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CEN-M</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2821,27 +2833,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8/12/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MARMOL, JOSE 228</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2851,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>808918687</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Se deriva directamente a traspaso de fuente ya que hay una columna existente</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2866,7 +2878,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2875,13 +2887,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.425858</v>
+        <v>-58.430613</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.61629</v>
+        <v>-34.608805</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2895,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>ALM-D</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2907,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>-579</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9/2/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pedro Rivera 2546</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2937,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ICD30612785</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Colocar R200 para pedir traspaso de equipos</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2964,14 +2976,14 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.462479</v>
+        <v>-58.50161</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.55765</v>
+        <v>-34.647648</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2981,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>COG-K</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2993,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3023,7 +3035,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3050,24 +3062,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.458298</v>
+        <v>-58.439164</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.566511</v>
+        <v>-34.597069</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3079,22 +3091,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9/16/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LARRALDE, CRISOLOGO AV. 3875</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3109,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>809784524</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3129,31 +3141,31 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.481316</v>
+        <v>-58.417634</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.556157</v>
+        <v>-34.587439</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>COG-O</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3165,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3195,17 +3207,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3215,31 +3227,31 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.409278</v>
+        <v>-58.48121</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.653566</v>
+        <v>-34.61126</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3251,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3281,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3296,7 +3308,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3308,14 +3320,14 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.399262</v>
+        <v>-58.440031</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.639685</v>
+        <v>-34.575409</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3325,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3337,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3367,7 +3379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3394,14 +3406,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.384406</v>
+        <v>-58.413563</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.622932</v>
+        <v>-34.624645</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3411,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3423,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2409</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3453,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810132768</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada volvio a ingresar mail con caso 7597</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3468,7 +3480,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3480,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.461482</v>
+        <v>-58.364132</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.632432</v>
+        <v>-34.628423</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3497,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3509,27 +3521,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3539,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3554,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3566,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.465176</v>
+        <v>-58.460356</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.680979</v>
+        <v>-34.630793</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3583,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3595,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3625,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.46138</v>
+        <v>-58.389676</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.629774</v>
+        <v>-34.618127</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3669,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3681,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3711,7 +3723,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3738,10 +3750,10 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.458516</v>
+        <v>-58.418108</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.646422</v>
+        <v>-34.62564</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3755,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3767,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3797,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3824,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.374086</v>
+        <v>-58.433855</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.633168</v>
+        <v>-34.614487</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3841,34 +3853,34 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3883,7 +3895,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3910,24 +3922,24 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.416237</v>
+        <v>-58.441198</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.65477</v>
+        <v>-34.605341</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3939,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3969,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3996,10 +4008,10 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.411426</v>
+        <v>-58.439239</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.633266</v>
+        <v>-34.6604</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4013,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4025,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4055,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4075,21 +4087,21 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.435731</v>
+        <v>-58.388529</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.597659</v>
+        <v>-34.655949</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4099,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4111,27 +4123,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ANCHORENA, TOMAS MANUEL DE, DR. 1754</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4141,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01230434</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Traspaso de nodo propio avisar a telecentro despues del traspaso</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4156,7 +4168,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4165,27 +4177,27 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.4018</v>
+        <v>-58.491325</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.590471</v>
+        <v>-34.647761</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>AGU-F</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4197,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4227,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.418542</v>
+        <v>-58.469394</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.624609</v>
+        <v>-34.626925</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4271,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4283,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4313,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4328,7 +4340,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4340,14 +4352,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.430613</v>
+        <v>-58.390974</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.608805</v>
+        <v>-34.594177</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4357,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4369,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4399,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4414,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4426,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.50161</v>
+        <v>-58.459955</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.647648</v>
+        <v>-34.631973</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4455,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4485,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,51 +4524,51 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.439164</v>
+        <v>-58.48802</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.597069</v>
+        <v>-34.641075</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4571,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4598,14 +4610,14 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.417634</v>
+        <v>-58.463198</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.587439</v>
+        <v>-34.62624</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4615,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4627,27 +4639,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S01150217</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vera 311</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4657,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01230602</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Traspasar Fuente</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4672,63 +4684,59 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.436262</v>
+        <v>-58.471183</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.600478</v>
+        <v>-34.638988</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>CLI-O</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4743,12 +4751,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,24 +4778,24 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.48121</v>
+        <v>-58.46357</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.61126</v>
+        <v>-34.623187</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4799,22 +4807,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4829,12 +4837,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4844,36 +4852,36 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.440031</v>
+        <v>-58.45732</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.575409</v>
+        <v>-34.581366</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4885,22 +4893,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4915,12 +4923,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,10 +4950,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.413563</v>
+        <v>-58.459547</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.624645</v>
+        <v>-34.626309</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4959,7 +4967,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4971,22 +4979,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5001,12 +5009,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5016,7 +5024,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5028,14 +5036,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.364132</v>
+        <v>-58.465166</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.628423</v>
+        <v>-34.670435</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5045,7 +5053,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5057,22 +5065,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5087,12 +5095,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5114,14 +5122,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.460356</v>
+        <v>-58.438399</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.630793</v>
+        <v>-34.663958</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5131,7 +5139,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5143,22 +5151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5173,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5200,14 +5208,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.389676</v>
+        <v>-58.475565</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.618127</v>
+        <v>-34.660488</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5217,7 +5225,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5229,27 +5237,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-670</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Timoteo Gordillo 1666</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5259,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810651269</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Cambiar columna de lugar la actual es un poste ex Cablevision correrla ya que el vecino reclama obstruccion de la cochera</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5286,24 +5294,24 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.510994</v>
+        <v>-58.460855</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.655027</v>
+        <v>-34.631046</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PAV-J</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5315,22 +5323,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5345,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5372,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.418108</v>
+        <v>-58.479751</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.62564</v>
+        <v>-34.677211</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5389,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5401,22 +5409,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5431,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5458,51 +5466,51 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.433855</v>
+        <v>-58.491573</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.614487</v>
+        <v>-34.639215</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5517,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5544,14 +5552,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.441198</v>
+        <v>-58.487715</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.605341</v>
+        <v>-34.636671</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5561,34 +5569,34 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5603,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5630,51 +5638,51 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.439239</v>
+        <v>-58.488539</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.6604</v>
+        <v>-34.640962</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5689,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5716,14 +5724,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.388529</v>
+        <v>-58.481162</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.655949</v>
+        <v>-34.665875</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5733,7 +5741,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5745,22 +5753,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5775,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5802,24 +5810,24 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.491325</v>
+        <v>-58.413945</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.647761</v>
+        <v>-34.582774</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5831,17 +5839,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5861,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5888,10 +5896,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.469394</v>
+        <v>-58.437739</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.626925</v>
+        <v>-34.638224</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5905,7 +5913,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5917,22 +5925,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5947,7 +5955,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5962,7 +5970,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5974,14 +5982,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.390974</v>
+        <v>-58.469878</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.594177</v>
+        <v>-34.626919</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5991,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6003,17 +6011,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6033,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6060,10 +6068,10 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.459955</v>
+        <v>-58.46026</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.631973</v>
+        <v>-34.640706</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6077,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6089,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6119,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6146,51 +6154,51 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.48802</v>
+        <v>-58.480708</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.641075</v>
+        <v>-34.667639</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pico 3481</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6205,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811198751</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6225,21 +6233,21 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Poste</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.484883</v>
+        <v>-58.488539</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.54464</v>
+        <v>-34.640962</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6249,29 +6257,29 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6291,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6318,51 +6326,51 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.463198</v>
+        <v>-58.474151</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.62624</v>
+        <v>-34.630046</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6377,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6392,54 +6400,58 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.471183</v>
+        <v>-58.464382</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.638988</v>
+        <v>-34.683083</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
+          <t>PAV-U</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6459,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6474,7 +6486,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6486,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.46357</v>
+        <v>-58.464205</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.623187</v>
+        <v>-34.636221</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6503,29 +6515,25 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NRA-E</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CASTRO, EMILIO AV. 7650</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6545,12 +6553,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>811299445</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6572,10 +6580,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.524273</v>
+        <v>-58.517269</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.65615</v>
+        <v>-34.639879</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6589,2324 +6597,10 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PAV-I</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1/8/2026</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>FOREST AV. 957</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>811453824</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>chocada</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" t="n">
-        <v>-58.45732</v>
-      </c>
-      <c r="N73" t="n">
-        <v>-34.581366</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>ATH-N</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>S00982176</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1/9/2026</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>GRANADEROS 110</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>811453890</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" t="n">
-        <v>-58.459547</v>
-      </c>
-      <c r="N74" t="n">
-        <v>-34.626309</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>PCH-H</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>8083</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1/13/2026</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>USPALLATA 3625</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>811454350</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" t="n">
-        <v>-58.414313</v>
-      </c>
-      <c r="N75" t="n">
-        <v>-34.641194</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>PPT-G</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>8127</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1/14/2026</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ESCALADA AV. 3100</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>811454435</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>1</v>
-      </c>
-      <c r="M76" t="n">
-        <v>-58.465166</v>
-      </c>
-      <c r="N76" t="n">
-        <v>-34.670435</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>PAV-?</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>8145</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1/16/2026</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>GUAMINI 5049</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>811498019</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" t="n">
-        <v>-58.475365</v>
-      </c>
-      <c r="N77" t="n">
-        <v>-34.688865</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>PAV-S</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>8203</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1/23/2026</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRAFUL 3812 </t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>811498075</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="n">
-        <v>-58.414437</v>
-      </c>
-      <c r="N78" t="n">
-        <v>-34.651882</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>PPT-H</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>8211</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1/26/2026</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>811626780</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>chocada</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" t="n">
-        <v>-58.438399</v>
-      </c>
-      <c r="N79" t="n">
-        <v>-34.663958</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>PPT-I</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>8223</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1/26/2026</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>811626771</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" t="n">
-        <v>-58.475565</v>
-      </c>
-      <c r="N80" t="n">
-        <v>-34.660488</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>PAV-P</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>-739</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1/27/2026</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>811626802</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" t="n">
-        <v>-58.460855</v>
-      </c>
-      <c r="N81" t="n">
-        <v>-34.631046</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>PCH-F</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>S01281615</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>811626968</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" t="n">
-        <v>-58.479751</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-34.677211</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>S01447367</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>MOZART 216</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>811626897</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>-58.491573</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-34.639215</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>S01447520</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>811626894</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" t="n">
-        <v>-58.487715</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-34.636671</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>8245</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>811626837</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>1</v>
-      </c>
-      <c r="M85" t="n">
-        <v>-58.488539</v>
-      </c>
-      <c r="N85" t="n">
-        <v>-34.640962</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>8270</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2/3/2026</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>811627028</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" t="n">
-        <v>-58.481162</v>
-      </c>
-      <c r="N86" t="n">
-        <v>-34.665875</v>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>8490</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2/4/2026</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ugarteche 2816</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>811627090</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>corroida inclinada</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" t="n">
-        <v>-58.413945</v>
-      </c>
-      <c r="N87" t="n">
-        <v>-34.582774</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>AGU-M</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>S01421388</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>MITRE, EMILIO 1602</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>812503538</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>corroida</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" t="n">
-        <v>-58.437739</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-34.638224</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>PPT-S</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>8545</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>TERRADA 402</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>812440368</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L89" t="n">
-        <v>1</v>
-      </c>
-      <c r="M89" t="n">
-        <v>-58.469878</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-34.626919</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>NRA-L</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>S00086082</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2/5/2026</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>812439923</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>inclinada corroida</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>-58.46026</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-34.640706</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>PPT-N</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>8268</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>MONTREAL 5391</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>812440314</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
-      <c r="M91" t="n">
-        <v>-58.480708</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-34.667639</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>PAV-Q</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>8244</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>812440296</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>-58.488539</v>
-      </c>
-      <c r="N92" t="n">
-        <v>-34.640962</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>S00936659</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>812440276</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>inclinada</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
-        <v>1</v>
-      </c>
-      <c r="M93" t="n">
-        <v>-58.474151</v>
-      </c>
-      <c r="N93" t="n">
-        <v>-34.630046</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>NRA-R</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2NRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>S00552343</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2/23/2026</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>inclinada base corroida</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
-      <c r="M94" t="n">
-        <v>-58.464382</v>
-      </c>
-      <c r="N94" t="n">
-        <v>-34.683083</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>PAV-U</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>S00176142</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>3/6/2026</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>CULPINA 533</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>base corroida</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Nodo Teco</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>-58.464205</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-34.636221</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>8554</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>OLIDEN 55</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>columna inclinada</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" t="n">
-        <v>-58.517269</v>
-      </c>
-      <c r="N96" t="n">
-        <v>-34.639879</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>PAV-B</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>-772</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>3/10/2026</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>LA PLATA AV. 2304</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Desplazar Columna</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
-        <v>1</v>
-      </c>
-      <c r="M97" t="n">
-        <v>-58.423086</v>
-      </c>
-      <c r="N97" t="n">
-        <v>-34.641356</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>PPT-L</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>-773</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>LA PLATA AV. 2244</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>desmonte</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Desmonte</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L98" t="n">
-        <v>1</v>
-      </c>
-      <c r="M98" t="n">
-        <v>-58.423288</v>
-      </c>
-      <c r="N98" t="n">
-        <v>-34.640581</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>PPT-L</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>-774</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>CASEROS AV. 4131</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>mover a 4111</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L99" t="n">
-        <v>1</v>
-      </c>
-      <c r="M99" t="n">
-        <v>-58.422741</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-34.639999</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>PPT-L</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1887,27 +1887,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>ALBARELLOS AV. 3100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Transito</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1917,17 +1917,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>ICD30340076</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>QAP fotos del gcba tenia las incorrectas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1937,21 +1937,21 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.458298</v>
+        <v>-58.512533</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.566511</v>
+        <v>-34.579243</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1973,22 +1973,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2023,31 +2023,31 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.409278</v>
+        <v>-58.458298</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.653566</v>
+        <v>-34.566511</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.399262</v>
+        <v>-58.409278</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.639685</v>
+        <v>-34.653566</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2145,22 +2145,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2202,10 +2202,10 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.384406</v>
+        <v>-58.399262</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.622932</v>
+        <v>-34.639685</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2288,14 +2288,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.46138</v>
+        <v>-58.384406</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.629774</v>
+        <v>-34.622932</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,17 +2317,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2374,10 +2374,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.458516</v>
+        <v>-58.46138</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.646422</v>
+        <v>-34.629774</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2460,14 +2460,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.374086</v>
+        <v>-58.458516</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.633168</v>
+        <v>-34.646422</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2477,29 +2477,29 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2546,10 +2546,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.416237</v>
+        <v>-58.374086</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.65477</v>
+        <v>-34.633168</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,34 +2563,34 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.411426</v>
+        <v>-58.416237</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.633266</v>
+        <v>-34.65477</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2661,22 +2661,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2711,21 +2711,21 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.435731</v>
+        <v>-58.411426</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.597659</v>
+        <v>-34.633266</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2747,22 +2747,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2797,21 +2797,21 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.418542</v>
+        <v>-58.435731</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.624609</v>
+        <v>-34.597659</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,7 +2833,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2890,14 +2890,14 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.430613</v>
+        <v>-58.418542</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.608805</v>
+        <v>-34.624609</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2976,24 +2976,24 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.50161</v>
+        <v>-58.430613</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.647648</v>
+        <v>-34.608805</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3062,24 +3062,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.439164</v>
+        <v>-58.50161</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.597069</v>
+        <v>-34.647648</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3148,10 +3148,10 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.417634</v>
+        <v>-58.439164</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.587439</v>
+        <v>-34.597069</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3234,24 +3234,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.48121</v>
+        <v>-58.417634</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.61126</v>
+        <v>-34.587439</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3320,24 +3320,24 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.440031</v>
+        <v>-58.48121</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.575409</v>
+        <v>-34.61126</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3406,14 +3406,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.413563</v>
+        <v>-58.440031</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.624645</v>
+        <v>-34.575409</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3492,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.364132</v>
+        <v>-58.413563</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.628423</v>
+        <v>-34.624645</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,22 +3521,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,14 +3578,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.460356</v>
+        <v>-58.364132</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.630793</v>
+        <v>-34.628423</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.389676</v>
+        <v>-58.460356</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.618127</v>
+        <v>-34.630793</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.418108</v>
+        <v>-58.389676</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.62564</v>
+        <v>-34.618127</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3836,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.433855</v>
+        <v>-58.418108</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.614487</v>
+        <v>-34.62564</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,24 +3922,24 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.441198</v>
+        <v>-58.433855</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.605341</v>
+        <v>-34.614487</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,24 +4008,24 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.439239</v>
+        <v>-58.441198</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.6604</v>
+        <v>-34.605341</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,10 +4094,10 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.388529</v>
+        <v>-58.439239</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.655949</v>
+        <v>-34.6604</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.491325</v>
+        <v>-58.388529</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.647761</v>
+        <v>-34.655949</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4266,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.469394</v>
+        <v>-58.491325</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.626925</v>
+        <v>-34.647761</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4352,14 +4352,14 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.390974</v>
+        <v>-58.469394</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.594177</v>
+        <v>-34.626925</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4438,14 +4438,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.459955</v>
+        <v>-58.390974</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.631973</v>
+        <v>-34.594177</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4524,51 +4524,51 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.48802</v>
+        <v>-58.459955</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.641075</v>
+        <v>-34.631973</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4610,51 +4610,51 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.463198</v>
+        <v>-58.48802</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.62624</v>
+        <v>-34.641075</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4696,47 +4696,51 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.471183</v>
+        <v>-58.463198</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.638988</v>
+        <v>-34.62624</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+          <t>NRA-E</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4751,7 +4755,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4778,51 +4782,47 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.46357</v>
+        <v>-58.471183</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.623187</v>
+        <v>-34.638988</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NRA-E</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4857,31 +4857,31 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.45732</v>
+        <v>-58.46357</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.581366</v>
+        <v>-34.623187</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4893,22 +4893,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4943,31 +4943,31 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.459547</v>
+        <v>-58.45732</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.626309</v>
+        <v>-34.581366</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4979,22 +4979,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5036,10 +5036,10 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.465166</v>
+        <v>-58.459547</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.670435</v>
+        <v>-34.626309</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5065,17 +5065,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5122,14 +5122,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.438399</v>
+        <v>-58.465166</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.663958</v>
+        <v>-34.670435</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5208,14 +5208,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.475565</v>
+        <v>-58.438399</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.660488</v>
+        <v>-34.663958</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5294,10 +5294,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.460855</v>
+        <v>-58.475565</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.631046</v>
+        <v>-34.660488</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,22 +5323,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.479751</v>
+        <v>-58.460855</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.677211</v>
+        <v>-34.631046</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,7 +5409,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,36 +5466,36 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.491573</v>
+        <v>-58.479751</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.639215</v>
+        <v>-34.677211</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5552,10 +5552,10 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.487715</v>
+        <v>-58.491573</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.636671</v>
+        <v>-34.639215</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.488539</v>
+        <v>-58.487715</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.640962</v>
+        <v>-34.636671</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5667,22 +5667,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,51 +5724,51 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.481162</v>
+        <v>-58.488539</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.665875</v>
+        <v>-34.640962</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,14 +5810,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.413945</v>
+        <v>-58.481162</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.582774</v>
+        <v>-34.665875</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,14 +5896,14 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.437739</v>
+        <v>-58.413945</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.638224</v>
+        <v>-34.582774</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5925,17 +5925,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,10 +5982,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.469878</v>
+        <v>-58.437739</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.626919</v>
+        <v>-34.638224</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,22 +6011,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6061,31 +6061,31 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.46026</v>
+        <v>-58.494814</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.640706</v>
+        <v>-34.601905</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,10 +6154,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.480708</v>
+        <v>-58.469878</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.667639</v>
+        <v>-34.626919</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,22 +6183,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>812440296</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6240,36 +6240,36 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.488539</v>
+        <v>-58.46026</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.640962</v>
+        <v>-34.640706</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6326,36 +6326,36 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.474151</v>
+        <v>-58.480708</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.630046</v>
+        <v>-34.667639</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6400,58 +6400,58 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.464382</v>
+        <v>-58.488539</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.683083</v>
+        <v>-34.640962</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6498,109 +6498,281 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.464205</v>
+        <v>-58.474151</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.636221</v>
+        <v>-34.630046</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
+          <t>NRA-R</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2NRA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>S00552343</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2/23/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>inclinada base corroida</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-58.464382</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-34.683083</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>PAV-U</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S00176142</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CULPINA 533</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>base corroida</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-58.464205</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-34.636221</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>8554</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>3/9/2026</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>OLIDEN 55</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>Pendiente ADM</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>columna inclinada</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="L72" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" t="n">
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
         <v>-58.517269</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N74" t="n">
         <v>-34.639879</v>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Devoto</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>PAV-B</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,96 +425,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R74"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tipo de tarea</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Tipo de Elemento</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
@@ -511,22 +523,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10/29/2024</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ESTADO DE ISRAEL AV. 4819</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,17 +553,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>798894281</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Inclinado</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -561,21 +573,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-58.432085</v>
+        <v>-58.423086</v>
       </c>
       <c r="N2" t="n">
-        <v>-34.60178</v>
+        <v>-34.641356</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -585,7 +597,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -597,22 +609,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10/29/2024</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HERRERA 402</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -627,17 +639,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>798894295</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Inclinado En el form cargaron foto de otro caso</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -654,24 +666,24 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>-58.378613</v>
+        <v>-58.517269</v>
       </c>
       <c r="N3" t="n">
-        <v>-34.6349</v>
+        <v>-34.639879</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -683,22 +695,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11/5/2024</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GODOY CRUZ 2604</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -713,17 +725,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>799246642</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Realizar traspasos y retiro de columna vieja</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -733,21 +745,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-58.426169</v>
+        <v>-58.422741</v>
       </c>
       <c r="N4" t="n">
-        <v>-34.579697</v>
+        <v>-34.639999</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -757,7 +769,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>VCR-N</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -769,22 +781,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12/19/2024</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LORA, FELIX 27</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -799,12 +811,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>801768138</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -814,7 +826,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -826,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-58.443626</v>
+        <v>-58.464205</v>
       </c>
       <c r="N5" t="n">
-        <v>-34.621032</v>
+        <v>-34.636221</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -843,34 +855,30 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PCH-G</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1/14/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Campana	534</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -885,12 +893,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>802657454</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -912,51 +920,51 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-58.477376</v>
+        <v>-58.469878</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.626126</v>
+        <v>-34.626919</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1/24/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BRASIL 2561</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -971,12 +979,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>802871857</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Colocar columna R400 - Fuente Teco</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -986,7 +994,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -998,14 +1006,14 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.400156</v>
+        <v>-58.480708</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.631369</v>
+        <v>-34.667639</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1015,7 +1023,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1027,22 +1035,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1/30/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RONDEAU 2775</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1057,12 +1065,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>802988219</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Relevar</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1072,7 +1080,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1084,51 +1092,51 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.402062</v>
+        <v>-58.488539</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.635143</v>
+        <v>-34.640962</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1143,12 +1151,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1170,51 +1178,51 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.423042</v>
+        <v>-58.474151</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.625868</v>
+        <v>-34.630046</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1229,12 +1237,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1244,26 +1252,26 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.425764</v>
+        <v>-58.464382</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.604359</v>
+        <v>-34.683083</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1273,7 +1281,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1285,22 +1293,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4/22/2025</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 511</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1315,12 +1323,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>804876051</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pegar los ductos al prfv</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1342,14 +1350,14 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.375515</v>
+        <v>-58.46026</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.634393</v>
+        <v>-34.640706</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1359,34 +1367,34 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1401,12 +1409,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1428,14 +1436,14 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.372751</v>
+        <v>-58.413945</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.631917</v>
+        <v>-34.582774</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1445,34 +1453,34 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1487,12 +1495,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1502,7 +1510,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1514,14 +1522,14 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.395063</v>
+        <v>-58.437739</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.606257</v>
+        <v>-34.638224</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1531,7 +1539,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1543,22 +1551,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1573,17 +1581,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1600,14 +1608,14 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.483927</v>
+        <v>-58.494814</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.570689</v>
+        <v>-34.601905</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1617,7 +1625,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1629,17 +1637,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1659,12 +1667,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1679,17 +1687,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.477944</v>
+        <v>-58.481162</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.675149</v>
+        <v>-34.665875</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1703,7 +1711,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1715,17 +1723,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1745,12 +1753,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1772,10 +1780,10 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.425478</v>
+        <v>-58.423058</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.601865</v>
+        <v>-34.608916</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1789,7 +1797,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1801,22 +1809,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1831,12 +1839,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Desmontar PRFV 400</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1846,7 +1854,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1858,14 +1866,14 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.401624</v>
+        <v>-58.479751</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.612001</v>
+        <v>-34.677211</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1875,7 +1883,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1887,27 +1895,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3100</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente de Transito</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1917,17 +1925,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ICD30340076</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>QAP fotos del gcba tenia las incorrectas</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1937,21 +1945,21 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.512533</v>
+        <v>-58.491573</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.579243</v>
+        <v>-34.639215</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1961,34 +1969,34 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2003,12 +2011,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2030,14 +2038,14 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.458298</v>
+        <v>-58.487715</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.566511</v>
+        <v>-34.636671</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2047,34 +2055,34 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2089,17 +2097,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2109,58 +2117,58 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.409278</v>
+        <v>-58.488539</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.653566</v>
+        <v>-34.640962</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,12 +2183,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2202,14 +2210,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.399262</v>
+        <v>-58.460855</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.639685</v>
+        <v>-34.631046</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2219,7 +2227,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2239,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,12 +2269,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2288,10 +2296,10 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.384406</v>
+        <v>-58.438399</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.622932</v>
+        <v>-34.663958</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2305,7 +2313,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,22 +2325,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,12 +2355,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2374,10 +2382,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.46138</v>
+        <v>-58.475565</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.629774</v>
+        <v>-34.660488</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2391,7 +2399,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2403,22 +2411,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,12 +2441,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2460,10 +2468,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.458516</v>
+        <v>-58.465166</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.646422</v>
+        <v>-34.670435</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2477,7 +2485,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,22 +2497,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2519,12 +2527,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2546,14 +2554,14 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.374086</v>
+        <v>-58.459547</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.633168</v>
+        <v>-34.626309</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2563,34 +2571,34 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,12 +2613,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2625,31 +2633,31 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.416237</v>
+        <v>-58.45732</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.65477</v>
+        <v>-34.581366</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2661,22 +2669,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2691,12 +2699,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2718,14 +2726,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.411426</v>
+        <v>-58.46357</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.633266</v>
+        <v>-34.623187</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2735,7 +2743,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2747,22 +2755,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2785,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2797,58 +2805,54 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.435731</v>
+        <v>-58.471183</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.597659</v>
+        <v>-34.638988</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>VCR-H</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2867,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2890,10 +2894,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.418542</v>
+        <v>-58.463198</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.624609</v>
+        <v>-34.62624</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2907,7 +2911,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2923,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,12 +2953,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2976,51 +2980,51 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.430613</v>
+        <v>-58.48802</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.608805</v>
+        <v>-34.641075</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3039,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3050,7 +3054,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3062,24 +3066,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.50161</v>
+        <v>-58.459955</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.647648</v>
+        <v>-34.631973</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,17 +3095,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3121,12 +3125,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3141,17 +3145,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.439164</v>
+        <v>-58.430396</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.597069</v>
+        <v>-34.599668</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3165,7 +3169,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3181,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,12 +3211,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3222,7 +3226,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,14 +3238,14 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.417634</v>
+        <v>-58.390974</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.587439</v>
+        <v>-34.594177</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3251,7 +3255,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3267,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3297,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3320,14 +3324,14 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.48121</v>
+        <v>-58.491325</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.61126</v>
+        <v>-34.647761</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3337,7 +3341,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3353,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3383,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3394,7 +3398,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3406,14 +3410,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.440031</v>
+        <v>-58.469394</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.575409</v>
+        <v>-34.626925</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3423,7 +3427,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3439,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3469,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3492,14 +3496,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.413563</v>
+        <v>-58.439239</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.624645</v>
+        <v>-34.6604</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3509,7 +3513,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,17 +3525,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3551,12 +3555,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3570,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,10 +3582,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.364132</v>
+        <v>-58.388529</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.628423</v>
+        <v>-34.655949</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3595,7 +3599,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3611,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,7 +3641,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3664,24 +3668,24 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.460356</v>
+        <v>-58.441198</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.630793</v>
+        <v>-34.605341</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3697,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3727,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3750,14 +3754,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.389676</v>
+        <v>-58.418108</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.618127</v>
+        <v>-34.62564</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,7 +3783,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3789,12 +3793,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3813,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3836,14 +3840,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.418108</v>
+        <v>-58.433855</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.62564</v>
+        <v>-34.614487</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3857,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3869,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3899,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3926,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.433855</v>
+        <v>-58.389676</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.614487</v>
+        <v>-34.618127</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3943,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3955,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,7 +3985,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4008,24 +4012,24 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.441198</v>
+        <v>-58.460356</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.605341</v>
+        <v>-34.630793</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4041,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4071,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4082,7 +4086,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4094,10 +4098,10 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.439239</v>
+        <v>-58.364132</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.6604</v>
+        <v>-34.628423</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4111,7 +4115,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4127,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4157,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4184,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.388529</v>
+        <v>-58.48121</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.655949</v>
+        <v>-34.61126</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4213,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4243,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,7 +4258,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4266,24 +4270,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.491325</v>
+        <v>-58.440031</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.647761</v>
+        <v>-34.575409</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4299,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4329,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,10 +4356,10 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.469394</v>
+        <v>-58.413563</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.626925</v>
+        <v>-34.624645</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4369,7 +4373,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,22 +4385,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4415,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4426,7 +4430,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4438,14 +4442,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.390974</v>
+        <v>-58.439164</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.594177</v>
+        <v>-34.597069</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4459,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4471,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4501,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4524,14 +4528,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.459955</v>
+        <v>-58.417634</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.631973</v>
+        <v>-34.587439</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4541,7 +4545,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4557,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4587,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4610,51 +4614,51 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.48802</v>
+        <v>-58.418542</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.641075</v>
+        <v>-34.624609</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4673,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4696,14 +4700,14 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.463198</v>
+        <v>-58.430613</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.62624</v>
+        <v>-34.608805</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4713,7 +4717,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,17 +4729,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4755,12 +4759,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4782,10 +4786,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.471183</v>
+        <v>-58.50161</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.638988</v>
+        <v>-34.647648</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4799,30 +4803,34 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+          <t>PAV-?</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4837,12 +4845,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4864,14 +4872,14 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.46357</v>
+        <v>-58.416237</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.623187</v>
+        <v>-34.65477</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4881,7 +4889,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4893,17 +4901,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4923,12 +4931,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4950,24 +4958,24 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.45732</v>
+        <v>-58.435731</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.581366</v>
+        <v>-34.597659</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4979,22 +4987,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5009,12 +5017,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5036,14 +5044,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.459547</v>
+        <v>-58.411426</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.626309</v>
+        <v>-34.633266</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5053,7 +5061,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5065,22 +5073,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5095,12 +5103,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5122,10 +5130,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.465166</v>
+        <v>-58.458516</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.670435</v>
+        <v>-34.646422</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5139,7 +5147,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5151,22 +5159,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,12 +5189,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5208,10 +5216,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.438399</v>
+        <v>-58.374086</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.663958</v>
+        <v>-34.633168</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5225,34 +5233,34 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5275,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5294,10 +5302,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.475565</v>
+        <v>-58.46138</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.660488</v>
+        <v>-34.629774</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5311,7 +5319,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,22 +5331,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5353,12 +5361,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,14 +5388,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.460855</v>
+        <v>-58.384406</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.631046</v>
+        <v>-34.622932</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5397,7 +5405,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,22 +5417,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5439,17 +5447,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5459,21 +5467,21 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.479751</v>
+        <v>-58.409278</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.677211</v>
+        <v>-34.653566</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,7 +5491,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5495,22 +5503,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5525,12 +5533,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5552,51 +5560,51 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.491573</v>
+        <v>-58.399262</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.639215</v>
+        <v>-34.639685</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,12 +5619,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,14 +5646,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.487715</v>
+        <v>-58.458298</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.636671</v>
+        <v>-34.566511</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5655,34 +5663,34 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5705,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5712,7 +5720,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5724,51 +5732,51 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.488539</v>
+        <v>-58.401624</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.640962</v>
+        <v>-34.612001</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5791,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,14 +5818,14 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.481162</v>
+        <v>-58.425478</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.665875</v>
+        <v>-34.601865</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5827,7 +5835,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5839,22 +5847,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,12 +5877,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5889,21 +5897,21 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.413945</v>
+        <v>-58.477944</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.582774</v>
+        <v>-34.675149</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5913,7 +5921,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5925,22 +5933,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,17 +5963,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5975,31 +5983,31 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.437739</v>
+        <v>-58.483927</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.638224</v>
+        <v>-34.570689</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,22 +6019,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6049,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6056,36 +6064,36 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.494814</v>
+        <v>-58.395063</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.601905</v>
+        <v>-34.606257</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,22 +6105,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>5/4/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t>AZARA 15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6135,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>805655333</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada entro tambien como reclamo 7611</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6162,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.469878</v>
+        <v>-58.372751</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.626919</v>
+        <v>-34.631917</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,34 +6179,34 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>4/22/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>MONTES DE OCA, MANUEL AV. 511</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6221,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>804876051</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>Pegar los ductos al prfv</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6240,14 +6248,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.46026</v>
+        <v>-58.375515</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.640706</v>
+        <v>-34.634393</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6257,34 +6265,34 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6307,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6326,14 +6334,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.480708</v>
+        <v>-58.425764</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.667639</v>
+        <v>-34.604359</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6343,7 +6351,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,22 +6363,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6393,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812440296</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6412,51 +6420,51 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.488539</v>
+        <v>-58.423042</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.640962</v>
+        <v>-34.625868</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>1/30/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>RONDEAU 2775</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6471,12 +6479,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>802988219</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Relevar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6486,7 +6494,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6498,51 +6506,51 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.474151</v>
+        <v>-58.402062</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.630046</v>
+        <v>-34.635143</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>1/24/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>BRASIL 2561</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,12 +6565,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>802871857</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>Colocar columna R400 - Fuente Teco</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6572,26 +6580,26 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.464382</v>
+        <v>-58.400156</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.683083</v>
+        <v>-34.631369</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6601,7 +6609,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6613,22 +6621,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>1/14/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>Campana	534</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,12 +6651,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>802657454</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6658,7 +6666,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6670,47 +6678,51 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.464205</v>
+        <v>-58.477376</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.636221</v>
+        <v>-34.626126</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
+          <t>NRA-R</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2NRA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>12/19/2024</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>LORA, FELIX 27</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6725,12 +6737,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>801768138</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6740,39 +6752,297 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>Nodo TLC</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-58.443626</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-34.621032</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>PCH-G</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>11/5/2024</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GODOY CRUZ 2604</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>799246642</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Realizar traspasos y retiro de columna vieja</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Terminal</t>
         </is>
       </c>
-      <c r="L74" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" t="n">
-        <v>-58.517269</v>
-      </c>
-      <c r="N74" t="n">
-        <v>-34.639879</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Devoto</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>PAV-B</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-58.426169</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-34.579697</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>VCR-N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10/29/2024</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ESTADO DE ISRAEL AV. 4819</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>798894281</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Inclinado</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-58.432085</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-34.60178</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10/29/2024</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HERRERA 402</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>798894295</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Inclinado En el form cargaron foto de otro caso</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-58.378613</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-34.6349</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>CON-H</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,96 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Caso</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>F. De Reclamo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Direccion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Proveedor Asignado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tipo de tarea</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tipo de Elemento</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Coordenada_X</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Coordenada_Y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Operacion</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
@@ -523,22 +511,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>10/29/2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>ESTADO DE ISRAEL AV. 4819</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,17 +541,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>798894281</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>Inclinado</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -573,21 +561,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-58.423086</v>
+        <v>-58.432085</v>
       </c>
       <c r="N2" t="n">
-        <v>-34.641356</v>
+        <v>-34.60178</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -597,7 +585,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -609,22 +597,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>10/29/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>HERRERA 402</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -639,17 +627,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>798894295</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Inclinado En el form cargaron foto de otro caso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -666,24 +654,24 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>-58.517269</v>
+        <v>-58.378613</v>
       </c>
       <c r="N3" t="n">
-        <v>-34.639879</v>
+        <v>-34.6349</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PAV-B</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -695,22 +683,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>11/5/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>GODOY CRUZ 2604</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -725,17 +713,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>799246642</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Realizar traspasos y retiro de columna vieja</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -745,21 +733,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-58.422741</v>
+        <v>-58.426169</v>
       </c>
       <c r="N4" t="n">
-        <v>-34.639999</v>
+        <v>-34.579697</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -769,7 +757,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>VCR-N</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -781,22 +769,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>12/19/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>LORA, FELIX 27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -811,12 +799,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>801768138</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -826,7 +814,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Nodo TLC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -838,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-58.464205</v>
+        <v>-58.443626</v>
       </c>
       <c r="N5" t="n">
-        <v>-34.636221</v>
+        <v>-34.621032</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -855,30 +843,34 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+          <t>PCH-G</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>1/14/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t>Campana	534</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -893,12 +885,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>802657454</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -920,51 +912,51 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-58.469878</v>
+        <v>-58.477376</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.626919</v>
+        <v>-34.626126</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>1/24/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t>BRASIL 2561</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -979,12 +971,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>802871857</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Colocar columna R400 - Fuente Teco</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -994,7 +986,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1006,14 +998,14 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-58.480708</v>
+        <v>-58.400156</v>
       </c>
       <c r="N7" t="n">
-        <v>-34.667639</v>
+        <v>-34.631369</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1023,7 +1015,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1035,22 +1027,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>1/30/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>RONDEAU 2775</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1065,12 +1057,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>812440296</t>
+          <t>802988219</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Relevar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1080,7 +1072,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1092,51 +1084,51 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-58.488539</v>
+        <v>-58.402062</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.640962</v>
+        <v>-34.635143</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/18/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>TREINTA Y TRES ORIENTALES 965</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1151,12 +1143,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>804161231</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1178,51 +1170,51 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-58.474151</v>
+        <v>-58.423042</v>
       </c>
       <c r="N9" t="n">
-        <v>-34.630046</v>
+        <v>-34.625868</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>4/8/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>SARMIENTO 4290</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1237,12 +1229,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>804569065</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>Columna corroída en su base entro tambien como caso 7049</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1252,26 +1244,26 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>-58.464382</v>
+        <v>-58.425764</v>
       </c>
       <c r="N10" t="n">
-        <v>-34.683083</v>
+        <v>-34.604359</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1281,7 +1273,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>ALM-L</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1293,22 +1285,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>4/22/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>MONTES DE OCA, MANUEL AV. 511</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1323,12 +1315,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>804876051</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>Pegar los ductos al prfv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1350,14 +1342,14 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-58.46026</v>
+        <v>-58.375515</v>
       </c>
       <c r="N11" t="n">
-        <v>-34.640706</v>
+        <v>-34.634393</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1367,34 +1359,34 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>5/4/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>AZARA 15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1409,12 +1401,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>805655333</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>Picada entro tambien como reclamo 7611</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1436,14 +1428,14 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.413945</v>
+        <v>-58.372751</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.582774</v>
+        <v>-34.631917</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1453,34 +1445,34 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1495,12 +1487,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1510,7 +1502,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1522,14 +1514,14 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.437739</v>
+        <v>-58.395063</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.638224</v>
+        <v>-34.606257</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1539,7 +1531,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1551,22 +1543,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1581,17 +1573,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1608,14 +1600,14 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.494814</v>
+        <v>-58.483927</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.601905</v>
+        <v>-34.570689</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1625,7 +1617,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1637,17 +1629,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1667,12 +1659,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1687,17 +1679,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.481162</v>
+        <v>-58.477944</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.665875</v>
+        <v>-34.675149</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1711,7 +1703,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1723,17 +1715,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1753,12 +1745,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1780,10 +1772,10 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.423058</v>
+        <v>-58.425478</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.608916</v>
+        <v>-34.601865</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1797,7 +1789,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1809,22 +1801,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1839,12 +1831,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1854,7 +1846,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1866,14 +1858,14 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.479751</v>
+        <v>-58.401624</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.677211</v>
+        <v>-34.612001</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1883,7 +1875,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1895,27 +1887,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>ALBARELLOS AV. 3100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Transito</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1925,17 +1917,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>ICD30340076</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>QAP fotos del gcba tenia las incorrectas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1945,21 +1937,21 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.491573</v>
+        <v>-58.512533</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.639215</v>
+        <v>-34.579243</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1969,34 +1961,34 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2011,12 +2003,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2038,14 +2030,14 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.487715</v>
+        <v>-58.458298</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.636671</v>
+        <v>-34.566511</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2055,34 +2047,34 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2097,17 +2089,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2117,58 +2109,58 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.488539</v>
+        <v>-58.409278</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.640962</v>
+        <v>-34.653566</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2183,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2210,14 +2202,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.460855</v>
+        <v>-58.399262</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.631046</v>
+        <v>-34.639685</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2227,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2239,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2269,12 +2261,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2296,10 +2288,10 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.438399</v>
+        <v>-58.384406</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.663958</v>
+        <v>-34.622932</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2313,7 +2305,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2325,22 +2317,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2355,12 +2347,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2382,10 +2374,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.475565</v>
+        <v>-58.46138</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.660488</v>
+        <v>-34.629774</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2399,7 +2391,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2411,22 +2403,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2441,12 +2433,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2468,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.465166</v>
+        <v>-58.458516</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.670435</v>
+        <v>-34.646422</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2485,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2497,22 +2489,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2527,12 +2519,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2554,14 +2546,14 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.459547</v>
+        <v>-58.374086</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.626309</v>
+        <v>-34.633168</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2571,34 +2563,34 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2613,12 +2605,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2633,31 +2625,31 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.45732</v>
+        <v>-58.416237</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.581366</v>
+        <v>-34.65477</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2669,22 +2661,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2699,12 +2691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2726,14 +2718,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.46357</v>
+        <v>-58.411426</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.623187</v>
+        <v>-34.633266</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2743,7 +2735,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2755,22 +2747,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2785,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2805,54 +2797,58 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.471183</v>
+        <v>-58.435731</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.638988</v>
+        <v>-34.597659</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+          <t>VCR-H</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2867,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2894,10 +2890,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.463198</v>
+        <v>-58.418542</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.62624</v>
+        <v>-34.624609</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2911,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2923,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2953,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2980,51 +2976,51 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.48802</v>
+        <v>-58.430613</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.641075</v>
+        <v>-34.608805</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3039,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3054,7 +3050,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3066,24 +3062,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.459955</v>
+        <v>-58.50161</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.631973</v>
+        <v>-34.647648</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3095,17 +3091,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3125,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3145,17 +3141,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.430396</v>
+        <v>-58.439164</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.599668</v>
+        <v>-34.597069</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3169,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3181,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3211,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3226,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3238,14 +3234,14 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.390974</v>
+        <v>-58.417634</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.594177</v>
+        <v>-34.587439</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3255,7 +3251,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3267,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3297,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3324,14 +3320,14 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.491325</v>
+        <v>-58.48121</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.647761</v>
+        <v>-34.61126</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3341,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3353,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3383,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3398,7 +3394,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3410,14 +3406,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.469394</v>
+        <v>-58.440031</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.626925</v>
+        <v>-34.575409</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3427,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3439,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3469,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3496,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.439239</v>
+        <v>-58.413563</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.6604</v>
+        <v>-34.624645</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3513,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3525,17 +3521,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3555,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3570,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3582,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.388529</v>
+        <v>-58.364132</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.655949</v>
+        <v>-34.628423</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3599,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3611,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3641,7 +3637,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3668,24 +3664,24 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.441198</v>
+        <v>-58.460356</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.605341</v>
+        <v>-34.630793</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3697,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3727,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3754,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.418108</v>
+        <v>-58.389676</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.62564</v>
+        <v>-34.618127</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3771,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3783,7 +3779,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3793,12 +3789,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3813,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3840,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.433855</v>
+        <v>-58.418108</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.614487</v>
+        <v>-34.62564</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3857,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3869,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3899,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3926,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.389676</v>
+        <v>-58.433855</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.618127</v>
+        <v>-34.614487</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3943,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3955,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3985,7 +3981,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4012,24 +4008,24 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.460356</v>
+        <v>-58.441198</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.630793</v>
+        <v>-34.605341</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4041,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4071,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4086,7 +4082,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4098,10 +4094,10 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.364132</v>
+        <v>-58.439239</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.628423</v>
+        <v>-34.6604</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4115,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4127,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4157,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4184,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.48121</v>
+        <v>-58.388529</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.61126</v>
+        <v>-34.655949</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4213,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4243,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4258,7 +4254,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4270,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.440031</v>
+        <v>-58.491325</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.575409</v>
+        <v>-34.647761</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4299,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4329,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4356,10 +4352,10 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.413563</v>
+        <v>-58.469394</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.624645</v>
+        <v>-34.626925</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4373,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4385,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4415,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4430,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4442,14 +4438,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.439164</v>
+        <v>-58.390974</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.597069</v>
+        <v>-34.594177</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4459,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4471,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4501,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4521,17 +4517,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.417634</v>
+        <v>-58.430396</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.587439</v>
+        <v>-34.599668</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4545,7 +4541,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4557,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4587,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4614,10 +4610,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.418542</v>
+        <v>-58.459955</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.624609</v>
+        <v>-34.631973</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4631,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4643,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4673,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4700,51 +4696,51 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.430613</v>
+        <v>-58.48802</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.608805</v>
+        <v>-34.641075</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4759,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4786,24 +4782,24 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.50161</v>
+        <v>-58.463198</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.647648</v>
+        <v>-34.62624</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4815,22 +4811,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4845,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4872,51 +4868,47 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.416237</v>
+        <v>-58.471183</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.65477</v>
+        <v>-34.638988</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PPT-H</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4931,12 +4923,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4951,21 +4943,21 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.435731</v>
+        <v>-58.46357</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.597659</v>
+        <v>-34.623187</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4975,7 +4967,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4987,22 +4979,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5017,12 +5009,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5037,31 +5029,31 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.411426</v>
+        <v>-58.45732</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.633266</v>
+        <v>-34.581366</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5073,17 +5065,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5103,12 +5095,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5130,10 +5122,10 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.458516</v>
+        <v>-58.459547</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.646422</v>
+        <v>-34.626309</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5147,7 +5139,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5159,22 +5151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5189,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5216,14 +5208,14 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.374086</v>
+        <v>-58.465166</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.633168</v>
+        <v>-34.670435</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5233,34 +5225,34 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5275,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5302,14 +5294,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.46138</v>
+        <v>-58.438399</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.629774</v>
+        <v>-34.663958</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5319,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5331,22 +5323,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5361,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5388,14 +5380,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.384406</v>
+        <v>-58.475565</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.622932</v>
+        <v>-34.660488</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5405,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5417,22 +5409,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5447,17 +5439,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5467,21 +5459,21 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.409278</v>
+        <v>-58.460855</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.653566</v>
+        <v>-34.631046</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5491,7 +5483,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5503,22 +5495,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5533,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5560,14 +5552,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.399262</v>
+        <v>-58.479751</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.639685</v>
+        <v>-34.677211</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5577,7 +5569,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5589,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5619,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5646,14 +5638,14 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.458298</v>
+        <v>-58.491573</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.566511</v>
+        <v>-34.639215</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5663,34 +5655,34 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5705,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Desmontar PRFV 400</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5720,7 +5712,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5732,51 +5724,51 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.401624</v>
+        <v>-58.487715</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.612001</v>
+        <v>-34.636671</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5791,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5818,51 +5810,51 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.425478</v>
+        <v>-58.488539</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.601865</v>
+        <v>-34.640962</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5877,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5897,21 +5889,21 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.477944</v>
+        <v>-58.423058</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.675149</v>
+        <v>-34.608916</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5921,7 +5913,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5933,22 +5925,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5963,17 +5955,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5983,31 +5975,31 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.483927</v>
+        <v>-58.481162</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.570689</v>
+        <v>-34.665875</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6019,22 +6011,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6049,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6064,7 +6056,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6076,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.395063</v>
+        <v>-58.413945</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.606257</v>
+        <v>-34.582774</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6093,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6105,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6135,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6162,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.372751</v>
+        <v>-58.437739</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.631917</v>
+        <v>-34.638224</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6179,34 +6171,34 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4/22/2025</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MONTES DE OCA, MANUEL AV. 511</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6221,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>804876051</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pegar los ductos al prfv</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6241,58 +6233,58 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.375515</v>
+        <v>-58.494814</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.634393</v>
+        <v>-34.601905</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4/8/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SARMIENTO 4290</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6307,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>804569065</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Columna corroída en su base entro tambien como caso 7049</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6334,14 +6326,14 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.425764</v>
+        <v>-58.469878</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.604359</v>
+        <v>-34.626919</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6351,7 +6343,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ALM-L</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6363,22 +6355,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3/18/2025</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TREINTA Y TRES ORIENTALES 965</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6393,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>804161231</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6420,10 +6412,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.423042</v>
+        <v>-58.46026</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.625868</v>
+        <v>-34.640706</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6437,7 +6429,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6449,22 +6441,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1/30/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RONDEAU 2775</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6479,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>802988219</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Relevar</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6494,7 +6486,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6506,14 +6498,14 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.402062</v>
+        <v>-58.480708</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.635143</v>
+        <v>-34.667639</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6523,7 +6515,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6535,22 +6527,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1/24/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BRASIL 2561</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6565,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>802871857</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Colocar columna R400 - Fuente Teco</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6580,7 +6572,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6592,51 +6584,51 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.400156</v>
+        <v>-58.488539</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.631369</v>
+        <v>-34.640962</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1/14/2025</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Campana	534</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6651,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>802657454</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6678,10 +6670,10 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.477376</v>
+        <v>-58.474151</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.626126</v>
+        <v>-34.630046</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6707,22 +6699,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12/19/2024</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LORA, FELIX 27</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6737,12 +6729,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>801768138</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Traspaso de redes y retiro de columna TLC ya traspaso el nodo</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6752,22 +6744,22 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nodo TLC</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.443626</v>
+        <v>-58.464382</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.621032</v>
+        <v>-34.683083</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6781,7 +6773,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PCH-G</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6793,22 +6785,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11/5/2024</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GODOY CRUZ 2604</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6823,41 +6815,41 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>799246642</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Realizar traspasos y retiro de columna vieja</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.426169</v>
+        <v>-58.464205</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.579697</v>
+        <v>-34.636221</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -6867,34 +6859,30 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>VCR-N</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10/29/2024</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ESTADO DE ISRAEL AV. 4819</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6909,17 +6897,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>798894281</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Inclinado</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6936,24 +6924,24 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.432085</v>
+        <v>-58.517269</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.60178</v>
+        <v>-34.639879</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6965,17 +6953,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10/29/2024</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HERRERA 402</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6995,17 +6983,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>798894295</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Inclinado En el form cargaron foto de otro caso</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7015,21 +7003,21 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.378613</v>
+        <v>-58.423086</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.6349</v>
+        <v>-34.641356</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7039,10 +7027,96 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>-774</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CASEROS AV. 4131</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>mover a 4111</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-58.422741</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-34.639999</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,22 +1371,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5/4/2025</t>
+          <t>5/19/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AZARA 15</t>
+          <t>AYACUCHO 267</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>805655333</t>
+          <t>806926385</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Picada entro tambien como reclamo 7611</t>
+          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1428,14 +1428,14 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.372751</v>
+        <v>-58.395063</v>
       </c>
       <c r="N12" t="n">
-        <v>-34.631917</v>
+        <v>-34.606257</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1445,34 +1445,34 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5/19/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AYACUCHO 267</t>
+          <t>ALVAREZ THOMAS AV. 3305</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1487,51 +1487,51 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>806926385</t>
+          <t>807044131</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Colocar columna y dar aviso para traspaso de nodo teco</t>
+          <t>Columna inclinada</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>-58.395063</v>
+        <v>-58.483927</v>
       </c>
       <c r="N13" t="n">
-        <v>-34.606257</v>
+        <v>-34.570689</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>PUE-E</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1543,22 +1543,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>6/2/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALVAREZ THOMAS AV. 3305</t>
+          <t>MURGUIONDO 3990</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1573,17 +1573,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>807044131</t>
+          <t>807129347</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Columna inclinada</t>
+          <t>COLUMNA INCLINADA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1600,24 +1600,24 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.483927</v>
+        <v>-58.477944</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.570689</v>
+        <v>-34.675149</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>PUE-E</t>
+          <t>PAV-V</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1629,22 +1629,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6/2/2025</t>
+          <t>6/5/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MURGUIONDO 3990</t>
+          <t>ESTADO DE PALESTINA 771</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>807129347</t>
+          <t>807215458</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>COLUMNA INCLINADA</t>
+          <t>Picada y mal ubicada ver con Pedro</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1679,21 +1679,21 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>-58.477944</v>
+        <v>-58.425478</v>
       </c>
       <c r="N15" t="n">
-        <v>-34.675149</v>
+        <v>-34.601865</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PAV-V</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1715,22 +1715,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6/5/2025</t>
+          <t>6/9/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 771</t>
+          <t>ALBERTI 191</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>807215458</t>
+          <t>810533286</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Picada y mal ubicada ver con Pedro</t>
+          <t>Desmontar PRFV 400</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-58.425478</v>
+        <v>-58.401624</v>
       </c>
       <c r="N16" t="n">
-        <v>-34.601865</v>
+        <v>-34.612001</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>CEN-G</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1801,22 +1801,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6/9/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALBERTI 191</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>810533286</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Desmontar PRFV 400</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1858,24 +1858,24 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.401624</v>
+        <v>-58.458298</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.612001</v>
+        <v>-34.566511</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CEN-G</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1887,27 +1887,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3100</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pendiente de Transito</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1917,17 +1917,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ICD30340076</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>QAP fotos del gcba tenia las incorrectas</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1941,27 +1941,27 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.512533</v>
+        <v>-58.409278</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.579243</v>
+        <v>-34.653566</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1973,22 +1973,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2030,24 +2030,24 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.458298</v>
+        <v>-58.399262</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.566511</v>
+        <v>-34.639685</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2059,22 +2059,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.409278</v>
+        <v>-58.384406</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.653566</v>
+        <v>-34.622932</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2145,22 +2145,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2202,14 +2202,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.399262</v>
+        <v>-58.46138</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.639685</v>
+        <v>-34.629774</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2288,14 +2288,14 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.384406</v>
+        <v>-58.458516</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.622932</v>
+        <v>-34.646422</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,22 +2317,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2374,14 +2374,14 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.46138</v>
+        <v>-58.374086</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.629774</v>
+        <v>-34.633168</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2391,34 +2391,34 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2460,14 +2460,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.458516</v>
+        <v>-58.416237</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.646422</v>
+        <v>-34.65477</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,22 +2489,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2546,10 +2546,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.374086</v>
+        <v>-58.411426</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.633168</v>
+        <v>-34.633266</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,19 +2563,19 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2625,21 +2625,21 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.416237</v>
+        <v>-58.435731</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.65477</v>
+        <v>-34.597659</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2661,17 +2661,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2718,14 +2718,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.411426</v>
+        <v>-58.418542</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.633266</v>
+        <v>-34.624609</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2747,22 +2747,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2797,21 +2797,21 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.435731</v>
+        <v>-58.430613</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.597659</v>
+        <v>-34.608805</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,7 +2833,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2890,24 +2890,24 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.418542</v>
+        <v>-58.50161</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.624609</v>
+        <v>-34.647648</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2976,14 +2976,14 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.430613</v>
+        <v>-58.439164</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.608805</v>
+        <v>-34.597069</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3062,24 +3062,24 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.50161</v>
+        <v>-58.417634</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.647648</v>
+        <v>-34.587439</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,22 +3091,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3148,24 +3148,24 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.439164</v>
+        <v>-58.48121</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.597069</v>
+        <v>-34.61126</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,17 +3177,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.417634</v>
+        <v>-58.440031</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.587439</v>
+        <v>-34.575409</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3320,24 +3320,24 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.48121</v>
+        <v>-58.413563</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.61126</v>
+        <v>-34.624645</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3406,14 +3406,14 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.440031</v>
+        <v>-58.364132</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.575409</v>
+        <v>-34.628423</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3492,10 +3492,10 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.413563</v>
+        <v>-58.460356</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.624645</v>
+        <v>-34.630793</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,22 +3521,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.364132</v>
+        <v>-58.389676</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.628423</v>
+        <v>-34.618127</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3664,10 +3664,10 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.460356</v>
+        <v>-58.418108</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.630793</v>
+        <v>-34.62564</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.389676</v>
+        <v>-58.433855</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.618127</v>
+        <v>-34.614487</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3836,24 +3836,24 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.418108</v>
+        <v>-58.441198</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.62564</v>
+        <v>-34.605341</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.433855</v>
+        <v>-58.439239</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.614487</v>
+        <v>-34.6604</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,24 +4008,24 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.441198</v>
+        <v>-58.388529</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.605341</v>
+        <v>-34.655949</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,24 +4094,24 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.439239</v>
+        <v>-58.491325</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.6604</v>
+        <v>-34.647761</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,14 +4180,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.388529</v>
+        <v>-58.469394</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.655949</v>
+        <v>-34.626925</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4266,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.491325</v>
+        <v>-58.390974</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.647761</v>
+        <v>-34.594177</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4345,21 +4345,21 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.469394</v>
+        <v>-58.430396</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.626925</v>
+        <v>-34.599668</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4438,14 +4438,14 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.390974</v>
+        <v>-58.459955</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.594177</v>
+        <v>-34.631973</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4517,53 +4517,53 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.430396</v>
+        <v>-58.48802</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.599668</v>
+        <v>-34.641075</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4610,10 +4610,10 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.459955</v>
+        <v>-58.463198</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.631973</v>
+        <v>-34.62624</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4696,10 +4696,10 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.48802</v>
+        <v>-58.471183</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.641075</v>
+        <v>-34.638988</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4713,29 +4713,25 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PCH-S</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4755,12 +4751,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4782,10 +4778,10 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.463198</v>
+        <v>-58.46357</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.62624</v>
+        <v>-34.623187</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4811,22 +4807,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4837,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4861,21 +4857,21 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.471183</v>
+        <v>-58.45732</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.638988</v>
+        <v>-34.581366</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4885,25 +4881,29 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
+          <t>ATH-N</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4950,10 +4950,10 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.46357</v>
+        <v>-58.459547</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.623187</v>
+        <v>-34.626309</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4979,22 +4979,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5029,31 +5029,31 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.45732</v>
+        <v>-58.465166</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.581366</v>
+        <v>-34.670435</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5065,22 +5065,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5122,14 +5122,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.459547</v>
+        <v>-58.438399</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.626309</v>
+        <v>-34.663958</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5151,17 +5151,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5208,10 +5208,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.465166</v>
+        <v>-58.475565</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.670435</v>
+        <v>-34.660488</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5294,14 +5294,14 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.438399</v>
+        <v>-58.460855</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.663958</v>
+        <v>-34.631046</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,17 +5323,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.475565</v>
+        <v>-58.479751</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.660488</v>
+        <v>-34.677211</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,22 +5409,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,36 +5466,36 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.460855</v>
+        <v>-58.491573</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.631046</v>
+        <v>-34.639215</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5552,36 +5552,36 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.479751</v>
+        <v>-58.487715</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.677211</v>
+        <v>-34.636671</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626837</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.491573</v>
+        <v>-58.488539</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.639215</v>
+        <v>-34.640962</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5667,22 +5667,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,51 +5724,51 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.487715</v>
+        <v>-58.423058</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.636671</v>
+        <v>-34.608916</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,51 +5810,51 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.488539</v>
+        <v>-58.481162</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.640962</v>
+        <v>-34.665875</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,14 +5896,14 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.423058</v>
+        <v>-58.413945</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.608916</v>
+        <v>-34.582774</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5925,22 +5925,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5982,10 +5982,10 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.481162</v>
+        <v>-58.437739</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.665875</v>
+        <v>-34.638224</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,7 +6011,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6061,31 +6061,31 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.413945</v>
+        <v>-58.494814</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.582774</v>
+        <v>-34.601905</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,17 +6097,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,10 +6154,10 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.437739</v>
+        <v>-58.469878</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.638224</v>
+        <v>-34.626919</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,22 +6183,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6233,31 +6233,31 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.494814</v>
+        <v>-58.46026</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.601905</v>
+        <v>-34.640706</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6326,10 +6326,10 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.469878</v>
+        <v>-58.480708</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.626919</v>
+        <v>-34.667639</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t xml:space="preserve">ZELADA 4401 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440296</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6412,36 +6412,36 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.46026</v>
+        <v>-58.488539</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.640706</v>
+        <v>-34.640962</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6498,36 +6498,36 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.480708</v>
+        <v>-58.474151</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.667639</v>
+        <v>-34.630046</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>812440296</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6572,58 +6572,58 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.488539</v>
+        <v>-58.464382</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.640962</v>
+        <v>-34.683083</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6670,51 +6670,47 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.474151</v>
+        <v>-58.464205</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.630046</v>
+        <v>-34.636221</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NRA-R</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2NRA</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6734,7 +6730,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6744,7 +6740,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6756,24 +6752,24 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.464382</v>
+        <v>-58.517269</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.683083</v>
+        <v>-34.639879</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6785,22 +6781,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6820,7 +6816,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6830,7 +6826,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6842,10 +6838,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.464205</v>
+        <v>-58.423086</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.636221</v>
+        <v>-34.641356</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6859,15 +6855,19 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6917,31 +6917,31 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.517269</v>
+        <v>-58.422741</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.639879</v>
+        <v>-34.639999</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PAV-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,17 +6953,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>JUJUY AV 1717</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6981,14 +6981,10 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7010,14 +7006,14 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.423086</v>
+        <v>-58.400922</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.641356</v>
+        <v>-34.630312</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7027,96 +7023,10 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>-774</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3/9/2026</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>CASEROS AV. 4131</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>mover a 4111</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="n">
-        <v>-58.422741</v>
-      </c>
-      <c r="N78" t="n">
-        <v>-34.639999</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Boedo</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Capital Sur</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>PPT-L</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,22 +1801,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1858,24 +1858,24 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.458298</v>
+        <v>-58.394543</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.566511</v>
+        <v>-34.620732</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1887,22 +1887,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1917,17 +1917,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1937,31 +1937,31 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.409278</v>
+        <v>-58.458298</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.653566</v>
+        <v>-34.566511</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2023,17 +2023,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.399262</v>
+        <v>-58.409278</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.639685</v>
+        <v>-34.653566</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2059,22 +2059,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2116,10 +2116,10 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.384406</v>
+        <v>-58.399262</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.622932</v>
+        <v>-34.639685</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2145,22 +2145,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2202,14 +2202,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.46138</v>
+        <v>-58.429159</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.629774</v>
+        <v>-34.577821</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>DIAZ, CESAR, GRAL. 1657</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>ICD31468700</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2288,24 +2288,24 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.458516</v>
+        <v>-58.463851</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.646422</v>
+        <v>-34.606961</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,22 +2317,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2374,10 +2374,10 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.374086</v>
+        <v>-58.384406</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.633168</v>
+        <v>-34.622932</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2391,34 +2391,34 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2460,14 +2460,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.416237</v>
+        <v>-58.46138</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.65477</v>
+        <v>-34.629774</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,22 +2489,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2546,14 +2546,14 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.411426</v>
+        <v>-58.458516</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.633266</v>
+        <v>-34.646422</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2575,22 +2575,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2625,21 +2625,21 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.435731</v>
+        <v>-58.374086</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.597659</v>
+        <v>-34.633168</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2649,34 +2649,34 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2718,14 +2718,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.418542</v>
+        <v>-58.416237</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.624609</v>
+        <v>-34.65477</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2747,22 +2747,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2804,14 +2804,14 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.430613</v>
+        <v>-58.411426</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.608805</v>
+        <v>-34.633266</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,22 +2833,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2878,36 +2878,36 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.50161</v>
+        <v>-58.435731</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.647648</v>
+        <v>-34.597659</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2976,14 +2976,14 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.439164</v>
+        <v>-58.418542</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.597069</v>
+        <v>-34.624609</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3062,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.417634</v>
+        <v>-58.430613</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.587439</v>
+        <v>-34.608805</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,22 +3091,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3148,14 +3148,14 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.48121</v>
+        <v>-58.50161</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.61126</v>
+        <v>-34.647648</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.440031</v>
+        <v>-58.439164</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.575409</v>
+        <v>-34.597069</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3320,14 +3320,14 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.413563</v>
+        <v>-58.417634</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.624645</v>
+        <v>-34.587439</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3406,24 +3406,24 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.364132</v>
+        <v>-58.48121</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.628423</v>
+        <v>-34.61126</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3492,14 +3492,14 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.460356</v>
+        <v>-58.440031</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.630793</v>
+        <v>-34.575409</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,22 +3521,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3578,14 +3578,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.389676</v>
+        <v>-58.413563</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.618127</v>
+        <v>-34.624645</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.418108</v>
+        <v>-58.364132</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.62564</v>
+        <v>-34.628423</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.433855</v>
+        <v>-58.460356</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.614487</v>
+        <v>-34.630793</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3836,24 +3836,24 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.441198</v>
+        <v>-58.389676</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.605341</v>
+        <v>-34.618127</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.439239</v>
+        <v>-58.418108</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.6604</v>
+        <v>-34.62564</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.388529</v>
+        <v>-58.433855</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.655949</v>
+        <v>-34.614487</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,14 +4094,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.491325</v>
+        <v>-58.441198</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.647761</v>
+        <v>-34.605341</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,14 +4180,14 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.469394</v>
+        <v>-58.439239</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.626925</v>
+        <v>-34.6604</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4266,14 +4266,14 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.390974</v>
+        <v>-58.388529</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.594177</v>
+        <v>-34.655949</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4345,31 +4345,31 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.430396</v>
+        <v>-58.491325</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.599668</v>
+        <v>-34.647761</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,17 +4381,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4438,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.459955</v>
+        <v>-58.469394</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.631973</v>
+        <v>-34.626925</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4524,51 +4524,51 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.48802</v>
+        <v>-58.390974</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.641075</v>
+        <v>-34.594177</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4603,21 +4603,21 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.463198</v>
+        <v>-58.430396</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.62624</v>
+        <v>-34.599668</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4696,47 +4696,51 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.471183</v>
+        <v>-58.459955</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.638988</v>
+        <v>-34.631973</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+          <t>PCH-F</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4751,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4778,51 +4782,51 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.46357</v>
+        <v>-58.48802</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.623187</v>
+        <v>-34.641075</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4837,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4857,31 +4861,31 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.45732</v>
+        <v>-58.463198</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.581366</v>
+        <v>-34.62624</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4893,22 +4897,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4923,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4938,7 +4942,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4950,14 +4954,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.459547</v>
+        <v>-58.402154</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.626309</v>
+        <v>-34.605295</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4967,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4979,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5009,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5036,51 +5040,47 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.465166</v>
+        <v>-58.471183</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.670435</v>
+        <v>-34.638988</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PAV-?</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5122,14 +5122,14 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.438399</v>
+        <v>-58.46357</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.663958</v>
+        <v>-34.623187</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5151,22 +5151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5201,31 +5201,31 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.475565</v>
+        <v>-58.45732</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.660488</v>
+        <v>-34.581366</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,17 +5237,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5294,10 +5294,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.460855</v>
+        <v>-58.459547</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.631046</v>
+        <v>-34.626309</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,17 +5323,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.479751</v>
+        <v>-58.465166</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.677211</v>
+        <v>-34.670435</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,22 +5409,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,51 +5466,51 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.491573</v>
+        <v>-58.438399</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.639215</v>
+        <v>-34.663958</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5552,51 +5552,51 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.487715</v>
+        <v>-58.475565</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.636671</v>
+        <v>-34.660488</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626837</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,51 +5638,51 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.488539</v>
+        <v>-58.460855</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.640962</v>
+        <v>-34.631046</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5724,14 +5724,14 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.423058</v>
+        <v>-58.479751</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.608916</v>
+        <v>-34.677211</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5753,22 +5753,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,51 +5810,51 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.481162</v>
+        <v>-58.491573</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.665875</v>
+        <v>-34.639215</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,51 +5896,51 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.413945</v>
+        <v>-58.487715</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.582774</v>
+        <v>-34.636671</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,14 +5982,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.437739</v>
+        <v>-58.423058</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.638224</v>
+        <v>-34.608916</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,22 +6011,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6061,31 +6061,31 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.494814</v>
+        <v>-58.481162</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.601905</v>
+        <v>-34.665875</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.469878</v>
+        <v>-58.413945</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.626919</v>
+        <v>-34.582774</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,17 +6183,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6240,10 +6240,10 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.46026</v>
+        <v>-58.437739</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.640706</v>
+        <v>-34.638224</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,22 +6269,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6319,31 +6319,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.480708</v>
+        <v>-58.494814</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.667639</v>
+        <v>-34.601905</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,7 +6355,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZELADA 4401 </t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812440296</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6412,46 +6412,46 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.488539</v>
+        <v>-58.469878</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.640962</v>
+        <v>-34.626919</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,36 +6498,36 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.474151</v>
+        <v>-58.46026</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.630046</v>
+        <v>-34.640706</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6572,22 +6572,22 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.464382</v>
+        <v>-58.480708</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.683083</v>
+        <v>-34.667639</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6613,17 +6613,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6670,47 +6670,51 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.464205</v>
+        <v>-58.474151</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.636221</v>
+        <v>-34.630046</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
+          <t>NRA-R</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2NRA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6730,7 +6734,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6740,7 +6744,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6752,24 +6756,24 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.517269</v>
+        <v>-58.464382</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.639879</v>
+        <v>-34.683083</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PAV-B</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -6781,22 +6785,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6816,7 +6820,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6826,7 +6830,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6838,10 +6842,10 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.423086</v>
+        <v>-58.464205</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.641356</v>
+        <v>-34.636221</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6855,19 +6859,15 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PPT-L</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6917,31 +6917,31 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.422741</v>
+        <v>-58.517269</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.639999</v>
+        <v>-34.639879</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,82 +6953,418 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>-772</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LA PLATA AV. 2304</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Desplazar Columna</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-58.423086</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-34.641356</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>-774</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3/9/2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CASEROS AV. 4131</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>mover a 4111</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-58.422741</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-34.639999</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>8597</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>3/13/2026</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>JUJUY AV 1717</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
         <is>
           <t>Cambiar Columna</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" t="n">
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
         <v>-58.400922</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N79" t="n">
         <v>-34.630312</v>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>San Telmo</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>PPT-F</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7460 </t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TERRADA 2720</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>RIENDA A PIQUE CORTADA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-58.486103</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-34.603895</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>NRA-P</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00000609</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ZELADA 4402</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-58.48834</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-34.641018</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>PCH-S</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,27 +1801,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>5/27/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>ALBARELLOS AV. 3100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Transito</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>ICD30340076</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>QAP fotos del gcba tenia las incorrectas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Tensor</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1851,31 +1851,31 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.394543</v>
+        <v>-58.512533</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.620732</v>
+        <v>-34.579243</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>PUE-J</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1887,22 +1887,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1944,24 +1944,24 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.458298</v>
+        <v>-58.394543</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.566511</v>
+        <v>-34.620732</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1973,22 +1973,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2023,31 +2023,31 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.409278</v>
+        <v>-58.458298</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.653566</v>
+        <v>-34.566511</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.399262</v>
+        <v>-58.409278</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.639685</v>
+        <v>-34.653566</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2145,22 +2145,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2202,14 +2202,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.429159</v>
+        <v>-58.399262</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.577821</v>
+        <v>-34.639685</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1657</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ICD31468700</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2288,24 +2288,24 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.463851</v>
+        <v>-58.429159</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.606961</v>
+        <v>-34.577821</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,7 +2317,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>DIAZ, CESAR, GRAL. 1657</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>ICD31468700</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2374,24 +2374,24 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.384406</v>
+        <v>-58.463851</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.622932</v>
+        <v>-34.606961</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2403,22 +2403,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2460,14 +2460,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.46138</v>
+        <v>-58.384406</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.629774</v>
+        <v>-34.622932</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,17 +2489,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2546,10 +2546,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.458516</v>
+        <v>-58.46138</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.646422</v>
+        <v>-34.629774</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2632,14 +2632,14 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.374086</v>
+        <v>-58.458516</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.633168</v>
+        <v>-34.646422</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2649,29 +2649,29 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2718,10 +2718,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.416237</v>
+        <v>-58.374086</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.65477</v>
+        <v>-34.633168</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2735,34 +2735,34 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2804,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.411426</v>
+        <v>-58.416237</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.633266</v>
+        <v>-34.65477</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,22 +2833,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2883,21 +2883,21 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.435731</v>
+        <v>-58.411426</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.597659</v>
+        <v>-34.633266</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2969,21 +2969,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.418542</v>
+        <v>-58.435731</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.624609</v>
+        <v>-34.597659</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3062,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.430613</v>
+        <v>-58.418542</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.608805</v>
+        <v>-34.624609</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3148,24 +3148,24 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.50161</v>
+        <v>-58.430613</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.647648</v>
+        <v>-34.608805</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,24 +3234,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.439164</v>
+        <v>-58.50161</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.597069</v>
+        <v>-34.647648</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3320,10 +3320,10 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.417634</v>
+        <v>-58.439164</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.587439</v>
+        <v>-34.597069</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3406,24 +3406,24 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.48121</v>
+        <v>-58.417634</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.61126</v>
+        <v>-34.587439</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3492,24 +3492,24 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.440031</v>
+        <v>-58.48121</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.575409</v>
+        <v>-34.61126</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,14 +3578,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.413563</v>
+        <v>-58.440031</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.624645</v>
+        <v>-34.575409</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.364132</v>
+        <v>-58.413563</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.628423</v>
+        <v>-34.624645</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.460356</v>
+        <v>-58.364132</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.630793</v>
+        <v>-34.628423</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3836,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.389676</v>
+        <v>-58.460356</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.618127</v>
+        <v>-34.630793</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.418108</v>
+        <v>-58.389676</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.62564</v>
+        <v>-34.618127</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.433855</v>
+        <v>-58.418108</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.614487</v>
+        <v>-34.62564</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,24 +4094,24 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.441198</v>
+        <v>-58.433855</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.605341</v>
+        <v>-34.614487</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.439239</v>
+        <v>-58.441198</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.6604</v>
+        <v>-34.605341</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4266,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.388529</v>
+        <v>-58.439239</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.655949</v>
+        <v>-34.6604</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,24 +4352,24 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.491325</v>
+        <v>-58.388529</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.647761</v>
+        <v>-34.655949</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4438,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.469394</v>
+        <v>-58.491325</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.626925</v>
+        <v>-34.647761</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4524,14 +4524,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.390974</v>
+        <v>-58.469394</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.594177</v>
+        <v>-34.626925</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4598,26 +4598,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.430396</v>
+        <v>-58.390974</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.599668</v>
+        <v>-34.594177</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4689,21 +4689,21 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.459955</v>
+        <v>-58.430396</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.631973</v>
+        <v>-34.599668</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,22 +4725,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4782,51 +4782,51 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.48802</v>
+        <v>-58.459955</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.641075</v>
+        <v>-34.631973</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,51 +4868,51 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.463198</v>
+        <v>-58.48802</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.62624</v>
+        <v>-34.641075</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4954,14 +4954,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.402154</v>
+        <v>-58.463198</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.605295</v>
+        <v>-34.62624</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,47 +5040,51 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.471183</v>
+        <v>-58.402154</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.638988</v>
+        <v>-34.605295</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
+          <t>CLI-D</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5095,7 +5099,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5122,51 +5126,47 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.46357</v>
+        <v>-58.471183</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.623187</v>
+        <v>-34.638988</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>NRA-E</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5201,31 +5201,31 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.45732</v>
+        <v>-58.46357</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.581366</v>
+        <v>-34.623187</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5287,31 +5287,31 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.459547</v>
+        <v>-58.45732</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.626309</v>
+        <v>-34.581366</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,22 +5323,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.465166</v>
+        <v>-58.459547</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.670435</v>
+        <v>-34.626309</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,17 +5409,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,14 +5466,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.438399</v>
+        <v>-58.465166</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.663958</v>
+        <v>-34.670435</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5552,14 +5552,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.475565</v>
+        <v>-58.438399</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.660488</v>
+        <v>-34.663958</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5581,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.460855</v>
+        <v>-58.475565</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.631046</v>
+        <v>-34.660488</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5667,22 +5667,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,10 +5724,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.479751</v>
+        <v>-58.460855</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.677211</v>
+        <v>-34.631046</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,36 +5810,36 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.491573</v>
+        <v>-58.479751</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.639215</v>
+        <v>-34.677211</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,10 +5896,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.487715</v>
+        <v>-58.491573</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.636671</v>
+        <v>-34.639215</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5925,22 +5925,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,51 +5982,51 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.423058</v>
+        <v>-58.487715</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.608916</v>
+        <v>-34.636671</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.481162</v>
+        <v>-58.423058</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.665875</v>
+        <v>-34.608916</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.413945</v>
+        <v>-58.481162</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.582774</v>
+        <v>-34.665875</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6240,14 +6240,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.437739</v>
+        <v>-58.413945</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.638224</v>
+        <v>-34.582774</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6319,31 +6319,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.494814</v>
+        <v>-58.437739</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.601905</v>
+        <v>-34.638224</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6405,31 +6405,31 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.469878</v>
+        <v>-58.494814</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.626919</v>
+        <v>-34.601905</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6441,17 +6441,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.46026</v>
+        <v>-58.469878</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.640706</v>
+        <v>-34.626919</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6527,22 +6527,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6584,10 +6584,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.480708</v>
+        <v>-58.46026</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.667639</v>
+        <v>-34.640706</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6670,36 +6670,36 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.474151</v>
+        <v>-58.480708</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.630046</v>
+        <v>-34.667639</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6744,63 +6744,63 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.464382</v>
+        <v>-58.474151</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.683083</v>
+        <v>-34.630046</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6835,17 +6835,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.464205</v>
+        <v>-58.464382</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.636221</v>
+        <v>-34.683083</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6859,30 +6859,34 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+          <t>PAV-U</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6902,7 +6906,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6912,63 +6916,59 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.517269</v>
+        <v>-58.464205</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.639879</v>
+        <v>-34.636221</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PAV-B</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7003,31 +7003,31 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.423086</v>
+        <v>-58.517269</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.641356</v>
+        <v>-34.639879</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7096,10 +7096,10 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.422741</v>
+        <v>-58.423086</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.639999</v>
+        <v>-34.641356</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7125,22 +7125,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JUJUY AV 1717</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7153,10 +7153,14 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7178,14 +7182,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.400922</v>
+        <v>-58.422741</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.630312</v>
+        <v>-34.639999</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7195,7 +7199,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7207,22 +7211,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7460 </t>
+          <t>8597</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TERRADA 2720</t>
+          <t>JUJUY AV 1717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7238,12 +7242,12 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>RIENDA A PIQUE CORTADA</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7253,31 +7257,31 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.486103</v>
+        <v>-58.400922</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.603895</v>
+        <v>-34.630312</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7289,7 +7293,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t xml:space="preserve">7460 </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7299,12 +7303,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>TERRADA 2720</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7320,49 +7324,131 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
+          <t>RIENDA A PIQUE CORTADA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-58.486103</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-34.603895</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>NRA-P</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00000609</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ZELADA 4402</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" t="n">
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
         <v>-58.48834</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N82" t="n">
         <v>-34.641018</v>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Devoto</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>PCH-S</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>ARATO-25058.PO.2PCH</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -1801,27 +1801,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5/27/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALBARELLOS AV. 3100</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pendiente de Transito</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ICD30340076</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>QAP fotos del gcba tenia las incorrectas</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1851,31 +1851,31 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.512533</v>
+        <v>-58.394543</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.579243</v>
+        <v>-34.620732</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>PUE-J</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1887,22 +1887,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1944,24 +1944,24 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.394543</v>
+        <v>-58.458298</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.620732</v>
+        <v>-34.566511</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1973,22 +1973,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2023,31 +2023,31 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.458298</v>
+        <v>-58.409278</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.566511</v>
+        <v>-34.653566</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.409278</v>
+        <v>-58.399262</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.653566</v>
+        <v>-34.639685</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2145,22 +2145,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2202,14 +2202,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.399262</v>
+        <v>-58.429159</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.639685</v>
+        <v>-34.577821</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>DIAZ, CESAR, GRAL. 1657</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>ICD31468700</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2288,24 +2288,24 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.429159</v>
+        <v>-58.463851</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.577821</v>
+        <v>-34.606961</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,7 +2317,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1657</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ICD31468700</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2374,24 +2374,24 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.463851</v>
+        <v>-58.384406</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.606961</v>
+        <v>-34.622932</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2403,22 +2403,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2460,14 +2460,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.384406</v>
+        <v>-58.46138</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.622932</v>
+        <v>-34.629774</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,17 +2489,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2546,10 +2546,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.46138</v>
+        <v>-58.458516</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.629774</v>
+        <v>-34.646422</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2632,14 +2632,14 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.458516</v>
+        <v>-58.374086</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.646422</v>
+        <v>-34.633168</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2649,29 +2649,29 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2718,10 +2718,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.374086</v>
+        <v>-58.416237</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.633168</v>
+        <v>-34.65477</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2735,34 +2735,34 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2804,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.416237</v>
+        <v>-58.411426</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.65477</v>
+        <v>-34.633266</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,22 +2833,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2883,21 +2883,21 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.411426</v>
+        <v>-58.435731</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.633266</v>
+        <v>-34.597659</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2969,21 +2969,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.435731</v>
+        <v>-58.418542</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.597659</v>
+        <v>-34.624609</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3062,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.418542</v>
+        <v>-58.430613</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.624609</v>
+        <v>-34.608805</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3148,24 +3148,24 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.430613</v>
+        <v>-58.50161</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.608805</v>
+        <v>-34.647648</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,24 +3234,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.50161</v>
+        <v>-58.439164</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.647648</v>
+        <v>-34.597069</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3320,10 +3320,10 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.439164</v>
+        <v>-58.417634</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.597069</v>
+        <v>-34.587439</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3406,24 +3406,24 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.417634</v>
+        <v>-58.48121</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.587439</v>
+        <v>-34.61126</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3492,24 +3492,24 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.48121</v>
+        <v>-58.440031</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.61126</v>
+        <v>-34.575409</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,14 +3578,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.440031</v>
+        <v>-58.413563</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.575409</v>
+        <v>-34.624645</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.413563</v>
+        <v>-58.364132</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.624645</v>
+        <v>-34.628423</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.364132</v>
+        <v>-58.460356</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.628423</v>
+        <v>-34.630793</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3836,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.460356</v>
+        <v>-58.389676</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.630793</v>
+        <v>-34.618127</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.389676</v>
+        <v>-58.418108</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.618127</v>
+        <v>-34.62564</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.418108</v>
+        <v>-58.433855</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.62564</v>
+        <v>-34.614487</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,24 +4094,24 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.433855</v>
+        <v>-58.441198</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.614487</v>
+        <v>-34.605341</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.441198</v>
+        <v>-58.439239</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.605341</v>
+        <v>-34.6604</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4266,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.439239</v>
+        <v>-58.388529</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.6604</v>
+        <v>-34.655949</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,24 +4352,24 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.388529</v>
+        <v>-58.491325</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.655949</v>
+        <v>-34.647761</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4438,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.491325</v>
+        <v>-58.469394</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.647761</v>
+        <v>-34.626925</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4524,14 +4524,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.469394</v>
+        <v>-58.390974</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.626925</v>
+        <v>-34.594177</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4598,26 +4598,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.390974</v>
+        <v>-58.430396</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.594177</v>
+        <v>-34.599668</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4689,21 +4689,21 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.430396</v>
+        <v>-58.459955</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.599668</v>
+        <v>-34.631973</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,22 +4725,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4782,51 +4782,51 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.459955</v>
+        <v>-58.48802</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.631973</v>
+        <v>-34.641075</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,51 +4868,51 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.48802</v>
+        <v>-58.463198</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.641075</v>
+        <v>-34.62624</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4954,14 +4954,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.463198</v>
+        <v>-58.402154</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.62624</v>
+        <v>-34.605295</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>CLI-D</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,51 +5040,47 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.402154</v>
+        <v>-58.471183</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.605295</v>
+        <v>-34.638988</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>CLI-D</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,7 +5095,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5126,47 +5122,51 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.471183</v>
+        <v>-58.46357</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.638988</v>
+        <v>-34.623187</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+          <t>NRA-E</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>1/8/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>FOREST AV. 957</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811453824</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5201,31 +5201,31 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.46357</v>
+        <v>-58.45732</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.623187</v>
+        <v>-34.581366</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>ATH-N</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5287,31 +5287,31 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.45732</v>
+        <v>-58.459547</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.581366</v>
+        <v>-34.626309</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,22 +5323,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.459547</v>
+        <v>-58.465166</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.626309</v>
+        <v>-34.670435</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,17 +5409,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,14 +5466,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.465166</v>
+        <v>-58.438399</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.670435</v>
+        <v>-34.663958</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5552,14 +5552,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.438399</v>
+        <v>-58.475565</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.663958</v>
+        <v>-34.660488</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5581,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.475565</v>
+        <v>-58.460855</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.660488</v>
+        <v>-34.631046</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5667,22 +5667,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,10 +5724,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.460855</v>
+        <v>-58.479751</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.631046</v>
+        <v>-34.677211</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,36 +5810,36 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.479751</v>
+        <v>-58.491573</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.677211</v>
+        <v>-34.639215</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,10 +5896,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.491573</v>
+        <v>-58.487715</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.639215</v>
+        <v>-34.636671</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5925,22 +5925,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,51 +5982,51 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.487715</v>
+        <v>-58.423058</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.636671</v>
+        <v>-34.608916</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.423058</v>
+        <v>-58.481162</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.608916</v>
+        <v>-34.665875</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.481162</v>
+        <v>-58.413945</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.665875</v>
+        <v>-34.582774</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6240,14 +6240,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.413945</v>
+        <v>-58.437739</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.582774</v>
+        <v>-34.638224</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6319,31 +6319,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.437739</v>
+        <v>-58.494814</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.638224</v>
+        <v>-34.601905</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6405,31 +6405,31 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.494814</v>
+        <v>-58.469878</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.601905</v>
+        <v>-34.626919</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6441,17 +6441,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.469878</v>
+        <v>-58.46026</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.626919</v>
+        <v>-34.640706</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6527,22 +6527,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6584,10 +6584,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.46026</v>
+        <v>-58.480708</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.640706</v>
+        <v>-34.667639</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6670,36 +6670,36 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.480708</v>
+        <v>-58.474151</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.667639</v>
+        <v>-34.630046</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6744,63 +6744,63 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.474151</v>
+        <v>-58.464382</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.630046</v>
+        <v>-34.683083</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6835,17 +6835,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.464382</v>
+        <v>-58.464205</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.683083</v>
+        <v>-34.636221</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6859,34 +6859,30 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PAV-U</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6906,7 +6902,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6916,59 +6912,63 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.464205</v>
+        <v>-58.517269</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.636221</v>
+        <v>-34.639879</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
+          <t>PAV-B</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7003,31 +7003,31 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.517269</v>
+        <v>-58.423086</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.639879</v>
+        <v>-34.641356</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PAV-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7096,10 +7096,10 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.423086</v>
+        <v>-58.422741</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.641356</v>
+        <v>-34.639999</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7125,22 +7125,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>JUJUY AV 1717</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7153,14 +7153,10 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7182,14 +7178,14 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.422741</v>
+        <v>-58.400922</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.639999</v>
+        <v>-34.630312</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7199,7 +7195,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7211,22 +7207,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t xml:space="preserve">7460 </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JUJUY AV 1717</t>
+          <t>TERRADA 2720</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7242,12 +7238,12 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>RIENDA A PIQUE CORTADA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7257,31 +7253,31 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.400922</v>
+        <v>-58.486103</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.630312</v>
+        <v>-34.603895</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7293,7 +7289,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7460 </t>
+          <t>00000609</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7303,12 +7299,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TERRADA 2720</t>
+          <t>ZELADA 4402</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7324,12 +7320,12 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>RIENDA A PIQUE CORTADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7339,21 +7335,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.486103</v>
+        <v>-58.48834</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.603895</v>
+        <v>-34.641018</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7363,34 +7359,34 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t>R0050</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/25/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>IBERA 3244</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7428,14 +7424,14 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.48834</v>
+        <v>-58.472542</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.641018</v>
+        <v>-34.55798</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -7445,12 +7441,12 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5151,22 +5151,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/8/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FOREST AV. 957</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811453824</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5201,31 +5201,31 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.45732</v>
+        <v>-58.459547</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.581366</v>
+        <v>-34.626309</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ATH-N</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5294,10 +5294,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.459547</v>
+        <v>-58.465166</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.626309</v>
+        <v>-34.670435</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,17 +5323,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,14 +5380,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.465166</v>
+        <v>-58.438399</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.670435</v>
+        <v>-34.663958</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,7 +5409,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,14 +5466,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.438399</v>
+        <v>-58.475565</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.663958</v>
+        <v>-34.660488</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5495,22 +5495,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5552,10 +5552,10 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.475565</v>
+        <v>-58.460855</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.660488</v>
+        <v>-34.631046</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5581,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.460855</v>
+        <v>-58.479751</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.631046</v>
+        <v>-34.677211</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,36 +5724,36 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.479751</v>
+        <v>-58.491573</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.677211</v>
+        <v>-34.639215</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,10 +5810,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.491573</v>
+        <v>-58.487715</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.639215</v>
+        <v>-34.636671</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5839,22 +5839,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,51 +5896,51 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.487715</v>
+        <v>-58.423058</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.636671</v>
+        <v>-34.608916</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,14 +5982,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.423058</v>
+        <v>-58.481162</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.608916</v>
+        <v>-34.665875</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,22 +6011,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.481162</v>
+        <v>-58.413945</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.665875</v>
+        <v>-34.582774</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.413945</v>
+        <v>-58.437739</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.582774</v>
+        <v>-34.638224</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6233,31 +6233,31 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.437739</v>
+        <v>-58.494814</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.638224</v>
+        <v>-34.601905</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,22 +6269,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6319,31 +6319,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.494814</v>
+        <v>-58.469878</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.601905</v>
+        <v>-34.626919</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,17 +6355,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6412,10 +6412,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.469878</v>
+        <v>-58.46026</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.626919</v>
+        <v>-34.640706</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6441,22 +6441,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.46026</v>
+        <v>-58.480708</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.640706</v>
+        <v>-34.667639</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6527,7 +6527,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6584,36 +6584,36 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.480708</v>
+        <v>-58.474151</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.667639</v>
+        <v>-34.630046</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6658,63 +6658,63 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.474151</v>
+        <v>-58.464382</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.630046</v>
+        <v>-34.683083</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.464382</v>
+        <v>-58.464205</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.683083</v>
+        <v>-34.636221</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6773,34 +6773,30 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PAV-U</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6820,7 +6816,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6830,59 +6826,63 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.464205</v>
+        <v>-58.517269</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.636221</v>
+        <v>-34.639879</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+          <t>PAV-B</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6917,31 +6917,31 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.517269</v>
+        <v>-58.423086</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.639879</v>
+        <v>-34.641356</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PAV-B</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,22 +6953,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7010,10 +7010,10 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.423086</v>
+        <v>-58.422741</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.641356</v>
+        <v>-34.639999</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>JUJUY AV 1717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7067,14 +7067,10 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Pendiente ADM</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7096,14 +7092,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.422741</v>
+        <v>-58.400922</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.639999</v>
+        <v>-34.630312</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7113,7 +7109,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7125,22 +7121,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t xml:space="preserve">7460 </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JUJUY AV 1717</t>
+          <t>TERRADA 2720</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7156,12 +7152,12 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>RIENDA A PIQUE CORTADA</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7171,31 +7167,31 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.400922</v>
+        <v>-58.486103</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.630312</v>
+        <v>-34.603895</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7207,7 +7203,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7460 </t>
+          <t>00000609</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7217,12 +7213,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TERRADA 2720</t>
+          <t>ZELADA 4402</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7238,12 +7234,12 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>RIENDA A PIQUE CORTADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7253,21 +7249,21 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.486103</v>
+        <v>-58.48834</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.603895</v>
+        <v>-34.641018</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7277,34 +7273,34 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t>R0050</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/25/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>IBERA 3244</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7342,14 +7338,14 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.48834</v>
+        <v>-58.472542</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.641018</v>
+        <v>-34.55798</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7359,92 +7355,10 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>COG-L</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
-        <is>
-          <t>ARATO-25058.PO.2PCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>R0050</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>3/25/2026</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>IBERA 3244</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" t="n">
-        <v>-58.472542</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-34.55798</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>COG-L</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7203,7 +7203,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t>00201041</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>HABANA 4448</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7234,7 +7234,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7256,14 +7256,14 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.48834</v>
+        <v>-58.518808</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.641018</v>
+        <v>-34.601236</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7273,34 +7273,34 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>R0050</t>
+          <t>00000609</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3/25/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IBERA 3244</t>
+          <t>ZELADA 4402</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7338,27 +7338,109 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
+        <v>-58.48834</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-34.641018</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>PCH-S</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2PCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>R0050</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>3/25/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IBERA 3244</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
         <v>-58.472542</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N82" t="n">
         <v>-34.55798</v>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>COG-L</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,27 +2403,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2460,10 +2460,10 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.46138</v>
+        <v>-58.465176</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.629774</v>
+        <v>-34.680979</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,17 +2489,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2546,10 +2546,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.458516</v>
+        <v>-58.46138</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.646422</v>
+        <v>-34.629774</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2632,14 +2632,14 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.374086</v>
+        <v>-58.458516</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.633168</v>
+        <v>-34.646422</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2649,29 +2649,29 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2718,10 +2718,10 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.416237</v>
+        <v>-58.374086</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.65477</v>
+        <v>-34.633168</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2735,34 +2735,34 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2804,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.411426</v>
+        <v>-58.416237</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.633266</v>
+        <v>-34.65477</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2833,22 +2833,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2883,21 +2883,21 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.435731</v>
+        <v>-58.411426</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.597659</v>
+        <v>-34.633266</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2969,21 +2969,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.418542</v>
+        <v>-58.435731</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.624609</v>
+        <v>-34.597659</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3062,14 +3062,14 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.430613</v>
+        <v>-58.418542</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.608805</v>
+        <v>-34.624609</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3148,24 +3148,24 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.50161</v>
+        <v>-58.430613</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.647648</v>
+        <v>-34.608805</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,22 +3177,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,24 +3234,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.439164</v>
+        <v>-58.50161</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.597069</v>
+        <v>-34.647648</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3320,10 +3320,10 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.417634</v>
+        <v>-58.439164</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.587439</v>
+        <v>-34.597069</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,22 +3349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3406,24 +3406,24 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.48121</v>
+        <v>-58.417634</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.61126</v>
+        <v>-34.587439</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3492,24 +3492,24 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.440031</v>
+        <v>-58.48121</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.575409</v>
+        <v>-34.61126</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,14 +3578,14 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.413563</v>
+        <v>-58.440031</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.624645</v>
+        <v>-34.575409</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,22 +3607,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.364132</v>
+        <v>-58.413563</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.628423</v>
+        <v>-34.624645</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.460356</v>
+        <v>-58.364132</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.630793</v>
+        <v>-34.628423</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3836,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.389676</v>
+        <v>-58.460356</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.618127</v>
+        <v>-34.630793</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.418108</v>
+        <v>-58.389676</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.62564</v>
+        <v>-34.618127</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.433855</v>
+        <v>-58.418108</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.614487</v>
+        <v>-34.62564</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,22 +4037,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,24 +4094,24 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.441198</v>
+        <v>-58.433855</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.605341</v>
+        <v>-34.614487</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.439239</v>
+        <v>-58.441198</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.6604</v>
+        <v>-34.605341</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4266,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.388529</v>
+        <v>-58.439239</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.655949</v>
+        <v>-34.6604</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,22 +4295,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,24 +4352,24 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.491325</v>
+        <v>-58.388529</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.647761</v>
+        <v>-34.655949</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4438,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.469394</v>
+        <v>-58.491325</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.626925</v>
+        <v>-34.647761</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,22 +4467,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4524,14 +4524,14 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.390974</v>
+        <v>-58.469394</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.594177</v>
+        <v>-34.626925</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4598,26 +4598,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.430396</v>
+        <v>-58.390974</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.599668</v>
+        <v>-34.594177</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4689,21 +4689,21 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.459955</v>
+        <v>-58.430396</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.631973</v>
+        <v>-34.599668</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,22 +4725,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4782,51 +4782,51 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.48802</v>
+        <v>-58.459955</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.641075</v>
+        <v>-34.631973</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,51 +4868,51 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.463198</v>
+        <v>-58.48802</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.62624</v>
+        <v>-34.641075</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4954,14 +4954,14 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.402154</v>
+        <v>-58.463198</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.605295</v>
+        <v>-34.62624</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4983,22 +4983,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,47 +5040,51 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.471183</v>
+        <v>-58.402154</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.638988</v>
+        <v>-34.605295</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
+          <t>CLI-D</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5095,7 +5099,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5122,46 +5126,42 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.46357</v>
+        <v>-58.471183</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.623187</v>
+        <v>-34.638988</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>NRA-E</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5208,10 +5208,10 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.459547</v>
+        <v>-58.46357</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.626309</v>
+        <v>-34.623187</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5237,22 +5237,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5294,10 +5294,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.465166</v>
+        <v>-58.459547</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.670435</v>
+        <v>-34.626309</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,17 +5323,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,14 +5380,14 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.438399</v>
+        <v>-58.465166</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.663958</v>
+        <v>-34.670435</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,7 +5409,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,14 +5466,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.475565</v>
+        <v>-58.438399</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.660488</v>
+        <v>-34.663958</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5495,22 +5495,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5552,10 +5552,10 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.460855</v>
+        <v>-58.475565</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.631046</v>
+        <v>-34.660488</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5581,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.479751</v>
+        <v>-58.460855</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.677211</v>
+        <v>-34.631046</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,36 +5724,36 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.491573</v>
+        <v>-58.479751</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.639215</v>
+        <v>-34.677211</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,10 +5810,10 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.487715</v>
+        <v>-58.491573</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.636671</v>
+        <v>-34.639215</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5839,22 +5839,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,51 +5896,51 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.423058</v>
+        <v>-58.487715</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.608916</v>
+        <v>-34.636671</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,14 +5982,14 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.481162</v>
+        <v>-58.423058</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.665875</v>
+        <v>-34.608916</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6011,22 +6011,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.413945</v>
+        <v>-58.481162</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.582774</v>
+        <v>-34.665875</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.437739</v>
+        <v>-58.413945</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.638224</v>
+        <v>-34.582774</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6233,31 +6233,31 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.494814</v>
+        <v>-58.437739</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.601905</v>
+        <v>-34.638224</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,22 +6269,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6319,31 +6319,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.469878</v>
+        <v>-58.494814</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.626919</v>
+        <v>-34.601905</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,17 +6355,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6412,10 +6412,10 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.46026</v>
+        <v>-58.469878</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.640706</v>
+        <v>-34.626919</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6441,22 +6441,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.480708</v>
+        <v>-58.46026</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.667639</v>
+        <v>-34.640706</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6527,7 +6527,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6584,36 +6584,36 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.474151</v>
+        <v>-58.480708</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.630046</v>
+        <v>-34.667639</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6658,63 +6658,63 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.464382</v>
+        <v>-58.474151</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.683083</v>
+        <v>-34.630046</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.464205</v>
+        <v>-58.464382</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.636221</v>
+        <v>-34.683083</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6773,30 +6773,34 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+          <t>PAV-U</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6816,7 +6820,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6826,63 +6830,59 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L75" t="n">
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.517269</v>
+        <v>-58.464205</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.639879</v>
+        <v>-34.636221</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PAV-B</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6917,31 +6917,31 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.423086</v>
+        <v>-58.517269</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.641356</v>
+        <v>-34.639879</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,22 +6953,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7010,10 +7010,10 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.422741</v>
+        <v>-58.423086</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.639999</v>
+        <v>-34.641356</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7039,22 +7039,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JUJUY AV 1717</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7067,10 +7067,14 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>mover a 4111</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7092,14 +7096,14 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.400922</v>
+        <v>-58.422741</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.630312</v>
+        <v>-34.639999</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7109,7 +7113,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7121,22 +7125,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7460 </t>
+          <t>8597</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/13/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TERRADA 2720</t>
+          <t>JUJUY AV 1717</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7152,12 +7156,12 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>RIENDA A PIQUE CORTADA</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7167,31 +7171,31 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.486103</v>
+        <v>-58.400922</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.603895</v>
+        <v>-34.630312</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7203,7 +7207,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>00201041</t>
+          <t xml:space="preserve">7460 </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7213,7 +7217,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HABANA 4448</t>
+          <t>TERRADA 2720</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7234,12 +7238,12 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
+          <t>RIENDA A PIQUE CORTADA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7249,17 +7253,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.518808</v>
+        <v>-58.486103</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.601236</v>
+        <v>-34.603895</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7273,7 +7277,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7285,7 +7289,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t>00201041</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7295,12 +7299,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>HABANA 4448</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7316,7 +7320,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7338,14 +7342,14 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.48834</v>
+        <v>-58.518808</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.641018</v>
+        <v>-34.601236</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7355,34 +7359,34 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>R0050</t>
+          <t>00000609</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3/25/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IBERA 3244</t>
+          <t>ZELADA 4402</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7420,27 +7424,109 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
+        <v>-58.48834</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-34.641018</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>PCH-S</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2PCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>R0050</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3/25/2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IBERA 3244</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
         <v>-58.472542</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N83" t="n">
         <v>-34.55798</v>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>COG-L</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
         </is>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1801,22 +1801,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8/26/2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SARANDI 1011</t>
+          <t>2 DE ABRIL DE 1982 6982</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>809195660</t>
+          <t>03534653</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Picada entro tambien como caso 7209</t>
+          <t>Traspasar a columna o cortar redes en punta y desmontar poste</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Desmonte</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1851,21 +1851,21 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>-58.394543</v>
+        <v>-58.494864</v>
       </c>
       <c r="N17" t="n">
-        <v>-34.620732</v>
+        <v>-34.678826</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>PAV-M</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1887,22 +1887,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9/10/2025</t>
+          <t>8/26/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vidal 1861</t>
+          <t>SARANDI 1011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>809642175</t>
+          <t>809195660</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada entro tambien como caso 7209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1944,24 +1944,24 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>-58.458298</v>
+        <v>-58.394543</v>
       </c>
       <c r="N18" t="n">
-        <v>-34.566511</v>
+        <v>-34.620732</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>COG-F</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1973,22 +1973,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9/17/2025</t>
+          <t>9/10/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Av Amancio Alcorta 3570</t>
+          <t>Vidal 1861</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>809800213</t>
+          <t>809642175</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>aplomar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2023,31 +2023,31 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>-58.409278</v>
+        <v>-58.458298</v>
       </c>
       <c r="N19" t="n">
-        <v>-34.653566</v>
+        <v>-34.566511</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>COG-F</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Patos 2702</t>
+          <t>Av Amancio Alcorta 3570</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>809818308</t>
+          <t>809800213</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
+          <t>aplomar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>-58.399262</v>
+        <v>-58.409278</v>
       </c>
       <c r="N20" t="n">
-        <v>-34.639685</v>
+        <v>-34.653566</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>PPT-K</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2145,22 +2145,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9/29/2025</t>
+          <t>9/17/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fitz Roy 2476</t>
+          <t>Los Patos 2702</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>810038995</t>
+          <t>809818308</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Sacar PRFV del cantero, colocar en vereda y aplomar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2202,14 +2202,14 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>-58.429159</v>
+        <v>-58.399262</v>
       </c>
       <c r="N21" t="n">
-        <v>-34.577821</v>
+        <v>-34.639685</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ATH-I</t>
+          <t>PPT-K</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2231,22 +2231,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10/2/2025</t>
+          <t>9/29/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIAZ, CESAR, GRAL. 1657</t>
+          <t>Fitz Roy 2476</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ICD31468700</t>
+          <t>810038995</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2288,24 +2288,24 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>-58.463851</v>
+        <v>-58.429159</v>
       </c>
       <c r="N22" t="n">
-        <v>-34.606961</v>
+        <v>-34.577821</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NRA-K</t>
+          <t>ATH-I</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2317,7 +2317,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SANTIAGO DEL ESTERO 1253</t>
+          <t>DIAZ, CESAR, GRAL. 1657</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>810132493</t>
+          <t>ICD31468700</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2374,24 +2374,24 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>-58.384406</v>
+        <v>-58.463851</v>
       </c>
       <c r="N23" t="n">
-        <v>-34.622932</v>
+        <v>-34.606961</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CON-M</t>
+          <t>NRA-K</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2403,27 +2403,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/6/2025</t>
+          <t>10/2/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
+          <t>SANTIAGO DEL ESTERO 1253</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendiente de Traspaso PROPIO</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>810132493</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Colocar R150 o R200</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2460,14 +2460,14 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-58.465176</v>
+        <v>-58.384406</v>
       </c>
       <c r="N24" t="n">
-        <v>-34.680979</v>
+        <v>-34.622932</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>CON-M</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2489,27 +2489,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>10/6/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 2353</t>
+          <t>VILLEGAS, CONRADO, GRAL. 5402</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Pendiente de Traspaso PROPIO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>810333018</t>
+          <t>Pendiente ADM</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R150 o R200</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2546,10 +2546,10 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>-58.46138</v>
+        <v>-58.465176</v>
       </c>
       <c r="N25" t="n">
-        <v>-34.629774</v>
+        <v>-34.680979</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2575,17 +2575,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ALVAREZ, CRISOSTOMO 3000</t>
+          <t>FALCON, RAMON L.,CNEL. 2353</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>810371027</t>
+          <t>810333018</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>-58.458516</v>
+        <v>-58.46138</v>
       </c>
       <c r="N26" t="n">
-        <v>-34.646422</v>
+        <v>-34.629774</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2661,7 +2661,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GARCIA, MARTIN AV. 772</t>
+          <t>ALVAREZ, CRISOSTOMO 3000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>810371042</t>
+          <t>810371027</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2718,14 +2718,14 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>-58.374086</v>
+        <v>-58.458516</v>
       </c>
       <c r="N27" t="n">
-        <v>-34.633168</v>
+        <v>-34.646422</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2735,29 +2735,29 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CON-B</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ARATO-25058.AF.1CON</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAENZ AV. 1204</t>
+          <t>GARCIA, MARTIN AV. 772</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>810416653</t>
+          <t>810371042</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2804,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.416237</v>
+        <v>-58.374086</v>
       </c>
       <c r="N28" t="n">
-        <v>-34.65477</v>
+        <v>-34.633168</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2821,34 +2821,34 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CON-B</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.AF.1CON</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/21/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SANCHEZ DE LORIA 1923</t>
+          <t>SAENZ AV. 1204</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>810416656</t>
+          <t>810416653</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2890,10 +2890,10 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>-58.411426</v>
+        <v>-58.416237</v>
       </c>
       <c r="N29" t="n">
-        <v>-34.633266</v>
+        <v>-34.65477</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PPT-Q</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>10/21/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AGUIRRE 508</t>
+          <t>SANCHEZ DE LORIA 1923</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>810421912</t>
+          <t>810416656</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>cambiar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2969,21 +2969,21 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-58.435731</v>
+        <v>-58.411426</v>
       </c>
       <c r="N30" t="n">
-        <v>-34.597659</v>
+        <v>-34.633266</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>VCR-H</t>
+          <t>PPT-Q</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3005,22 +3005,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CALVO, CARLOS 3762</t>
+          <t>AGUIRRE 508</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>810451584</t>
+          <t>810421912</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3055,21 +3055,21 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-58.418542</v>
+        <v>-58.435731</v>
       </c>
       <c r="N31" t="n">
-        <v>-34.624609</v>
+        <v>-34.597659</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>VCR-H</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIAZ VELEZ AV. 4516</t>
+          <t>CALVO, CARLOS 3762</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>810454541</t>
+          <t>810451584</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3148,14 +3148,14 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>-58.430613</v>
+        <v>-58.418542</v>
       </c>
       <c r="N32" t="n">
-        <v>-34.608805</v>
+        <v>-34.624609</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3177,7 +3177,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MIRALLA 950</t>
+          <t>DIAZ VELEZ AV. 4516</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01233440</t>
+          <t>810454541</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3234,24 +3234,24 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-58.50161</v>
+        <v>-58.430613</v>
       </c>
       <c r="N33" t="n">
-        <v>-34.647648</v>
+        <v>-34.608805</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3263,22 +3263,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10/28/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ACEVEDO 524</t>
+          <t>MIRALLA 950</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>810458896</t>
+          <t>01233440</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3320,24 +3320,24 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>-58.439164</v>
+        <v>-58.50161</v>
       </c>
       <c r="N34" t="n">
-        <v>-34.597069</v>
+        <v>-34.647648</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>VCR-J</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ARAOZ 2313</t>
+          <t>ACEVEDO 524</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>01450977</t>
+          <t>810458896</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Picada y cable cortado</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3406,10 +3406,10 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>-58.417634</v>
+        <v>-58.439164</v>
       </c>
       <c r="N35" t="n">
-        <v>-34.587439</v>
+        <v>-34.597069</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>VCR-G</t>
+          <t>VCR-J</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3435,22 +3435,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>10/28/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAN BLAS 2891</t>
+          <t>ARAOZ 2313</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>810487021</t>
+          <t>01450977</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Picada y cable cortado</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3492,24 +3492,24 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>-58.48121</v>
+        <v>-58.417634</v>
       </c>
       <c r="N36" t="n">
-        <v>-34.61126</v>
+        <v>-34.587439</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>NRA-Q</t>
+          <t>VCR-G</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CIUDAD DE LA PAZ 180</t>
+          <t>SAN BLAS 2891</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01229656</t>
+          <t>810487021</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Colocar R400 para traspaso</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nodo/Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3578,24 +3578,24 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>-58.440031</v>
+        <v>-58.48121</v>
       </c>
       <c r="N37" t="n">
-        <v>-34.575409</v>
+        <v>-34.61126</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>COG-B</t>
+          <t>NRA-Q</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LINIERS VIRREY 1142</t>
+          <t>CIUDAD DE LA PAZ 180</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>810487035</t>
+          <t>01229656</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R400 para traspaso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo/Fuente Teco</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3664,14 +3664,14 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>-58.413563</v>
+        <v>-58.440031</v>
       </c>
       <c r="N38" t="n">
-        <v>-34.624645</v>
+        <v>-34.575409</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>CEN-P</t>
+          <t>COG-B</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3693,22 +3693,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NECOCHEA 369</t>
+          <t>LINIERS VIRREY 1142</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01233359</t>
+          <t>810487035</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Colocar R200 para rtaspaso de nodo</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3750,14 +3750,14 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>-58.364132</v>
+        <v>-58.413563</v>
       </c>
       <c r="N39" t="n">
-        <v>-34.628423</v>
+        <v>-34.624645</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>CON-F</t>
+          <t>CEN-P</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3779,22 +3779,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
+          <t>NECOCHEA 369</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>810526272</t>
+          <t>01233359</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Colocar R200 para rtaspaso de nodo</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3836,14 +3836,14 @@
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>-58.460356</v>
+        <v>-58.364132</v>
       </c>
       <c r="N40" t="n">
-        <v>-34.630793</v>
+        <v>-34.628423</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PCH-J</t>
+          <t>CON-F</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3865,22 +3865,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA AV. 1654</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2309</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>810573618</t>
+          <t>810526272</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Columna picada e inclinada</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3922,14 +3922,14 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>-58.389676</v>
+        <v>-58.460356</v>
       </c>
       <c r="N41" t="n">
-        <v>-34.618127</v>
+        <v>-34.630793</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>CEN-?</t>
+          <t>PCH-J</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAN JUAN AV. 3741</t>
+          <t>INDEPENDENCIA AV. 1654</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>810712796</t>
+          <t>810573618</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Columna picada e inclinada</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4008,14 +4008,14 @@
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>-58.418108</v>
+        <v>-58.389676</v>
       </c>
       <c r="N42" t="n">
-        <v>-34.62564</v>
+        <v>-34.618127</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ALM-A</t>
+          <t>CEN-?</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAMPICHUELO 229</t>
+          <t>SAN JUAN AV. 3741</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>810712887</t>
+          <t>810712796</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cambiar</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4094,14 +4094,14 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>-58.433855</v>
+        <v>-58.418108</v>
       </c>
       <c r="N43" t="n">
-        <v>-34.614487</v>
+        <v>-34.62564</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>ALM-J</t>
+          <t>ALM-A</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4123,22 +4123,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FERRARI 410</t>
+          <t>CAMPICHUELO 229</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>810713039</t>
+          <t>810712887</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Picada</t>
+          <t>Cambiar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4180,24 +4180,24 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>-58.441198</v>
+        <v>-58.433855</v>
       </c>
       <c r="N44" t="n">
-        <v>-34.605341</v>
+        <v>-34.614487</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ALM-O</t>
+          <t>ALM-J</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4209,22 +4209,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S00958024</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SAN PEDRITO 3010</t>
+          <t>FERRARI 410</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>810804380</t>
+          <t>810713039</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>columna inclinada base corroida</t>
+          <t>Picada</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4266,24 +4266,24 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-58.439239</v>
+        <v>-58.441198</v>
       </c>
       <c r="N45" t="n">
-        <v>-34.6604</v>
+        <v>-34.605341</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>ALM-O</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4295,7 +4295,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S01140678</t>
+          <t>S00958024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
+          <t>SAN PEDRITO 3010</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>810804375</t>
+          <t>810804380</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>columna inclinada corroida</t>
+          <t>columna inclinada base corroida</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4352,10 +4352,10 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>-58.388529</v>
+        <v>-58.439239</v>
       </c>
       <c r="N46" t="n">
-        <v>-34.655949</v>
+        <v>-34.6604</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4381,22 +4381,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S01112737</t>
+          <t>S01140678</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RODO, JOSE E. 4799</t>
+          <t xml:space="preserve"> VELEZ SARSFIELD AV. 1722</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>810820822</t>
+          <t>810804375</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>columna inclinada corroida</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4438,24 +4438,24 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>-58.491325</v>
+        <v>-58.388529</v>
       </c>
       <c r="N47" t="n">
-        <v>-34.647761</v>
+        <v>-34.655949</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4467,7 +4467,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>S01112737</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOGOTA 2770</t>
+          <t>RODO, JOSE E. 4799</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>810820553</t>
+          <t>810820822</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>base picada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4524,24 +4524,24 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-58.469394</v>
+        <v>-58.491325</v>
       </c>
       <c r="N48" t="n">
-        <v>-34.626925</v>
+        <v>-34.647761</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Juncal 1642</t>
+          <t>BOGOTA 2770</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">01749376 </t>
+          <t>810820553</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>base picada</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4610,14 +4610,14 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-58.390974</v>
+        <v>-58.469394</v>
       </c>
       <c r="N49" t="n">
-        <v>-34.594177</v>
+        <v>-34.626925</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>RET-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4639,22 +4639,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CASTILLO 12</t>
+          <t>Juncal 1642</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>810984643</t>
+          <t xml:space="preserve">01749376 </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4684,26 +4684,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>-58.430396</v>
+        <v>-58.390974</v>
       </c>
       <c r="N50" t="n">
-        <v>-34.599668</v>
+        <v>-34.594177</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>RET-N</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4725,22 +4725,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BONIFACIO, JOSE 2319</t>
+          <t>CASTILLO 12</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>810984687</t>
+          <t>810984643</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4775,21 +4775,21 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>-58.459955</v>
+        <v>-58.430396</v>
       </c>
       <c r="N51" t="n">
-        <v>-34.631973</v>
+        <v>-34.599668</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4811,22 +4811,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S01204545</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medina 420</t>
+          <t>BONIFACIO, JOSE 2319</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>811131640</t>
+          <t>810984687</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>inclinado</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4868,51 +4868,51 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-58.48802</v>
+        <v>-58.459955</v>
       </c>
       <c r="N52" t="n">
-        <v>-34.641075</v>
+        <v>-34.631973</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>S01204545</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BACACAY 2357</t>
+          <t>Medina 420</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>811198692</t>
+          <t>811131640</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">base corroida </t>
+          <t>inclinado</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4954,51 +4954,51 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>-58.463198</v>
+        <v>-58.48802</v>
       </c>
       <c r="N53" t="n">
-        <v>-34.62624</v>
+        <v>-34.641075</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>NRA-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>-705</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Larrea 370</t>
+          <t>BACACAY 2357</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02013924</t>
+          <t>811198692</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t xml:space="preserve">base corroida </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5040,14 +5040,14 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>-58.402154</v>
+        <v>-58.463198</v>
       </c>
       <c r="N54" t="n">
-        <v>-34.605295</v>
+        <v>-34.62624</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>CLI-D</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5069,22 +5069,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>-705</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/29/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>REMEDIOS 3285</t>
+          <t>Larrea 370</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811299402</t>
+          <t>02013924</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5126,47 +5126,51 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>-58.471183</v>
+        <v>-58.402154</v>
       </c>
       <c r="N55" t="n">
-        <v>-34.638988</v>
+        <v>-34.605295</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>PCH-O</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+          <t>CLI-D</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1/2/2026</t>
+          <t>12/29/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CARACAS 554</t>
+          <t>REMEDIOS 3285</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5181,7 +5185,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>811299453</t>
+          <t>811299402</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5208,46 +5212,42 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>-58.46357</v>
+        <v>-58.471183</v>
       </c>
       <c r="N56" t="n">
-        <v>-34.623187</v>
+        <v>-34.638988</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>NRA-E</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-O</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S00982176</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>1/2/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GRANADEROS 110</t>
+          <t>CARACAS 554</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>811453890</t>
+          <t>811299453</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5294,10 +5294,10 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>-58.459547</v>
+        <v>-58.46357</v>
       </c>
       <c r="N57" t="n">
-        <v>-34.626309</v>
+        <v>-34.623187</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>PCH-H</t>
+          <t>NRA-E</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5323,22 +5323,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>S00982176</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/14/2026</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ESCALADA AV. 3100</t>
+          <t>GRANADEROS 110</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>811454435</t>
+          <t>811453890</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5380,10 +5380,10 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>-58.465166</v>
+        <v>-58.459547</v>
       </c>
       <c r="N58" t="n">
-        <v>-34.670435</v>
+        <v>-34.626309</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>PAV-?</t>
+          <t>PCH-H</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5409,17 +5409,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/26/2026</t>
+          <t>1/14/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
+          <t>ESCALADA AV. 3100</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>811626780</t>
+          <t>811454435</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>chocada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5466,14 +5466,14 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>-58.438399</v>
+        <v>-58.465166</v>
       </c>
       <c r="N59" t="n">
-        <v>-34.663958</v>
+        <v>-34.670435</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PPT-I</t>
+          <t>PAV-?</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESCALADA AV. 2421</t>
+          <t>RABANAL, FRANCISCO, INTENDENTE AV. 3085</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>811626771</t>
+          <t>811626780</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>chocada</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5552,14 +5552,14 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>-58.475565</v>
+        <v>-58.438399</v>
       </c>
       <c r="N60" t="n">
-        <v>-34.660488</v>
+        <v>-34.663958</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>PAV-P</t>
+          <t>PPT-I</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5581,22 +5581,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>-739</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1/27/2026</t>
+          <t>1/26/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
+          <t xml:space="preserve"> ESCALADA AV. 2421</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>811626802</t>
+          <t>811626771</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5638,10 +5638,10 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>-58.460855</v>
+        <v>-58.475565</v>
       </c>
       <c r="N61" t="n">
-        <v>-34.631046</v>
+        <v>-34.660488</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PCH-F</t>
+          <t>PAV-P</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5667,22 +5667,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S01281615</t>
+          <t>-739</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1/29/2026</t>
+          <t>1/27/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RUCCI, JOSE IGNACIO 4011</t>
+          <t>ALBERDI, JUAN BAUTISTA AV. 2352</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>811626968</t>
+          <t>811626802</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5724,10 +5724,10 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>-58.479751</v>
+        <v>-58.460855</v>
       </c>
       <c r="N62" t="n">
-        <v>-34.677211</v>
+        <v>-34.631046</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S01447367</t>
+          <t>S01281615</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MOZART 216</t>
+          <t>RUCCI, JOSE IGNACIO 4011</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>811626897</t>
+          <t>811626968</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5810,36 +5810,36 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>-58.491573</v>
+        <v>-58.479751</v>
       </c>
       <c r="N63" t="n">
-        <v>-34.639215</v>
+        <v>-34.677211</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S01447520</t>
+          <t>S01447367</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FALCON, RAMON L.,CNEL. 4326</t>
+          <t>MOZART 216</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>811626894</t>
+          <t>811626897</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5896,10 +5896,10 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>-58.487715</v>
+        <v>-58.491573</v>
       </c>
       <c r="N64" t="n">
-        <v>-34.636671</v>
+        <v>-34.639215</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5925,22 +5925,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>S01447520</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2/2/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
+          <t>FALCON, RAMON L.,CNEL. 4326</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>811626981</t>
+          <t>811626894</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5982,51 +5982,51 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>-58.423058</v>
+        <v>-58.487715</v>
       </c>
       <c r="N65" t="n">
-        <v>-34.608916</v>
+        <v>-34.636671</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>ALM-E</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2/3/2026</t>
+          <t>2/2/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CASCO, HORACIO, DR. 5287</t>
+          <t>ACUÑA DE FIGUEROA, FRANCISCO 180</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>811627028</t>
+          <t>811626981</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6068,14 +6068,14 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>-58.481162</v>
+        <v>-58.423058</v>
       </c>
       <c r="N66" t="n">
-        <v>-34.665875</v>
+        <v>-34.608916</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>ALM-E</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6097,22 +6097,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2/4/2026</t>
+          <t>2/3/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ugarteche 2816</t>
+          <t>CASCO, HORACIO, DR. 5287</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>811627090</t>
+          <t>811627028</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>corroida inclinada</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6154,14 +6154,14 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>-58.413945</v>
+        <v>-58.481162</v>
       </c>
       <c r="N67" t="n">
-        <v>-34.582774</v>
+        <v>-34.665875</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>AGU-M</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S01421388</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MITRE, EMILIO 1602</t>
+          <t>Ugarteche 2816</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>812503538</t>
+          <t>811627090</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>corroida</t>
+          <t>corroida inclinada</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6240,14 +6240,14 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>-58.437739</v>
+        <v>-58.413945</v>
       </c>
       <c r="N68" t="n">
-        <v>-34.638224</v>
+        <v>-34.582774</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>PPT-S</t>
+          <t>AGU-M</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>900009468810</t>
+          <t>S01421388</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUENCA 3033 </t>
+          <t>MITRE, EMILIO 1602</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>811627041</t>
+          <t>812503538</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>tensor roto</t>
+          <t>corroida</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6319,31 +6319,31 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>-58.494814</v>
+        <v>-58.437739</v>
       </c>
       <c r="N69" t="n">
-        <v>-34.601905</v>
+        <v>-34.638224</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>DEV-B</t>
+          <t>PPT-S</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6355,22 +6355,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>900009468810</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/4/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TERRADA 402</t>
+          <t xml:space="preserve">CUENCA 3033 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>812440368</t>
+          <t>811627041</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>base corroida</t>
+          <t>tensor roto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6405,31 +6405,31 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>-58.469878</v>
+        <v>-58.494814</v>
       </c>
       <c r="N70" t="n">
-        <v>-34.626919</v>
+        <v>-34.601905</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>NRA-L</t>
+          <t>DEV-B</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6441,17 +6441,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S00086082</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2/5/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
+          <t>TERRADA 402</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>812439923</t>
+          <t>812440368</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>inclinada corroida</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6498,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>-58.46026</v>
+        <v>-58.469878</v>
       </c>
       <c r="N71" t="n">
-        <v>-34.640706</v>
+        <v>-34.626919</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>PPT-N</t>
+          <t>NRA-L</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6527,22 +6527,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>S00086082</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2/23/2026</t>
+          <t>2/5/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MONTREAL 5391</t>
+          <t xml:space="preserve"> PRIMERA JUNTA 2899</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>812440314</t>
+          <t>812439923</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>inclinada</t>
+          <t>inclinada corroida</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6584,10 +6584,10 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>-58.480708</v>
+        <v>-58.46026</v>
       </c>
       <c r="N72" t="n">
-        <v>-34.667639</v>
+        <v>-34.640706</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>PAV-Q</t>
+          <t>PPT-N</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S00936659</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLORES, VENANCIO, GRAL. 3197</t>
+          <t>MONTREAL 5391</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>812440276</t>
+          <t>812440314</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6670,36 +6670,36 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>-58.474151</v>
+        <v>-58.480708</v>
       </c>
       <c r="N73" t="n">
-        <v>-34.630046</v>
+        <v>-34.667639</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NRA-R</t>
+          <t>PAV-Q</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2NRA</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S00552343</t>
+          <t>S00936659</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
+          <t>FLORES, VENANCIO, GRAL. 3197</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812440276</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>inclinada base corroida</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6744,63 +6744,63 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>-58.464382</v>
+        <v>-58.474151</v>
       </c>
       <c r="N74" t="n">
-        <v>-34.683083</v>
+        <v>-34.630046</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>PAV-U</t>
+          <t>NRA-R</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2NRA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S00176142</t>
+          <t>-765</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3/6/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CULPINA 533</t>
+          <t>AVALOS 180</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503657</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6842,47 +6842,51 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>-58.464205</v>
+        <v>-58.465874</v>
       </c>
       <c r="N75" t="n">
-        <v>-34.636221</v>
+        <v>-34.594613</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>PCH-N</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+          <t>ATH-F</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>-768</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OLIDEN 55</t>
+          <t>CONCORDIA 3581</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6897,12 +6901,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503649</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>columna inclinada</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6917,21 +6921,21 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L76" t="n">
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>-58.517269</v>
+        <v>-58.502724</v>
       </c>
       <c r="N76" t="n">
-        <v>-34.639879</v>
+        <v>-34.599311</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -6941,7 +6945,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>PAV-B</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -6953,22 +6957,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>-772</t>
+          <t>-767</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3/10/2026</t>
+          <t>3/2/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LA PLATA AV. 2304</t>
+          <t>CONCORDIA 3525</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6983,12 +6987,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pendiente ADM</t>
+          <t>812503647</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Desplazar Columna</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7003,31 +7007,31 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>-58.423086</v>
+        <v>-58.502389</v>
       </c>
       <c r="N77" t="n">
-        <v>-34.641356</v>
+        <v>-34.599679</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PUE-B</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7039,22 +7043,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>S00552343</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3/9/2026</t>
+          <t>2/23/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CASEROS AV. 4131</t>
+          <t xml:space="preserve">Nicolás Descalzi 5582 </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7074,7 +7078,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>mover a 4111</t>
+          <t>inclinada base corroida</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7084,22 +7088,22 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L78" t="n">
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>-58.422741</v>
+        <v>-58.464382</v>
       </c>
       <c r="N78" t="n">
-        <v>-34.639999</v>
+        <v>-34.683083</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7113,7 +7117,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>PPT-L</t>
+          <t>PAV-U</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7125,22 +7129,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>-770</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3/13/2026</t>
+          <t>3/5/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JUJUY AV 1717</t>
+          <t>SAN JUAN AV. 1245</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7153,10 +7157,14 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>inclinada</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7166,7 +7174,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7178,10 +7186,10 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>-58.400922</v>
+        <v>-58.383649</v>
       </c>
       <c r="N79" t="n">
-        <v>-34.630312</v>
+        <v>-34.622187</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7195,7 +7203,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7207,22 +7215,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7460 </t>
+          <t>S00176142</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/6/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TERRADA 2720</t>
+          <t>CULPINA 533</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7235,76 +7243,76 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>RIENDA A PIQUE CORTADA</t>
+          <t>base corroida</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>-58.486103</v>
+        <v>-58.464205</v>
       </c>
       <c r="N80" t="n">
-        <v>-34.603895</v>
+        <v>-34.636221</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>NRA-P</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
+          <t>PCH-N</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>00201041</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HABANA 4448</t>
+          <t>OLIDEN 55</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7317,10 +7325,14 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DEMONTAR POSTE Y REEMPLAZAR POR COLUMNA</t>
+          <t>columna inclinada</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7335,21 +7347,21 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>-58.518808</v>
+        <v>-58.517269</v>
       </c>
       <c r="N81" t="n">
-        <v>-34.601236</v>
+        <v>-34.639879</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7359,7 +7371,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PAV-B</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7371,22 +7383,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t>-772</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/10/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>LA PLATA AV. 2304</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7399,10 +7411,14 @@
           <t>Optical Power</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>Desplazar Columna</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7424,111 +7440,2777 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>-58.48834</v>
+        <v>-58.423086</v>
       </c>
       <c r="N82" t="n">
-        <v>-34.641018</v>
+        <v>-34.641356</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>PPT-L</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>R0050</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3/25/2026</t>
+          <t>3/9/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IBERA 3244</t>
+          <t>CASEROS AV. 4131</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>mover a 4111</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-58.422741</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-34.639999</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>PPT-L</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LIVERPOOL 2975</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-58.483044</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-34.583393</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8455</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LIVERPOOL 2849</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-58.481371</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-34.582578</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>ATH-D</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>LONDRES 4142</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>-58.479712</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-34.581443</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GAMARRA y TREVERIS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-58.477099</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-34.582525</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>ATH-S</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>8460</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>3/10/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>VICTORICA, BENJAMIN, GENERAL, AV. 2968</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pendiente ADM</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Columna Picada</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-58.479692</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-34.586552</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>ATH-G</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8470 </t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AV. GRAL.BENJAMIN VICTORICA 2826</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>812878680</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Cambiar columna</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>-58.479404</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-34.585508</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>ATH-G</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8473 </t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>VIRREY AVILES 3883</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>812878777</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>-58.46429</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-34.578287</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>ATH-H</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>8597</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>JUJUY AV 1717</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>812879486</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>-58.400922</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-34.630312</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>8598</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IGUAZU 590</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>812879488</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>-58.405605</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-34.644231</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>PPT-K</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>8602</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAZ CNEL AV 2139 </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>812879521</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>-58.408769</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-34.587342</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>AGU-J</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>8606</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>YRIGOYEN HIPOLITO 1934</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>812879544</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>-58.394029</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-34.610507</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>CEN-G</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>8609</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SEGUI JUAN FRANCISCO 4691</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>812879559</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>-58.422229</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-34.573148</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>VCR-M</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8610</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>GANDHI MAHATMA 295</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>812879573</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Columna Inclinada</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-58.440568</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-34.6034</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>ALM-N</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3/13/2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AGUIRRE 794</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>812879594</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-58.438085</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-34.595145</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>VCR-H</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>00191122</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3/19/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SAN PEDRITO AV 384</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>812879887</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Cambiar Columna</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>-58.467504</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-34.635231</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>PCH-F</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>00084267</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MOLDES 920</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>812879919</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>-58.472542</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-34.55798</v>
-      </c>
-      <c r="O83" t="inlineStr">
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>-58.44958</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-34.57149</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>COG-?</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>00781500</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>RAVIGNANI EMILIO DR 1498</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>812879925</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>-58.441411</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-34.583443</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>ATH-M</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>00056825</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LERMA 585</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>812879938</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Nodo Teco</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>-58.432774</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-34.593289</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>VCR-I</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>00050599</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>812879940</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>-58.418254</v>
+      </c>
+      <c r="N102" t="n">
+        <v>-34.615692</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>ALM-C</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7460 </t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TERRADA 2720</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>812879976</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>RIENDA A PIQUE CORTADA</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>-58.486103</v>
+      </c>
+      <c r="N103" t="n">
+        <v>-34.603895</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Paternal</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>NRA-P</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>00000609</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>3/21/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ZELADA 4402</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>812880445</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-58.48834</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-34.641018</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>PCH-S</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.2PCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>00317296</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AGRELO 3620</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>812880625</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-58.417002</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-34.618613</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>ALM-B</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>00322642</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ESTADO DE PALESTINA 727</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>812880655</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>-58.425539</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-34.602286</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>CLI-N</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>8263</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MEXICO 3306</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>812880662</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>-58.412865</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-34.619484</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>CEN-J</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>8265</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HUMBERTO 1 1999</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>812880685</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>-58.394304</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-34.621645</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>CEN-B</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>08672</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>HERRERA 540</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>812880701</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-58.378264</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-34.636021</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>CON-H</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>8647</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3/24/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MELIAN AV 4827 </t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>812880706</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" t="n">
+        <v>-58.487048</v>
+      </c>
+      <c r="N110" t="n">
+        <v>-34.545509</v>
+      </c>
+      <c r="O110" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>Capital Norte</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>COG-L</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>COG-Q</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
         <is>
           <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>8674</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>3/23/2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BRASIL 2509</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>812880723</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-58.399415</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-34.631112</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>PPT-F</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11070617 </t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FONROUGE 1697</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>812880729</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-58.496881</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-34.653948</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Devoto</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Capital Norte</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>PAV-H</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>8703</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>RIVADAVIA AV 1985</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>812880736</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>APLOMAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Aplomo</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Fuente Teco</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-58.394609</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-34.609304</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>CLI-B</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>8702</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>JUNCAL 2249</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>812880742</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CAMBIAR COLUMNA</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-58.399319</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-34.592221</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>RET-E</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>

--- a/mapa_interactivo_Optical_Power.xlsx
+++ b/mapa_interactivo_Optical_Power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R205"/>
+  <dimension ref="A1:R211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11317,24 +11317,20 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>00191122</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3/19/2026</t>
+          <t>3/18/2026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SAN PEDRITO AV 384</t>
+          <t>GALLARDO, ANGEL AV. 1072</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11349,12 +11345,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>812879887</t>
+          <t>812879764</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Cambiar Columna</t>
+          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -11376,182 +11372,174 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>-58.467504</v>
+        <v>-58.444908</v>
       </c>
       <c r="N128" t="n">
-        <v>-34.635231</v>
+        <v>-34.607205</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Capital Sur</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>ALM-O</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3/18/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>GALLARDO, ANGEL AV. 1072</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>812879764</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sin equipos</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Pasante</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-58.419576</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-34.621289</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
           <t>Boedo</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P129" t="inlineStr">
         <is>
           <t>Capital Sur</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>PCH-F</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>00084267</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>MOLDES 920</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>812879919</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>ALM-A</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Fuera de Poligono OVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3/18/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>GALLARDO, ANGEL AV. 1072</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Optical Power</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>812879764</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Reubicar columna y rienda, Angel Gallardo 1072 a 1084</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Cambio</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
         <is>
           <t>Sin equipos</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t>Pasante</t>
         </is>
       </c>
-      <c r="L129" t="n">
-        <v>1</v>
-      </c>
-      <c r="M129" t="n">
-        <v>-58.44958</v>
-      </c>
-      <c r="N129" t="n">
-        <v>-34.57149</v>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>Colegiales</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Capital Norte</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>COG-?</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Fuera de Poligono OVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>00781500</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>3/21/2026</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>RAVIGNANI EMILIO DR 1498</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Optical Power</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>812879925</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>CAMBIAR COLUMNA</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Cambio</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Sin equipos</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Pasante</t>
-        </is>
-      </c>
       <c r="L130" t="n">
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>-58.441411</v>
+        <v>-58.430568</v>
       </c>
       <c r="N130" t="n">
-        <v>-34.583443</v>
+        <v>-34.599485</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11565,7 +11553,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>ATH-M</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11577,22 +11565,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>00056825</t>
+          <t>00191122</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3/21/2026</t>
+          <t>3/19/2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LERMA 585</t>
+          <t>SAN PEDRITO AV 384</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11607,12 +11595,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>812879938</t>
+          <t>812879887</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>Cambiar Columna</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -11622,7 +11610,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Nodo Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -11634,14 +11622,14 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>-58.432774</v>
+        <v>-58.467504</v>
       </c>
       <c r="N131" t="n">
-        <v>-34.593289</v>
+        <v>-34.635231</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boedo</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -11651,7 +11639,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>VCR-I</t>
+          <t>PCH-F</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11663,7 +11651,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>00050599</t>
+          <t>00084267</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11673,12 +11661,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELGRANO AV 3689 </t>
+          <t>MOLDES 920</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11693,7 +11681,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>812879940</t>
+          <t>812879919</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -11720,24 +11708,24 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>-58.418254</v>
+        <v>-58.44958</v>
       </c>
       <c r="N132" t="n">
-        <v>-34.615692</v>
+        <v>-34.57149</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>ALM-C</t>
+          <t>COG-?</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11749,7 +11737,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">7460 </t>
+          <t>00781500</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11759,12 +11747,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TERRADA 2720</t>
+          <t>RAVIGNANI EMILIO DR 1498</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11779,17 +11767,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>812879976</t>
+          <t>812879925</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>RIENDA A PIQUE CORTADA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11799,31 +11787,31 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>-58.486103</v>
+        <v>-58.441411</v>
       </c>
       <c r="N133" t="n">
-        <v>-34.603895</v>
+        <v>-34.583443</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>NRA-P</t>
+          <t>ATH-M</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -11835,7 +11823,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>00000609</t>
+          <t>00056825</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11845,12 +11833,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ZELADA 4402</t>
+          <t>LERMA 585</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11865,7 +11853,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>812880445</t>
+          <t>812879938</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -11880,7 +11868,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Nodo Teco</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11892,46 +11880,46 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>-58.48834</v>
+        <v>-58.432774</v>
       </c>
       <c r="N134" t="n">
-        <v>-34.641018</v>
+        <v>-34.593289</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>PCH-S</t>
+          <t>VCR-I</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.2PCH</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>00317296</t>
+          <t>00050599</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AGRELO 3620</t>
+          <t xml:space="preserve">BELGRANO AV 3689 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11951,7 +11939,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>812880625</t>
+          <t>812879940</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -11978,10 +11966,10 @@
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>-58.417002</v>
+        <v>-58.418254</v>
       </c>
       <c r="N135" t="n">
-        <v>-34.618613</v>
+        <v>-34.615692</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11995,7 +11983,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>ALM-B</t>
+          <t>ALM-C</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12007,22 +11995,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>00322642</t>
+          <t xml:space="preserve">7460 </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ESTADO DE PALESTINA 727</t>
+          <t>TERRADA 2720</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12037,17 +12025,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>812880655</t>
+          <t>812879976</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>RIENDA A PIQUE CORTADA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -12057,31 +12045,31 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Pasante</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-58.425539</v>
+        <v>-58.486103</v>
       </c>
       <c r="N136" t="n">
-        <v>-34.602286</v>
+        <v>-34.603895</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>CLI-N</t>
+          <t>NRA-P</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12093,22 +12081,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>00000609</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3/23/2026</t>
+          <t>3/21/2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MEXICO 3306</t>
+          <t>ZELADA 4402</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12123,7 +12111,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>812880662</t>
+          <t>812880445</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12150,36 +12138,36 @@
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>-58.412865</v>
+        <v>-58.48834</v>
       </c>
       <c r="N137" t="n">
-        <v>-34.619484</v>
+        <v>-34.641018</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>PCH-S</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.2PCH</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>00317296</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12189,12 +12177,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HUMBERTO 1 1999</t>
+          <t>AGRELO 3620</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12209,7 +12197,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>812880685</t>
+          <t>812880625</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12224,7 +12212,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -12236,14 +12224,14 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>-58.394304</v>
+        <v>-58.417002</v>
       </c>
       <c r="N138" t="n">
-        <v>-34.621645</v>
+        <v>-34.618613</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -12253,7 +12241,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CEN-B</t>
+          <t>ALM-B</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -12265,7 +12253,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>08672</t>
+          <t>00322642</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12275,12 +12263,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HERRERA 540</t>
+          <t>ESTADO DE PALESTINA 727</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12295,7 +12283,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>812880701</t>
+          <t>812880655</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -12322,14 +12310,14 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>-58.378264</v>
+        <v>-58.425539</v>
       </c>
       <c r="N139" t="n">
-        <v>-34.636021</v>
+        <v>-34.602286</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -12339,7 +12327,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CON-H</t>
+          <t>CLI-N</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -12351,22 +12339,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3/24/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELIAN AV 4827 </t>
+          <t>MEXICO 3306</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12381,12 +12369,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>812880706</t>
+          <t>812880662</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CAMBIAR POSTE POR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12408,24 +12396,24 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>-58.487048</v>
+        <v>-58.412865</v>
       </c>
       <c r="N140" t="n">
-        <v>-34.545509</v>
+        <v>-34.619484</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>COG-Q</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -12437,7 +12425,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12447,12 +12435,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BRASIL 2509</t>
+          <t>HUMBERTO 1 1999</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12467,7 +12455,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>812880723</t>
+          <t>812880685</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -12482,7 +12470,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -12494,10 +12482,10 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>-58.399415</v>
+        <v>-58.394304</v>
       </c>
       <c r="N141" t="n">
-        <v>-34.631112</v>
+        <v>-34.621645</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12511,7 +12499,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>PPT-F</t>
+          <t>CEN-B</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12523,22 +12511,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">11070617 </t>
+          <t>08672</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FONROUGE 1697</t>
+          <t>HERRERA 540</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12553,7 +12541,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>812880729</t>
+          <t>812880701</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -12580,24 +12568,24 @@
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>-58.496881</v>
+        <v>-58.378264</v>
       </c>
       <c r="N142" t="n">
-        <v>-34.653948</v>
+        <v>-34.636021</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>PAV-H</t>
+          <t>CON-H</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -12609,22 +12597,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>3/24/2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RIVADAVIA AV 1985</t>
+          <t xml:space="preserve">MELIAN AV 4827 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12639,22 +12627,22 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>812880736</t>
+          <t>812880706</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Fuente Teco</t>
+          <t>Sin equipos</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -12666,24 +12654,24 @@
         <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>-58.394609</v>
+        <v>-58.487048</v>
       </c>
       <c r="N143" t="n">
-        <v>-34.609304</v>
+        <v>-34.545509</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>CLI-B</t>
+          <t>COG-Q</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12695,22 +12683,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3/28/2026</t>
+          <t>3/23/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>JUNCAL 2249</t>
+          <t>BRASIL 2509</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12725,7 +12713,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>812880742</t>
+          <t>812880723</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -12752,14 +12740,14 @@
         <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>-58.399319</v>
+        <v>-58.399415</v>
       </c>
       <c r="N144" t="n">
-        <v>-34.592221</v>
+        <v>-34.631112</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -12769,30 +12757,34 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>RET-E</t>
+          <t>PPT-F</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>ARATO-25058.PO.1RET</t>
+          <t>Fuera de Poligono OVL</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">900009880510 </t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t xml:space="preserve">11070617 </t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3/28/2026</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GUTENBERG 4150</t>
+          <t>FONROUGE 1697</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12807,12 +12799,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>813046368</t>
+          <t>812880729</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CAMBIAR POSTE POR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -12834,14 +12826,14 @@
         <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>-58.516791</v>
+        <v>-58.496881</v>
       </c>
       <c r="N145" t="n">
-        <v>-34.596662</v>
+        <v>-34.653948</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -12851,7 +12843,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>PUE-P</t>
+          <t>PAV-H</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12863,22 +12855,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LERMA 311</t>
+          <t>RIVADAVIA AV 1985</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12893,22 +12885,22 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>813046616</t>
+          <t>812880736</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Sin equipos</t>
+          <t>Fuente Teco</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -12920,14 +12912,14 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>-58.430656</v>
+        <v>-58.394609</v>
       </c>
       <c r="N146" t="n">
-        <v>-34.595567</v>
+        <v>-34.609304</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -12937,7 +12929,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>CLI-B</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12949,22 +12941,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4/11/2026</t>
+          <t>3/28/2026</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ARAOZ 1020</t>
+          <t>JUNCAL 2249</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12979,17 +12971,17 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>813046622</t>
+          <t>812880742</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -13006,14 +12998,14 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>-58.430374</v>
+        <v>-58.399319</v>
       </c>
       <c r="N147" t="n">
-        <v>-34.595571</v>
+        <v>-34.592221</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -13023,34 +13015,30 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>CLI-O</t>
+          <t>RET-E</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Fuera de Poligono OVL</t>
+          <t>ARATO-25058.PO.1RET</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8768</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>4/11/2026</t>
-        </is>
-      </c>
+          <t xml:space="preserve">900009880510 </t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SALTA 1061</t>
+          <t>GUTENBERG 4150</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13065,12 +13053,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>813046630</t>
+          <t>813046368</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>CAMBIAR POSTE POR COLUMNA</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13092,24 +13080,24 @@
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>-58.383028</v>
+        <v>-58.516791</v>
       </c>
       <c r="N148" t="n">
-        <v>-34.620345</v>
+        <v>-34.596662</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>CEN-A</t>
+          <t>PUE-P</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13121,7 +13109,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13131,7 +13119,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NAON ROMULO 3405</t>
+          <t>LERMA 311</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13151,17 +13139,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>813046635</t>
+          <t>813046616</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -13178,24 +13166,24 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>-58.480063</v>
+        <v>-58.430656</v>
       </c>
       <c r="N149" t="n">
-        <v>-34.558156</v>
+        <v>-34.595567</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>COG-N</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -13207,7 +13195,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13217,12 +13205,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TERRERO 1390</t>
+          <t>ARAOZ 1020</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13237,17 +13225,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>813046644</t>
+          <t>813046622</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -13264,24 +13252,24 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>-58.463605</v>
+        <v>-58.430374</v>
       </c>
       <c r="N150" t="n">
-        <v>-34.612257</v>
+        <v>-34.595571</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>NRA-J</t>
+          <t>CLI-O</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -13293,7 +13281,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13303,12 +13291,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RINCON 731</t>
+          <t>SALTA 1061</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13323,7 +13311,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>813046658</t>
+          <t>813046630</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -13350,14 +13338,14 @@
         <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>-58.396088</v>
+        <v>-58.383028</v>
       </c>
       <c r="N151" t="n">
-        <v>-34.617527</v>
+        <v>-34.620345</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -13367,7 +13355,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>CEN-C</t>
+          <t>CEN-A</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -13379,7 +13367,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13389,7 +13377,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BARZANA 1685</t>
+          <t>NAON ROMULO 3405</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13409,17 +13397,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>813046666</t>
+          <t>813046635</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -13436,14 +13424,14 @@
         <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>-58.484374</v>
+        <v>-58.480063</v>
       </c>
       <c r="N152" t="n">
-        <v>-34.583484</v>
+        <v>-34.558156</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -13453,7 +13441,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>COG-N</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -13465,7 +13453,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13475,12 +13463,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ARGERICH 3685</t>
+          <t>TERRERO 1390</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13495,7 +13483,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>813046706</t>
+          <t>813046644</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -13505,7 +13493,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -13522,10 +13510,10 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>-58.496794</v>
+        <v>-58.463605</v>
       </c>
       <c r="N153" t="n">
-        <v>-34.594395</v>
+        <v>-34.612257</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13539,7 +13527,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>NRA-J</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -13551,7 +13539,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S00289486</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13561,12 +13549,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PARAGUAY 4585</t>
+          <t>RINCON 731</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13581,7 +13569,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>813046715</t>
+          <t>813046658</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -13608,14 +13596,14 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>-58.42498</v>
+        <v>-58.396088</v>
       </c>
       <c r="N154" t="n">
-        <v>-34.584031</v>
+        <v>-34.617527</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -13625,7 +13613,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>VCR-P</t>
+          <t>CEN-C</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -13637,7 +13625,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S00325208</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13647,12 +13635,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PARAGUAY 3711</t>
+          <t>BARZANA 1685</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -13667,7 +13655,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>813046718</t>
+          <t>813046666</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -13694,24 +13682,24 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>-58.416117</v>
+        <v>-58.484374</v>
       </c>
       <c r="N155" t="n">
-        <v>-34.590942</v>
+        <v>-34.583484</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>VCR-C</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -13723,7 +13711,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S00337251</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13733,12 +13721,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SANCHEZ DE BUSTAMANTE 2450</t>
+          <t>ARGERICH 3685</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13753,7 +13741,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>813046724</t>
+          <t>813046706</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -13763,7 +13751,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -13780,24 +13768,24 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>-58.403295</v>
+        <v>-58.496794</v>
       </c>
       <c r="N156" t="n">
-        <v>-34.585041</v>
+        <v>-34.594395</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>AGU-H</t>
+          <t>PUE-G</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13809,7 +13797,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S00328975</t>
+          <t>S00289486</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13819,12 +13807,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>EINSTEIN ALBERTO 350</t>
+          <t>PARAGUAY 4585</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13839,7 +13827,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>813046733</t>
+          <t>813046715</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -13866,14 +13854,14 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>-58.413179</v>
+        <v>-58.42498</v>
       </c>
       <c r="N157" t="n">
-        <v>-34.649733</v>
+        <v>-34.584031</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -13883,7 +13871,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>VCR-P</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13895,7 +13883,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S00334337</t>
+          <t>S00325208</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13905,12 +13893,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>LUZURIAGA 905</t>
+          <t>PARAGUAY 3711</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13925,7 +13913,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>813046739</t>
+          <t>813046718</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -13952,14 +13940,14 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>-58.388385</v>
+        <v>-58.416117</v>
       </c>
       <c r="N158" t="n">
-        <v>-34.644336</v>
+        <v>-34.590942</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -13969,7 +13957,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>CON-K</t>
+          <t>VCR-C</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -13981,7 +13969,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S00337329</t>
+          <t>S00337251</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13991,12 +13979,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AV SAENZ 1319</t>
+          <t>SANCHEZ DE BUSTAMANTE 2450</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14011,7 +13999,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>813046749</t>
+          <t>813046724</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -14038,14 +14026,14 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>-58.416649</v>
+        <v>-58.403295</v>
       </c>
       <c r="N159" t="n">
-        <v>-34.656395</v>
+        <v>-34.585041</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -14055,7 +14043,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>AGU-H</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14067,7 +14055,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S00355203</t>
+          <t>S00328975</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14077,7 +14065,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>EREZCANO 2989</t>
+          <t>EINSTEIN ALBERTO 350</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -14097,7 +14085,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>813046757</t>
+          <t>813046733</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -14124,10 +14112,10 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>-58.428907</v>
+        <v>-58.413179</v>
       </c>
       <c r="N160" t="n">
-        <v>-34.653746</v>
+        <v>-34.649733</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -14141,7 +14129,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>PPT-J</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14153,7 +14141,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S00356525</t>
+          <t>S00334337</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14163,7 +14151,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>VILLARINO 2225</t>
+          <t>LUZURIAGA 905</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14183,7 +14171,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>813046763</t>
+          <t>813046739</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14210,10 +14198,10 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>-58.376974</v>
+        <v>-58.388385</v>
       </c>
       <c r="N161" t="n">
-        <v>-34.653657</v>
+        <v>-34.644336</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -14227,7 +14215,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>CON-I</t>
+          <t>CON-K</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -14239,7 +14227,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S01150941</t>
+          <t>S00337329</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14249,7 +14237,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>GUALEGUAY 1054</t>
+          <t>AV SAENZ 1319</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14269,7 +14257,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>813046767</t>
+          <t>813046749</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -14296,10 +14284,10 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>-58.368312</v>
+        <v>-58.416649</v>
       </c>
       <c r="N162" t="n">
-        <v>-34.632528</v>
+        <v>-34.656395</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -14313,7 +14301,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>CON-D</t>
+          <t>PPT-H</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -14325,7 +14313,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S00304430</t>
+          <t>S00355203</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14335,12 +14323,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BARZANA 1906</t>
+          <t>EREZCANO 2989</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14355,17 +14343,17 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>813046771</t>
+          <t>813046757</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>APLOMAR COLUMNA</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Aplomo</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -14382,24 +14370,24 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>-58.486035</v>
+        <v>-58.428907</v>
       </c>
       <c r="N163" t="n">
-        <v>-34.581541</v>
+        <v>-34.653746</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>ATH-S</t>
+          <t>PPT-J</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -14411,7 +14399,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S00363991</t>
+          <t>S00356525</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14421,12 +14409,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ARCOS 2981</t>
+          <t>VILLARINO 2225</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14441,7 +14429,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>813046774</t>
+          <t>813046763</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -14468,24 +14456,24 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>-58.461029</v>
+        <v>-58.376974</v>
       </c>
       <c r="N164" t="n">
-        <v>-34.552021</v>
+        <v>-34.653657</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>BLO-Q</t>
+          <t>CON-I</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -14497,7 +14485,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S00364003</t>
+          <t>S01150941</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14507,12 +14495,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>OHIGGINS 2715</t>
+          <t>GUALEGUAY 1054</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14527,7 +14515,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>813046777</t>
+          <t>813046767</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14554,24 +14542,24 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>-58.45782</v>
+        <v>-58.368312</v>
       </c>
       <c r="N165" t="n">
-        <v>-34.554154</v>
+        <v>-34.632528</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>BLO-Q</t>
+          <t>CON-D</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -14583,7 +14571,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S00364886</t>
+          <t>S00304430</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14593,12 +14581,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
+          <t>BARZANA 1906</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14613,17 +14601,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>813046778</t>
+          <t>813046771</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>CAMBIAR COLUMNA</t>
+          <t>APLOMAR COLUMNA</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Aplomo</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -14640,24 +14628,24 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>-58.434778</v>
+        <v>-58.486035</v>
       </c>
       <c r="N166" t="n">
-        <v>-34.569188</v>
+        <v>-34.581541</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Paternal</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>BLO-I</t>
+          <t>ATH-S</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -14669,7 +14657,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S00373014</t>
+          <t>S00363991</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14679,12 +14667,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BYRON 150</t>
+          <t>ARCOS 2981</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14699,7 +14687,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>813046780</t>
+          <t>813046774</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -14726,14 +14714,14 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>-58.501659</v>
+        <v>-58.461029</v>
       </c>
       <c r="N167" t="n">
-        <v>-34.63959</v>
+        <v>-34.552021</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Devoto</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -14743,7 +14731,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>PAV-F</t>
+          <t>BLO-Q</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -14755,7 +14743,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S00374917</t>
+          <t>S00364003</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14765,12 +14753,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>24 DE NOVIEMBRE 695</t>
+          <t>OHIGGINS 2715</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14785,7 +14773,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>813046791</t>
+          <t>813046777</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -14812,24 +14800,24 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>-58.411053</v>
+        <v>-58.45782</v>
       </c>
       <c r="N168" t="n">
-        <v>-34.618979</v>
+        <v>-34.554154</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>CEN-J</t>
+          <t>BLO-Q</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -14841,7 +14829,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S00379764</t>
+          <t>S00364886</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14851,12 +14839,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>JAURES JEAN 491</t>
+          <t>MATIENZO BENJAMIN TENIENTE 1830</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14871,7 +14859,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>813046795</t>
+          <t>813046778</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -14898,14 +14886,14 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>-58.408934</v>
+        <v>-58.434778</v>
       </c>
       <c r="N169" t="n">
-        <v>-34.604273</v>
+        <v>-34.569188</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -14915,7 +14903,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>CLI-H</t>
+          <t>BLO-I</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14927,7 +14915,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S00379996</t>
+          <t>S00373014</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14937,12 +14925,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SARANDI 1439</t>
+          <t>BYRON 150</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14957,7 +14945,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>813046806</t>
+          <t>813046780</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -14984,24 +14972,24 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>-58.393455</v>
+        <v>-58.501659</v>
       </c>
       <c r="N170" t="n">
-        <v>-34.625779</v>
+        <v>-34.63959</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Devoto</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Capital Sur</t>
+          <t>Capital Norte</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>CON-C</t>
+          <t>PAV-F</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15013,7 +15001,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>900009925610</t>
+          <t>S00374917</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15023,12 +15011,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ASUNCION 3283</t>
+          <t>24 DE NOVIEMBRE 695</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15043,17 +15031,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>813046810</t>
+          <t>813046791</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIENDA A PIQUE</t>
+          <t>CAMBIAR COLUMNA</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Tensor</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -15063,31 +15051,31 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Pasante</t>
         </is>
       </c>
       <c r="L171" t="n">
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>-58.501589</v>
+        <v>-58.411053</v>
       </c>
       <c r="N171" t="n">
-        <v>-34.594928</v>
+        <v>-34.618979</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Paternal</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Capital Norte</t>
+          <t>Capital Sur</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>PUE-G</t>
+          <t>CEN-J</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15099,7 +15087,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>S00379764</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15109,12 +15097,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ALCORTA AMANCIO AV 4200</t>
+          <t>JAURES JEAN 491</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15129,7 +15117,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>813046812</t>
+          <t>813046795</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -15156,14 +15144,14 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>-58.416172</v>
+        <v>-58.408934</v>
       </c>
       <c r="N172" t="n">
-        <v>-34.657075</v>
+        <v>-34.604273</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -15173,7 +15161,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>PPT-H</t>
+          <t>CLI-H</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -15185,7 +15173,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>S00379996</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15195,12 +15183,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CUENCA 2082</t>
+          <t>SARANDI 1439</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15215,17 +15203,17 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>813046813</t>
+          <t>813046806</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>NORMALIZAR RIEN